--- a/trackers/all-sites.xlsx
+++ b/trackers/all-sites.xlsx
@@ -2532,1970 +2532,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Dr. Vinay  ·  cioncancerdrvinay.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Slug</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Types of cancer surgery</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>types-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/types-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Laparoscopic cancer surgery explained</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>laparoscopic-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/laparoscopic-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Breast conservation surgery lumpectomy</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>lumpectomy-breast-surgery</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/lumpectomy-breast-surgery.html</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Mastectomy types and recovery</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>mastectomy-types-recovery</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/mastectomy-types-recovery.html</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Sentinel lymph node biopsy</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>sentinel-lymph-node-biopsy</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Thyroid cancer surgery</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>thyroid-surgery-cancer</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/thyroid-surgery-cancer.html</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Colorectal cancer surgery</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>colorectal-surgery</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/colorectal-surgery.html</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Colostomy explained for patients</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>colostomy-explained</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/colostomy-explained.html</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Ileostomy care and management</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>ileostomy-care</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/ileostomy-care.html</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Liver resection surgery</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>liver-resection-surgery</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/liver-resection-surgery.html</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Splenectomy for cancer</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>splenectomy-cancer</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/splenectomy-cancer.html</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Kidney nephrectomy surgery</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>nephrectomy-surgery</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/nephrectomy-surgery.html</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Ovarian cancer debulking surgery</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>ovarian-debulking-surgery</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/ovarian-debulking-surgery.html</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Cancer surgery wound care</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>cancer-surgery-wound-care</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-wound-care.html</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Post-surgery pain management</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>post-surgery-pain-management</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/post-surgery-pain-management.html</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Recovery after cancer surgery</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>cancer-surgery-recovery</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-recovery.html</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Cancer surgery complications</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>cancer-surgery-complications</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-complications.html</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>DVT prevention after cancer surgery</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>dvt-prevention-after-surgery</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/dvt-prevention-after-surgery.html</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Pre-surgery preparation for cancer</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>pre-surgery-preparation</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/pre-surgery-preparation.html</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Nutrition before cancer surgery</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>nutrition-before-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/nutrition-before-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Cancer surgery anaesthesia</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>cancer-surgery-anaesthesia</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-anaesthesia.html</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Surgical staging of cancer</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>surgical-staging-cancer</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/surgical-staging-cancer.html</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Curative vs palliative surgery</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>curative-vs-palliative-surgery</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/curative-vs-palliative-surgery.html</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breast reconstruction after mastectomy</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>breast-reconstruction-after-mastectomy</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/breast-reconstruction-after-mastectomy.html</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Port insertion for chemotherapy</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>port-insertion-surgery</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/port-insertion-surgery.html</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Thoracoscopy VATS cancer surgery</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>vats-thoracoscopy</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/vats-thoracoscopy.html</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Esophagectomy for esophageal cancer</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>esophagectomy-surgery</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/esophagectomy-surgery.html</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Gastrectomy types for stomach cancer</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>gastrectomy-types</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/gastrectomy-types.html</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Pancreatectomy procedure</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>pancreatectomy-procedure</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/pancreatectomy-procedure.html</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Whipple surgery recovery</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>whipple-surgery-recovery</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/whipple-surgery-recovery.html</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Hernia after cancer surgery</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>hernia-after-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/hernia-after-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Scar management after cancer surgery</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>scar-management-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/scar-management-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Cancer surgery in elderly patients</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>cancer-surgery-elderly</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-elderly.html</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Cancer surgery cost Hyderabad</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>cancer-surgery-cost-hyderabad</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-cost-hyderabad.html</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Questions before cancer surgery</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>cancer-surgery-questions</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-questions.html</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Life after cancer surgery</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>life-after-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/life-after-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Robotic cancer surgery India</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>robotic-cancer-surgery-india</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/robotic-cancer-surgery-india.html</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Abdominal cancer surgery recovery</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>abdominal-cancer-surgery-recovery</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/abdominal-cancer-surgery-recovery.html</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Rectal cancer surgery options</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>rectal-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/rectal-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Parathyroid surgery for cancer</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>parathyroid-surgery</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/parathyroid-surgery.html</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Adrenalectomy procedure</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>adrenalectomy-procedure</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/adrenalectomy-procedure.html</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Pelvic exenteration surgery</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>pelvic-exenteration-surgery</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/pelvic-exenteration-surgery.html</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Surgical removal of lymph nodes</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>lymph-node-removal-surgery</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/lymph-node-removal-surgery.html</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Cancer biopsy types explained</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>cancer-biopsy-types</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-biopsy-types.html</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Intraoperative frozen section</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>intraoperative-frozen-section</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/intraoperative-frozen-section.html</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>R0 R1 R2 resection margins</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>cancer-resection-margins</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-resection-margins.html</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Cancer surgery second opinion</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>cancer-surgery-second-opinion</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-surgery-second-opinion.html</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Day surgery cancer procedures</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>day-surgery-cancer</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/day-surgery-cancer.html</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Reconstructive flap surgery cancer</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>reconstructive-flap-surgery</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/reconstructive-flap-surgery.html</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Preparing questions for your surgeon</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>questions-for-cancer-surgeon</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/questions-for-cancer-surgeon.html</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/about.html</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>book-appointment</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/book-appointment.html</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>breast-cancer</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/breast-cancer.html</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>breast-conserving-surgery</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/breast-conserving-surgery.html</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>cancer-cost-and-aarogyasri</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-cost-and-aarogyasri.html</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>cancer-treatment-options</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-treatment-options.html</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>cancer-warning-signs</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cancer-warning-signs.html</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>caring-for-a-cancer-patient</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/caring-for-a-cancer-patient.html</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>cervical-cancer</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/cervical-cancer.html</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>faq</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/faq.html</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>how-cancer-is-diagnosed</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/how-cancer-is-diagnosed.html</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/index.html</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>mastectomy-and-reconstruction</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/mastectomy-and-reconstruction.html</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>oncoplastic-breast-surgery</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/oncoplastic-breast-surgery.html</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>privacy</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/privacy.html</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>second-opinion</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/second-opinion.html</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>sentinel-lymph-node-biopsy</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>(pre-existing page)</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>understanding-cancer</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/understanding-cancer.html</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId68"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4509,7 +2545,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Murali  ·  cioncancerdrmurali.com</t>
+          <t>Dr. Vinay  ·  cioncancerdrvinay.com</t>
         </is>
       </c>
     </row>
@@ -4543,49 +2579,49 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Melanoma surgery and margins</t>
+          <t>(pre-existing page)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>melanoma-surgery</t>
+          <t>stomach-cancer-surgery</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/melanoma-surgery.html</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+          <t>https://cioncancerdrvinay.com/stomach-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Skin cancer surgery types</t>
+          <t>Types of cancer surgery</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>skin-cancer-surgery</t>
+          <t>types-cancer-surgery</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/skin-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/types-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -4597,22 +2633,22 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Retroperitoneal sarcoma surgery</t>
+          <t>Laparoscopic cancer surgery explained</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>retroperitoneal-sarcoma-surgery</t>
+          <t>laparoscopic-cancer-surgery</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/retroperitoneal-sarcoma-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/laparoscopic-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -4624,22 +2660,22 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Leiomyosarcoma treatment</t>
+          <t>Breast conservation surgery lumpectomy</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>leiomyosarcoma-treatment</t>
+          <t>lumpectomy-breast-surgery</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/leiomyosarcoma-treatment.html</t>
+          <t>https://cioncancerdrvinay.com/lumpectomy-breast-surgery.html</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -4651,22 +2687,22 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Liposarcoma surgery</t>
+          <t>Mastectomy types and recovery</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>liposarcoma-surgery</t>
+          <t>mastectomy-types-recovery</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/liposarcoma-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/mastectomy-types-recovery.html</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -4678,22 +2714,22 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Limb-sparing surgery for bone cancer</t>
+          <t>Sentinel lymph node biopsy</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>limb-sparing-surgery</t>
+          <t>sentinel-lymph-node-biopsy</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/limb-sparing-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -4705,22 +2741,22 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Osteosarcoma limb salvage</t>
+          <t>Thyroid cancer surgery</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>osteosarcoma-limb-salvage</t>
+          <t>thyroid-surgery-cancer</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/osteosarcoma-limb-salvage.html</t>
+          <t>https://cioncancerdrvinay.com/thyroid-surgery-cancer.html</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -4732,22 +2768,22 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Rectal cancer sphincter preservation</t>
+          <t>Colorectal cancer surgery</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>rectal-sphincter-preservation</t>
+          <t>colorectal-surgery</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/rectal-sphincter-preservation.html</t>
+          <t>https://cioncancerdrvinay.com/colorectal-surgery.html</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -4759,22 +2795,22 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Low anterior resection surgery</t>
+          <t>Colostomy explained for patients</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>low-anterior-resection</t>
+          <t>colostomy-explained</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/low-anterior-resection.html</t>
+          <t>https://cioncancerdrvinay.com/colostomy-explained.html</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -4786,22 +2822,22 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Sigmoid colon cancer surgery</t>
+          <t>Ileostomy care and management</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>sigmoid-colon-cancer-surgery</t>
+          <t>ileostomy-care</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/sigmoid-colon-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/ileostomy-care.html</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -4813,22 +2849,22 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Laparoscopic bowel resection</t>
+          <t>Liver resection surgery</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>laparoscopic-bowel-resection</t>
+          <t>liver-resection-surgery</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/laparoscopic-bowel-resection.html</t>
+          <t>https://cioncancerdrvinay.com/liver-resection-surgery.html</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -4840,22 +2876,22 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Hemorrhoids vs rectal cancer</t>
+          <t>Splenectomy for cancer</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>hemorrhoids-vs-rectal-cancer</t>
+          <t>splenectomy-cancer</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/hemorrhoids-vs-rectal-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/splenectomy-cancer.html</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -4867,22 +2903,22 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Liver metastases surgery</t>
+          <t>Kidney nephrectomy surgery</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>liver-metastases-surgery</t>
+          <t>nephrectomy-surgery</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/liver-metastases-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/nephrectomy-surgery.html</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -4894,22 +2930,22 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Thermal ablation liver tumours</t>
+          <t>Ovarian cancer debulking surgery</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>thermal-ablation-liver-tumours</t>
+          <t>ovarian-debulking-surgery</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/thermal-ablation-liver-tumours.html</t>
+          <t>https://cioncancerdrvinay.com/ovarian-debulking-surgery.html</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -4921,22 +2957,22 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bile duct repair surgery</t>
+          <t>Cancer surgery wound care</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>bile-duct-repair-surgery</t>
+          <t>cancer-surgery-wound-care</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/bile-duct-repair-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-wound-care.html</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -4948,22 +2984,22 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Cholecystectomy for gallbladder cancer</t>
+          <t>Post-surgery pain management</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>cholecystectomy-gallbladder-cancer</t>
+          <t>post-surgery-pain-management</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cholecystectomy-gallbladder-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/post-surgery-pain-management.html</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -4975,22 +3011,22 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Total gastrectomy recovery</t>
+          <t>Recovery after cancer surgery</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>total-gastrectomy-recovery</t>
+          <t>cancer-surgery-recovery</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/total-gastrectomy-recovery.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-recovery.html</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -5002,22 +3038,22 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Small bowel resection surgery</t>
+          <t>Cancer surgery complications</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>small-bowel-resection</t>
+          <t>cancer-surgery-complications</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/small-bowel-resection.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-complications.html</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -5029,22 +3065,22 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Peritoneal wash cytology</t>
+          <t>DVT prevention after cancer surgery</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>peritoneal-wash-cytology</t>
+          <t>dvt-prevention-after-surgery</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/peritoneal-wash-cytology.html</t>
+          <t>https://cioncancerdrvinay.com/dvt-prevention-after-surgery.html</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -5056,22 +3092,22 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Second-look surgery ovarian cancer</t>
+          <t>Pre-surgery preparation for cancer</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>second-look-surgery-ovarian</t>
+          <t>pre-surgery-preparation</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/second-look-surgery-ovarian.html</t>
+          <t>https://cioncancerdrvinay.com/pre-surgery-preparation.html</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -5083,22 +3119,22 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Interval debulking surgery</t>
+          <t>Nutrition before cancer surgery</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>interval-debulking-surgery</t>
+          <t>nutrition-before-cancer-surgery</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/interval-debulking-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/nutrition-before-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -5110,22 +3146,22 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Cancer surgery in patients with diabetes</t>
+          <t>Cancer surgery anaesthesia</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>cancer-surgery-diabetes</t>
+          <t>cancer-surgery-anaesthesia</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cancer-surgery-diabetes.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-anaesthesia.html</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -5137,22 +3173,22 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Anastomosis leak prevention after bowel surgery</t>
+          <t>Surgical staging of cancer</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>anastomosis-leak-prevention</t>
+          <t>surgical-staging-cancer</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/anastomosis-leak-prevention.html</t>
+          <t>https://cioncancerdrvinay.com/surgical-staging-cancer.html</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -5164,22 +3200,22 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ewing sarcoma treatment</t>
+          <t>Curative vs palliative surgery</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>ewing-sarcoma-treatment</t>
+          <t>curative-vs-palliative-surgery</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/ewing-sarcoma-treatment.html</t>
+          <t>https://cioncancerdrvinay.com/curative-vs-palliative-surgery.html</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -5191,22 +3227,22 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Synovial sarcoma treatment</t>
+          <t>Breast reconstruction after mastectomy</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>synovial-sarcoma-treatment</t>
+          <t>breast-reconstruction-after-mastectomy</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/synovial-sarcoma-treatment.html</t>
+          <t>https://cioncancerdrvinay.com/breast-reconstruction-after-mastectomy.html</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -5218,22 +3254,22 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Amputation for bone cancer</t>
+          <t>Port insertion for chemotherapy</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>amputation-bone-cancer</t>
+          <t>port-insertion-surgery</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/amputation-bone-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/port-insertion-surgery.html</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -5245,22 +3281,22 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Right hemicolectomy surgery</t>
+          <t>Thoracoscopy VATS cancer surgery</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>right-hemicolectomy</t>
+          <t>vats-thoracoscopy</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/right-hemicolectomy.html</t>
+          <t>https://cioncancerdrvinay.com/vats-thoracoscopy.html</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -5272,22 +3308,22 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Left hemicolectomy surgery</t>
+          <t>Esophagectomy for esophageal cancer</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>left-hemicolectomy</t>
+          <t>esophagectomy-surgery</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/left-hemicolectomy.html</t>
+          <t>https://cioncancerdrvinay.com/esophagectomy-surgery.html</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -5299,22 +3335,22 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>D2 lymphadenectomy gastric cancer</t>
+          <t>Gastrectomy types for stomach cancer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>d2-lymphadenectomy-gastric</t>
+          <t>gastrectomy-types</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/d2-lymphadenectomy-gastric.html</t>
+          <t>https://cioncancerdrvinay.com/gastrectomy-types.html</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -5326,22 +3362,22 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Portal vein embolization surgery</t>
+          <t>Pancreatectomy procedure</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>portal-vein-embolization</t>
+          <t>pancreatectomy-procedure</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/portal-vein-embolization.html</t>
+          <t>https://cioncancerdrvinay.com/pancreatectomy-procedure.html</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -5353,22 +3389,22 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Distal pancreatectomy procedure</t>
+          <t>Whipple surgery recovery</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>distal-pancreatectomy</t>
+          <t>whipple-surgery-recovery</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/distal-pancreatectomy.html</t>
+          <t>https://cioncancerdrvinay.com/whipple-surgery-recovery.html</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -5380,22 +3416,22 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Gallbladder cancer radical cholecystectomy</t>
+          <t>Hernia after cancer surgery</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>radical-cholecystectomy-gallbladder</t>
+          <t>hernia-after-cancer-surgery</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/radical-cholecystectomy-gallbladder.html</t>
+          <t>https://cioncancerdrvinay.com/hernia-after-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -5407,22 +3443,22 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GIST gastrointestinal stromal tumour</t>
+          <t>Scar management after cancer surgery</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>gist-tumour-treatment</t>
+          <t>scar-management-cancer-surgery</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/gist-tumour-treatment.html</t>
+          <t>https://cioncancerdrvinay.com/scar-management-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -5434,22 +3470,22 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Mesenteric tumour resection</t>
+          <t>Cancer surgery in elderly patients</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>mesenteric-tumour-resection</t>
+          <t>cancer-surgery-elderly</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/mesenteric-tumour-resection.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-elderly.html</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -5461,22 +3497,22 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Colon cancer with peritoneal spread</t>
+          <t>Cancer surgery cost Hyderabad</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>colon-cancer-peritoneal-spread</t>
+          <t>cancer-surgery-cost-hyderabad</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/colon-cancer-peritoneal-spread.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-cost-hyderabad.html</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -5488,22 +3524,22 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Uterine cancer surgery</t>
+          <t>Questions before cancer surgery</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>uterine-cancer-surgery</t>
+          <t>cancer-surgery-questions</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/uterine-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-questions.html</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -5515,22 +3551,22 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Malignant ascites management</t>
+          <t>Life after cancer surgery</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>malignant-ascites-management</t>
+          <t>life-after-cancer-surgery</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/malignant-ascites-management.html</t>
+          <t>https://cioncancerdrvinay.com/life-after-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -5542,22 +3578,22 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Laparoscopic staging peritoneal cancer</t>
+          <t>Robotic cancer surgery India</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>laparoscopic-staging-peritoneal</t>
+          <t>robotic-cancer-surgery-india</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/laparoscopic-staging-peritoneal.html</t>
+          <t>https://cioncancerdrvinay.com/robotic-cancer-surgery-india.html</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -5569,22 +3605,22 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Transverse colon cancer surgery</t>
+          <t>Abdominal cancer surgery recovery</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>transverse-colon-cancer</t>
+          <t>abdominal-cancer-surgery-recovery</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/transverse-colon-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/abdominal-cancer-surgery-recovery.html</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -5596,22 +3632,22 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Anorectal cancer surgery</t>
+          <t>Rectal cancer surgery options</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>anorectal-cancer-surgery</t>
+          <t>rectal-cancer-surgery</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/anorectal-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/rectal-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -5623,22 +3659,22 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Diverticulitis vs colon cancer</t>
+          <t>Parathyroid surgery for cancer</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>diverticulitis-vs-colon-cancer</t>
+          <t>parathyroid-surgery</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/diverticulitis-vs-colon-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/parathyroid-surgery.html</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -5650,22 +3686,22 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Phantom limb pain management</t>
+          <t>Adrenalectomy procedure</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>phantom-limb-pain-management</t>
+          <t>adrenalectomy-procedure</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/phantom-limb-pain-management.html</t>
+          <t>https://cioncancerdrvinay.com/adrenalectomy-procedure.html</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -5677,22 +3713,22 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Intraoperative bleeding management</t>
+          <t>Pelvic exenteration surgery</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>intraoperative-bleeding-management</t>
+          <t>pelvic-exenteration-surgery</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/intraoperative-bleeding-management.html</t>
+          <t>https://cioncancerdrvinay.com/pelvic-exenteration-surgery.html</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -5704,22 +3740,22 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Liver cancer thermal microwave ablation</t>
+          <t>Surgical removal of lymph nodes</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>microwave-ablation-liver</t>
+          <t>lymph-node-removal-surgery</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/microwave-ablation-liver.html</t>
+          <t>https://cioncancerdrvinay.com/lymph-node-removal-surgery.html</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -5731,22 +3767,22 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Proximal gastrectomy stomach cancer</t>
+          <t>Cancer biopsy types explained</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>proximal-gastrectomy</t>
+          <t>cancer-biopsy-types</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/proximal-gastrectomy.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-biopsy-types.html</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -5758,22 +3794,22 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Pancreatic resection recovery</t>
+          <t>Intraoperative frozen section</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>pancreatic-resection-recovery</t>
+          <t>intraoperative-frozen-section</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/pancreatic-resection-recovery.html</t>
+          <t>https://cioncancerdrvinay.com/intraoperative-frozen-section.html</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -5785,22 +3821,22 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Abdominoperineal resection APR</t>
+          <t>R0 R1 R2 resection margins</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>abdominoperineal-resection</t>
+          <t>cancer-resection-margins</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/abdominoperineal-resection.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-resection-margins.html</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -5812,22 +3848,22 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Stoma reversal after bowel surgery</t>
+          <t>Cancer surgery second opinion</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>stoma-reversal-surgery</t>
+          <t>cancer-surgery-second-opinion</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/stoma-reversal-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-surgery-second-opinion.html</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -5839,22 +3875,22 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Enhanced recovery after surgery ERAS</t>
+          <t>Day surgery cancer procedures</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>eras-protocol-cancer-surgery</t>
+          <t>day-surgery-cancer</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/eras-protocol-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/day-surgery-cancer.html</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -5866,22 +3902,22 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cancer surgery blood loss management</t>
+          <t>Reconstructive flap surgery cancer</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>cancer-surgery-blood-loss</t>
+          <t>reconstructive-flap-surgery</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cancer-surgery-blood-loss.html</t>
+          <t>https://cioncancerdrvinay.com/reconstructive-flap-surgery.html</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -5893,27 +3929,27 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>(pre-existing page)</t>
+          <t>Preparing questions for your surgeon</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>questions-for-cancer-surgeon</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/about.html</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
+          <t>https://cioncancerdrvinay.com/questions-for-cancer-surgeon.html</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -5930,12 +3966,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>book-appointment</t>
+          <t>about</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/book-appointment.html</t>
+          <t>https://cioncancerdrvinay.com/about.html</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -5957,12 +3993,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>breast-surgery</t>
+          <t>book-appointment</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/breast-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/book-appointment.html</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -5984,12 +4020,12 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>cancer-cost-and-aarogyasri</t>
+          <t>breast-cancer</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cancer-cost-and-aarogyasri.html</t>
+          <t>https://cioncancerdrvinay.com/breast-cancer.html</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
@@ -6011,12 +4047,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>cancer-surgery</t>
+          <t>breast-conserving-surgery</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/breast-conserving-surgery.html</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -6038,12 +4074,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>cancer-treatment-options</t>
+          <t>cancer-cost-and-aarogyasri</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cancer-treatment-options.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-cost-and-aarogyasri.html</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
@@ -6065,12 +4101,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>cancer-warning-signs</t>
+          <t>cancer-treatment-options</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/cancer-warning-signs.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-treatment-options.html</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -6092,12 +4128,12 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>caring-for-a-cancer-patient</t>
+          <t>cancer-warning-signs</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/caring-for-a-cancer-patient.html</t>
+          <t>https://cioncancerdrvinay.com/cancer-warning-signs.html</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
@@ -6119,12 +4155,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>caring-for-a-cancer-patient</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/faq.html</t>
+          <t>https://cioncancerdrvinay.com/caring-for-a-cancer-patient.html</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -6146,12 +4182,12 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>gastrointestinal-cancer</t>
+          <t>cervical-cancer</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/gastrointestinal-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/cervical-cancer.html</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
@@ -6173,12 +4209,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>head-neck-surgery</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/head-neck-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/faq.html</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -6205,7 +4241,7 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/how-cancer-is-diagnosed.html</t>
+          <t>https://cioncancerdrvinay.com/how-cancer-is-diagnosed.html</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -6232,7 +4268,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/index.html</t>
+          <t>https://cioncancerdrvinay.com/index.html</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -6254,12 +4290,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>laparoscopic-cancer-surgery</t>
+          <t>mastectomy-and-reconstruction</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/laparoscopic-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/mastectomy-and-reconstruction.html</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -6281,12 +4317,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>oncoplastic-breast-surgery</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/privacy.html</t>
+          <t>https://cioncancerdrvinay.com/oncoplastic-breast-surgery.html</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -6308,12 +4344,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>robotic-cancer-surgery</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/robotic-cancer-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/privacy.html</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -6340,7 +4376,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/second-opinion.html</t>
+          <t>https://cioncancerdrvinay.com/second-opinion.html</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -6362,12 +4398,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>soft-tissue-sarcoma-surgery</t>
+          <t>sentinel-lymph-node-biopsy</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/soft-tissue-sarcoma-surgery.html</t>
+          <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -6394,7 +4430,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrmurali.com/understanding-cancer.html</t>
+          <t>https://cioncancerdrvinay.com/understanding-cancer.html</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -6482,13 +4518,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6501,7 +4537,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Sandeep  ·  cioncancerdrsandeep.com</t>
+          <t>Dr. Murali  ·  cioncancerdrmurali.com</t>
         </is>
       </c>
     </row>
@@ -6535,49 +4571,49 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Oral cancer surgery treatment</t>
+          <t>(pre-existing page)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>oral-cancer-surgery</t>
+          <t>pancreatic-cancer-surgery</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/oral-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+          <t>https://cioncancerdrmurali.com/pancreatic-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Tongue cancer treatment</t>
+          <t>Melanoma surgery and margins</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>tongue-cancer-treatment</t>
+          <t>melanoma-surgery</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/tongue-cancer-treatment.html</t>
+          <t>https://cioncancerdrmurali.com/melanoma-surgery.html</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -6589,22 +4625,22 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Lip cancer surgery</t>
+          <t>Skin cancer surgery types</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>lip-cancer-surgery</t>
+          <t>skin-cancer-surgery</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/lip-cancer-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/skin-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -6616,22 +4652,22 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Buccal mucosa cheek cancer</t>
+          <t>Retroperitoneal sarcoma surgery</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>buccal-mucosa-cancer</t>
+          <t>retroperitoneal-sarcoma-surgery</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/buccal-mucosa-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/retroperitoneal-sarcoma-surgery.html</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -6643,22 +4679,22 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Floor of mouth cancer</t>
+          <t>Leiomyosarcoma treatment</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>floor-of-mouth-cancer</t>
+          <t>leiomyosarcoma-treatment</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/floor-of-mouth-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/leiomyosarcoma-treatment.html</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -6670,22 +4706,22 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Laryngeal cancer voice box</t>
+          <t>Liposarcoma surgery</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>laryngeal-cancer-treatment</t>
+          <t>liposarcoma-surgery</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/laryngeal-cancer-treatment.html</t>
+          <t>https://cioncancerdrmurali.com/liposarcoma-surgery.html</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -6697,22 +4733,22 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Total laryngectomy voice rehabilitation</t>
+          <t>Limb-sparing surgery for bone cancer</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>laryngectomy-voice-rehab</t>
+          <t>limb-sparing-surgery</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/laryngectomy-voice-rehab.html</t>
+          <t>https://cioncancerdrmurali.com/limb-sparing-surgery.html</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -6724,22 +4760,22 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Hypopharyngeal cancer</t>
+          <t>Osteosarcoma limb salvage</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>hypopharyngeal-cancer</t>
+          <t>osteosarcoma-limb-salvage</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/hypopharyngeal-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/osteosarcoma-limb-salvage.html</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -6751,22 +4787,22 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Oropharyngeal cancer HPV related</t>
+          <t>Rectal cancer sphincter preservation</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>oropharyngeal-cancer-hpv</t>
+          <t>rectal-sphincter-preservation</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/oropharyngeal-cancer-hpv.html</t>
+          <t>https://cioncancerdrmurali.com/rectal-sphincter-preservation.html</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -6778,22 +4814,22 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Tonsil cancer treatment</t>
+          <t>Low anterior resection surgery</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>tonsil-cancer-treatment</t>
+          <t>low-anterior-resection</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/tonsil-cancer-treatment.html</t>
+          <t>https://cioncancerdrmurali.com/low-anterior-resection.html</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -6805,22 +4841,22 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Nasopharyngeal cancer</t>
+          <t>Sigmoid colon cancer surgery</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>nasopharyngeal-cancer</t>
+          <t>sigmoid-colon-cancer-surgery</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/nasopharyngeal-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/sigmoid-colon-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -6832,22 +4868,22 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Nasal cavity cancer</t>
+          <t>Laparoscopic bowel resection</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>nasal-cavity-cancer</t>
+          <t>laparoscopic-bowel-resection</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/nasal-cavity-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/laparoscopic-bowel-resection.html</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -6859,22 +4895,22 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Salivary gland cancer types</t>
+          <t>Hemorrhoids vs rectal cancer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>salivary-gland-cancer</t>
+          <t>hemorrhoids-vs-rectal-cancer</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/salivary-gland-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/hemorrhoids-vs-rectal-cancer.html</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -6886,22 +4922,22 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Parotid gland tumour surgery</t>
+          <t>Liver metastases surgery</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>parotid-gland-surgery</t>
+          <t>liver-metastases-surgery</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/parotid-gland-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/liver-metastases-surgery.html</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -6913,22 +4949,22 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Neck dissection types</t>
+          <t>Thermal ablation liver tumours</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>neck-dissection-types</t>
+          <t>thermal-ablation-liver-tumours</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/neck-dissection-types.html</t>
+          <t>https://cioncancerdrmurali.com/thermal-ablation-liver-tumours.html</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -6940,22 +4976,22 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Modified radical neck dissection</t>
+          <t>Bile duct repair surgery</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>modified-radical-neck-dissection</t>
+          <t>bile-duct-repair-surgery</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/modified-radical-neck-dissection.html</t>
+          <t>https://cioncancerdrmurali.com/bile-duct-repair-surgery.html</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -6967,22 +5003,22 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Total thyroidectomy surgery</t>
+          <t>Cholecystectomy for gallbladder cancer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>total-thyroidectomy</t>
+          <t>cholecystectomy-gallbladder-cancer</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/total-thyroidectomy.html</t>
+          <t>https://cioncancerdrmurali.com/cholecystectomy-gallbladder-cancer.html</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -6994,22 +5030,22 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Papillary thyroid cancer treatment</t>
+          <t>Total gastrectomy recovery</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>papillary-thyroid-cancer</t>
+          <t>total-gastrectomy-recovery</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/papillary-thyroid-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/total-gastrectomy-recovery.html</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -7021,22 +5057,22 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Follicular thyroid cancer</t>
+          <t>Small bowel resection surgery</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>follicular-thyroid-cancer</t>
+          <t>small-bowel-resection</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/follicular-thyroid-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/small-bowel-resection.html</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -7048,22 +5084,22 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Medullary thyroid cancer</t>
+          <t>Peritoneal wash cytology</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>medullary-thyroid-cancer</t>
+          <t>peritoneal-wash-cytology</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/medullary-thyroid-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/peritoneal-wash-cytology.html</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -7075,22 +5111,22 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Thyroid cancer recurrence</t>
+          <t>Second-look surgery ovarian cancer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>thyroid-cancer-recurrence</t>
+          <t>second-look-surgery-ovarian</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/thyroid-cancer-recurrence.html</t>
+          <t>https://cioncancerdrmurali.com/second-look-surgery-ovarian.html</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -7102,22 +5138,22 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Skull base tumour surgery</t>
+          <t>Interval debulking surgery</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>skull-base-tumour-surgery</t>
+          <t>interval-debulking-surgery</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/skull-base-tumour-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/interval-debulking-surgery.html</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -7129,22 +5165,22 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Carotid body tumour paraganglioma</t>
+          <t>Cancer surgery in patients with diabetes</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>paraganglioma-treatment</t>
+          <t>cancer-surgery-diabetes</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/paraganglioma-treatment.html</t>
+          <t>https://cioncancerdrmurali.com/cancer-surgery-diabetes.html</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -7156,22 +5192,22 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Adenoid cystic carcinoma</t>
+          <t>Anastomosis leak prevention after bowel surgery</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>adenoid-cystic-carcinoma</t>
+          <t>anastomosis-leak-prevention</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/adenoid-cystic-carcinoma.html</t>
+          <t>https://cioncancerdrmurali.com/anastomosis-leak-prevention.html</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -7183,22 +5219,22 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Mucoepidermoid carcinoma</t>
+          <t>Ewing sarcoma treatment</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>mucoepidermoid-carcinoma</t>
+          <t>ewing-sarcoma-treatment</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/mucoepidermoid-carcinoma.html</t>
+          <t>https://cioncancerdrmurali.com/ewing-sarcoma-treatment.html</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -7210,22 +5246,22 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Head neck cancer trismus jaw</t>
+          <t>Synovial sarcoma treatment</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>head-neck-cancer-trismus</t>
+          <t>synovial-sarcoma-treatment</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/head-neck-cancer-trismus.html</t>
+          <t>https://cioncancerdrmurali.com/synovial-sarcoma-treatment.html</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -7237,22 +5273,22 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Dry mouth xerostomia after head neck cancer</t>
+          <t>Amputation for bone cancer</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>xerostomia-cancer-treatment</t>
+          <t>amputation-bone-cancer</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/xerostomia-cancer-treatment.html</t>
+          <t>https://cioncancerdrmurali.com/amputation-bone-cancer.html</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -7264,22 +5300,22 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Swallowing difficulty after head neck cancer</t>
+          <t>Right hemicolectomy surgery</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>dysphagia-head-neck-cancer</t>
+          <t>right-hemicolectomy</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/dysphagia-head-neck-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/right-hemicolectomy.html</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -7291,22 +5327,22 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Head neck cancer rehabilitation</t>
+          <t>Left hemicolectomy surgery</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>head-neck-cancer-rehabilitation</t>
+          <t>left-hemicolectomy</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/head-neck-cancer-rehabilitation.html</t>
+          <t>https://cioncancerdrmurali.com/left-hemicolectomy.html</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -7318,22 +5354,22 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Speech therapy after laryngectomy</t>
+          <t>D2 lymphadenectomy gastric cancer</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>speech-therapy-laryngectomy</t>
+          <t>d2-lymphadenectomy-gastric</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/speech-therapy-laryngectomy.html</t>
+          <t>https://cioncancerdrmurali.com/d2-lymphadenectomy-gastric.html</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -7345,22 +5381,22 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Neck lump when to worry</t>
+          <t>Portal vein embolization surgery</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>neck-lump-causes</t>
+          <t>portal-vein-embolization</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/neck-lump-causes.html</t>
+          <t>https://cioncancerdrmurali.com/portal-vein-embolization.html</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -7372,22 +5408,22 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Hoarseness persistent causes cancer</t>
+          <t>Distal pancreatectomy procedure</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>hoarseness-cancer-signs</t>
+          <t>distal-pancreatectomy</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/hoarseness-cancer-signs.html</t>
+          <t>https://cioncancerdrmurali.com/distal-pancreatectomy.html</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -7399,22 +5435,22 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Non-healing mouth ulcer and cancer</t>
+          <t>Gallbladder cancer radical cholecystectomy</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>mouth-ulcer-cancer-warning</t>
+          <t>radical-cholecystectomy-gallbladder</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/mouth-ulcer-cancer-warning.html</t>
+          <t>https://cioncancerdrmurali.com/radical-cholecystectomy-gallbladder.html</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -7426,22 +5462,22 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Leukoplakia oral cancer risk</t>
+          <t>GIST gastrointestinal stromal tumour</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>leukoplakia-oral-cancer</t>
+          <t>gist-tumour-treatment</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/leukoplakia-oral-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/gist-tumour-treatment.html</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -7453,22 +5489,22 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Submucous fibrosis and cancer</t>
+          <t>Mesenteric tumour resection</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>submucous-fibrosis-cancer</t>
+          <t>mesenteric-tumour-resection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/submucous-fibrosis-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/mesenteric-tumour-resection.html</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -7480,22 +5516,22 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Tobacco gutka and oral cancer</t>
+          <t>Colon cancer with peritoneal spread</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>tobacco-oral-cancer</t>
+          <t>colon-cancer-peritoneal-spread</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/tobacco-oral-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/colon-cancer-peritoneal-spread.html</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -7507,22 +5543,22 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Base of tongue cancer</t>
+          <t>Uterine cancer surgery</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>base-of-tongue-cancer</t>
+          <t>uterine-cancer-surgery</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/base-of-tongue-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/uterine-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -7534,22 +5570,22 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Partial laryngectomy voice preservation</t>
+          <t>Malignant ascites management</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>partial-laryngectomy</t>
+          <t>malignant-ascites-management</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/partial-laryngectomy.html</t>
+          <t>https://cioncancerdrmurali.com/malignant-ascites-management.html</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -7561,22 +5597,22 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Palate cancer surgery</t>
+          <t>Laparoscopic staging peritoneal cancer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>palate-cancer-surgery</t>
+          <t>laparoscopic-staging-peritoneal</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/palate-cancer-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/laparoscopic-staging-peritoneal.html</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -7588,22 +5624,22 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Jaw mandibular cancer surgery</t>
+          <t>Transverse colon cancer surgery</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>jaw-cancer-surgery</t>
+          <t>transverse-colon-cancer</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/jaw-cancer-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/transverse-colon-cancer.html</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -7615,22 +5651,22 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Paranasal sinus cancer</t>
+          <t>Anorectal cancer surgery</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>paranasal-sinus-cancer</t>
+          <t>anorectal-cancer-surgery</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/paranasal-sinus-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/anorectal-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -7642,22 +5678,22 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Anaplastic thyroid cancer</t>
+          <t>Diverticulitis vs colon cancer</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>anaplastic-thyroid-cancer</t>
+          <t>diverticulitis-vs-colon-cancer</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/anaplastic-thyroid-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/diverticulitis-vs-colon-cancer.html</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -7669,22 +5705,22 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Head neck cancer Hyderabad treatment</t>
+          <t>Phantom limb pain management</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>head-neck-cancer-hyderabad</t>
+          <t>phantom-limb-pain-management</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/head-neck-cancer-hyderabad.html</t>
+          <t>https://cioncancerdrmurali.com/phantom-limb-pain-management.html</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -7696,22 +5732,22 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Swallowing therapy after head neck cancer</t>
+          <t>Intraoperative bleeding management</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>swallowing-therapy-cancer</t>
+          <t>intraoperative-bleeding-management</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/swallowing-therapy-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/intraoperative-bleeding-management.html</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -7723,22 +5759,22 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Radiation after head neck surgery</t>
+          <t>Liver cancer thermal microwave ablation</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>radiation-head-neck-surgery</t>
+          <t>microwave-ablation-liver</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/radiation-head-neck-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/microwave-ablation-liver.html</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -7750,22 +5786,22 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Chemotherapy for head neck cancer</t>
+          <t>Proximal gastrectomy stomach cancer</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>chemotherapy-head-neck-cancer</t>
+          <t>proximal-gastrectomy</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/chemotherapy-head-neck-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/proximal-gastrectomy.html</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -7777,22 +5813,22 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Head neck cancer nutrition support</t>
+          <t>Pancreatic resection recovery</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>head-neck-cancer-nutrition</t>
+          <t>pancreatic-resection-recovery</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/head-neck-cancer-nutrition.html</t>
+          <t>https://cioncancerdrmurali.com/pancreatic-resection-recovery.html</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -7804,22 +5840,22 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Tracheostomy care after head neck surgery</t>
+          <t>Abdominoperineal resection APR</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>tracheostomy-care-cancer</t>
+          <t>abdominoperineal-resection</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/tracheostomy-care-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/abdominoperineal-resection.html</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -7831,22 +5867,22 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Reconstructive surgery after head neck cancer</t>
+          <t>Stoma reversal after bowel surgery</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>reconstruction-head-neck-cancer</t>
+          <t>stoma-reversal-surgery</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/reconstruction-head-neck-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/stoma-reversal-surgery.html</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -7858,22 +5894,22 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Questions to ask head neck cancer surgeon</t>
+          <t>Enhanced recovery after surgery ERAS</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>head-neck-cancer-surgeon-questions</t>
+          <t>eras-protocol-cancer-surgery</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/head-neck-cancer-surgeon-questions.html</t>
+          <t>https://cioncancerdrmurali.com/eras-protocol-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -7885,27 +5921,27 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>(pre-existing page)</t>
+          <t>Cancer surgery blood loss management</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>cancer-surgery-blood-loss</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/about.html</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
+          <t>https://cioncancerdrmurali.com/cancer-surgery-blood-loss.html</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -7922,12 +5958,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>book-appointment</t>
+          <t>about</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/book-appointment.html</t>
+          <t>https://cioncancerdrmurali.com/about.html</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -7949,12 +5985,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>cancer-cost-and-aarogyasri</t>
+          <t>book-appointment</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/cancer-cost-and-aarogyasri.html</t>
+          <t>https://cioncancerdrmurali.com/book-appointment.html</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -7976,12 +6012,12 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>cancer-treatment-options</t>
+          <t>breast-surgery</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/cancer-treatment-options.html</t>
+          <t>https://cioncancerdrmurali.com/breast-surgery.html</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
@@ -8003,12 +6039,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>cancer-warning-signs</t>
+          <t>cancer-cost-and-aarogyasri</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/cancer-warning-signs.html</t>
+          <t>https://cioncancerdrmurali.com/cancer-cost-and-aarogyasri.html</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -8030,12 +6066,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>caring-for-a-cancer-patient</t>
+          <t>cancer-surgery</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/caring-for-a-cancer-patient.html</t>
+          <t>https://cioncancerdrmurali.com/cancer-surgery.html</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
@@ -8057,12 +6093,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>cancer-treatment-options</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/faq.html</t>
+          <t>https://cioncancerdrmurali.com/cancer-treatment-options.html</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -8084,12 +6120,12 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>how-cancer-is-diagnosed</t>
+          <t>cancer-warning-signs</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/how-cancer-is-diagnosed.html</t>
+          <t>https://cioncancerdrmurali.com/cancer-warning-signs.html</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
@@ -8111,12 +6147,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>caring-for-a-cancer-patient</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/index.html</t>
+          <t>https://cioncancerdrmurali.com/caring-for-a-cancer-patient.html</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -8138,12 +6174,12 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>laryngeal-cancer-surgery</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/laryngeal-cancer-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/faq.html</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
@@ -8165,12 +6201,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>neck-dissection</t>
+          <t>gastrointestinal-cancer</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/neck-dissection.html</t>
+          <t>https://cioncancerdrmurali.com/gastrointestinal-cancer.html</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -8192,12 +6228,12 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>oral-cancer</t>
+          <t>head-neck-surgery</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/oral-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/head-neck-surgery.html</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -8219,12 +6255,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>how-cancer-is-diagnosed</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/privacy.html</t>
+          <t>https://cioncancerdrmurali.com/how-cancer-is-diagnosed.html</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -8246,12 +6282,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>salivary-gland-tumour</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/salivary-gland-tumour.html</t>
+          <t>https://cioncancerdrmurali.com/index.html</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -8273,12 +6309,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>second-opinion</t>
+          <t>laparoscopic-cancer-surgery</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/second-opinion.html</t>
+          <t>https://cioncancerdrmurali.com/laparoscopic-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -8300,12 +6336,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>throat-cancer</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/throat-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/privacy.html</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -8327,12 +6363,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>thyroid-cancer</t>
+          <t>robotic-cancer-surgery</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/thyroid-cancer.html</t>
+          <t>https://cioncancerdrmurali.com/robotic-cancer-surgery.html</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -8354,12 +6390,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>tongue-cancer-surgery</t>
+          <t>second-opinion</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrsandeep.com/tongue-cancer-surgery.html</t>
+          <t>https://cioncancerdrmurali.com/second-opinion.html</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -8381,15 +6417,42 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
+          <t>soft-tissue-sarcoma-surgery</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrmurali.com/soft-tissue-sarcoma-surgery.html</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
           <t>understanding-cancer</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrsandeep.com/understanding-cancer.html</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrmurali.com/understanding-cancer.html</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>Published ✓</t>
         </is>
@@ -8469,6 +6532,2027 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId70"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dr. Sandeep  ·  cioncancerdrsandeep.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>parotid-gland-tumour-surgery</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/parotid-gland-tumour-surgery.html</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Oral cancer surgery treatment</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>oral-cancer-surgery</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/oral-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tongue cancer treatment</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>tongue-cancer-treatment</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/tongue-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Lip cancer surgery</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>lip-cancer-surgery</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/lip-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Buccal mucosa cheek cancer</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>buccal-mucosa-cancer</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/buccal-mucosa-cancer.html</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Floor of mouth cancer</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>floor-of-mouth-cancer</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/floor-of-mouth-cancer.html</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Laryngeal cancer voice box</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>laryngeal-cancer-treatment</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/laryngeal-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Total laryngectomy voice rehabilitation</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>laryngectomy-voice-rehab</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/laryngectomy-voice-rehab.html</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Hypopharyngeal cancer</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>hypopharyngeal-cancer</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/hypopharyngeal-cancer.html</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Oropharyngeal cancer HPV related</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>oropharyngeal-cancer-hpv</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/oropharyngeal-cancer-hpv.html</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Tonsil cancer treatment</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>tonsil-cancer-treatment</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/tonsil-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Nasopharyngeal cancer</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>nasopharyngeal-cancer</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/nasopharyngeal-cancer.html</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Nasal cavity cancer</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>nasal-cavity-cancer</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/nasal-cavity-cancer.html</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Salivary gland cancer types</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>salivary-gland-cancer</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/salivary-gland-cancer.html</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Parotid gland tumour surgery</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>parotid-gland-surgery</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/parotid-gland-surgery.html</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Neck dissection types</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>neck-dissection-types</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/neck-dissection-types.html</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Modified radical neck dissection</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>modified-radical-neck-dissection</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/modified-radical-neck-dissection.html</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Total thyroidectomy surgery</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>total-thyroidectomy</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/total-thyroidectomy.html</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Papillary thyroid cancer treatment</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>papillary-thyroid-cancer</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/papillary-thyroid-cancer.html</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Follicular thyroid cancer</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>follicular-thyroid-cancer</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/follicular-thyroid-cancer.html</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Medullary thyroid cancer</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>medullary-thyroid-cancer</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/medullary-thyroid-cancer.html</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Thyroid cancer recurrence</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>thyroid-cancer-recurrence</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/thyroid-cancer-recurrence.html</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Skull base tumour surgery</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>skull-base-tumour-surgery</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/skull-base-tumour-surgery.html</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Carotid body tumour paraganglioma</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>paraganglioma-treatment</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/paraganglioma-treatment.html</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Adenoid cystic carcinoma</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>adenoid-cystic-carcinoma</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/adenoid-cystic-carcinoma.html</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Mucoepidermoid carcinoma</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>mucoepidermoid-carcinoma</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/mucoepidermoid-carcinoma.html</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Head neck cancer trismus jaw</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>head-neck-cancer-trismus</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/head-neck-cancer-trismus.html</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Dry mouth xerostomia after head neck cancer</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>xerostomia-cancer-treatment</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/xerostomia-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Swallowing difficulty after head neck cancer</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>dysphagia-head-neck-cancer</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/dysphagia-head-neck-cancer.html</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Head neck cancer rehabilitation</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>head-neck-cancer-rehabilitation</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/head-neck-cancer-rehabilitation.html</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Speech therapy after laryngectomy</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>speech-therapy-laryngectomy</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/speech-therapy-laryngectomy.html</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Neck lump when to worry</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>neck-lump-causes</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/neck-lump-causes.html</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Hoarseness persistent causes cancer</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>hoarseness-cancer-signs</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/hoarseness-cancer-signs.html</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Non-healing mouth ulcer and cancer</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>mouth-ulcer-cancer-warning</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/mouth-ulcer-cancer-warning.html</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Leukoplakia oral cancer risk</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>leukoplakia-oral-cancer</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/leukoplakia-oral-cancer.html</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Submucous fibrosis and cancer</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>submucous-fibrosis-cancer</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/submucous-fibrosis-cancer.html</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Tobacco gutka and oral cancer</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>tobacco-oral-cancer</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/tobacco-oral-cancer.html</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Base of tongue cancer</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>base-of-tongue-cancer</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/base-of-tongue-cancer.html</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Partial laryngectomy voice preservation</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>partial-laryngectomy</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/partial-laryngectomy.html</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Palate cancer surgery</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>palate-cancer-surgery</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/palate-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Jaw mandibular cancer surgery</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>jaw-cancer-surgery</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/jaw-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Paranasal sinus cancer</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>paranasal-sinus-cancer</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/paranasal-sinus-cancer.html</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Anaplastic thyroid cancer</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>anaplastic-thyroid-cancer</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/anaplastic-thyroid-cancer.html</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Head neck cancer Hyderabad treatment</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>head-neck-cancer-hyderabad</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/head-neck-cancer-hyderabad.html</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Swallowing therapy after head neck cancer</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>swallowing-therapy-cancer</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/swallowing-therapy-cancer.html</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Radiation after head neck surgery</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>radiation-head-neck-surgery</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/radiation-head-neck-surgery.html</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Chemotherapy for head neck cancer</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>chemotherapy-head-neck-cancer</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/chemotherapy-head-neck-cancer.html</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Head neck cancer nutrition support</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>head-neck-cancer-nutrition</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/head-neck-cancer-nutrition.html</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Tracheostomy care after head neck surgery</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>tracheostomy-care-cancer</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/tracheostomy-care-cancer.html</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Reconstructive surgery after head neck cancer</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>reconstruction-head-neck-cancer</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/reconstruction-head-neck-cancer.html</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Questions to ask head neck cancer surgeon</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>head-neck-cancer-surgeon-questions</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/head-neck-cancer-surgeon-questions.html</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>about</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/about.html</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>book-appointment</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/book-appointment.html</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>cancer-cost-and-aarogyasri</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/cancer-cost-and-aarogyasri.html</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>cancer-treatment-options</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/cancer-treatment-options.html</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>cancer-warning-signs</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/cancer-warning-signs.html</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>caring-for-a-cancer-patient</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/caring-for-a-cancer-patient.html</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>faq</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/faq.html</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>how-cancer-is-diagnosed</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/how-cancer-is-diagnosed.html</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/index.html</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>laryngeal-cancer-surgery</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/laryngeal-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>neck-dissection</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/neck-dissection.html</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>oral-cancer</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/oral-cancer.html</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/privacy.html</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>salivary-gland-tumour</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/salivary-gland-tumour.html</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>second-opinion</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/second-opinion.html</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>throat-cancer</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/throat-cancer.html</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>thyroid-cancer</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/thyroid-cancer.html</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>tongue-cancer-surgery</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/tongue-cancer-surgery.html</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>understanding-cancer</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrsandeep.com/understanding-cancer.html</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trackers/all-sites.xlsx
+++ b/trackers/all-sites.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,13 @@
       <color rgb="00888888"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +85,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -141,10 +151,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -623,17 +645,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>nausea-vomiting-chemotherapy</t>
+          <t>what-is-a-chemo-port</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/nausea-vomiting-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+          <t>https://cioncancerdrowais.com/what-is-a-chemo-port.html</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
         </is>
       </c>
     </row>
@@ -658,7 +680,7 @@
           <t>https://cioncancerdrowais.com/hair-loss-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -685,7 +707,7 @@
           <t>https://cioncancerdrowais.com/cancer-fatigue-management.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -712,7 +734,7 @@
           <t>https://cioncancerdrowais.com/cancer-nutrition-diet.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -739,7 +761,7 @@
           <t>https://cioncancerdrowais.com/breast-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -766,7 +788,7 @@
           <t>https://cioncancerdrowais.com/cervical-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -793,7 +815,7 @@
           <t>https://cioncancerdrowais.com/ovarian-cancer-diagnosis.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -820,7 +842,7 @@
           <t>https://cioncancerdrowais.com/colorectal-cancer-screening.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -847,7 +869,7 @@
           <t>https://cioncancerdrowais.com/what-is-lymphoma.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -874,7 +896,7 @@
           <t>https://cioncancerdrowais.com/types-of-leukemia.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -901,7 +923,7 @@
           <t>https://cioncancerdrowais.com/multiple-myeloma-treatment.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -928,7 +950,7 @@
           <t>https://cioncancerdrowais.com/blood-tests-cancer-diagnosis.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -955,7 +977,7 @@
           <t>https://cioncancerdrowais.com/pet-ct-scan-explained.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -982,7 +1004,7 @@
           <t>https://cioncancerdrowais.com/palliative-care-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1009,7 +1031,7 @@
           <t>https://cioncancerdrowais.com/genetic-testing-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1036,7 +1058,7 @@
           <t>https://cioncancerdrowais.com/hereditary-cancer-syndromes.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1063,7 +1085,7 @@
           <t>https://cioncancerdrowais.com/managing-cancer-recurrence.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1090,7 +1112,7 @@
           <t>https://cioncancerdrowais.com/immunotherapy-side-effects.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1117,7 +1139,7 @@
           <t>https://cioncancerdrowais.com/targeted-therapy-explained.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1144,7 +1166,7 @@
           <t>https://cioncancerdrowais.com/oral-chemotherapy-medications.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1171,7 +1193,7 @@
           <t>https://cioncancerdrowais.com/chemotherapy-port-explained.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1198,7 +1220,7 @@
           <t>https://cioncancerdrowais.com/cancer-clinical-trials-india.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1225,7 +1247,7 @@
           <t>https://cioncancerdrowais.com/questions-to-ask-oncologist.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1252,7 +1274,7 @@
           <t>https://cioncancerdrowais.com/cancer-survivorship-care.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1279,7 +1301,7 @@
           <t>https://cioncancerdrowais.com/fertility-preservation-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1306,7 +1328,7 @@
           <t>https://cioncancerdrowais.com/mouth-sores-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1333,7 +1355,7 @@
           <t>https://cioncancerdrowais.com/chemotherapy-neuropathy.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1360,7 +1382,7 @@
           <t>https://cioncancerdrowais.com/cancer-diabetes-management.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1387,7 +1409,7 @@
           <t>https://cioncancerdrowais.com/blood-transfusion-cancer.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1414,7 +1436,7 @@
           <t>https://cioncancerdrowais.com/anti-nausea-medications-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1441,7 +1463,7 @@
           <t>https://cioncancerdrowais.com/cancer-diagnosis-process.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1468,7 +1490,7 @@
           <t>https://cioncancerdrowais.com/reading-pathology-report.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1495,7 +1517,7 @@
           <t>https://cioncancerdrowais.com/cancer-prognosis-explained.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1522,7 +1544,7 @@
           <t>https://cioncancerdrowais.com/cancer-related-anaemia.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1549,7 +1571,7 @@
           <t>https://cioncancerdrowais.com/skin-changes-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1576,7 +1598,7 @@
           <t>https://cioncancerdrowais.com/cancer-treatment-pregnancy.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1603,7 +1625,7 @@
           <t>https://cioncancerdrowais.com/triple-negative-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1630,7 +1652,7 @@
           <t>https://cioncancerdrowais.com/her2-positive-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1657,7 +1679,7 @@
           <t>https://cioncancerdrowais.com/stomach-cancer-symptoms.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1684,7 +1706,7 @@
           <t>https://cioncancerdrowais.com/kidney-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1711,7 +1733,7 @@
           <t>https://cioncancerdrowais.com/bladder-cancer-diagnosis.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1738,7 +1760,7 @@
           <t>https://cioncancerdrowais.com/thyroid-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1765,7 +1787,7 @@
           <t>https://cioncancerdrowais.com/prostate-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1792,7 +1814,7 @@
           <t>https://cioncancerdrowais.com/esophageal-cancer-symptoms.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1819,7 +1841,7 @@
           <t>https://cioncancerdrowais.com/cervical-cancer-hpv-vaccine.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1846,7 +1868,7 @@
           <t>https://cioncancerdrowais.com/cancer-screening-india.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1873,7 +1895,7 @@
           <t>https://cioncancerdrowais.com/why-cancer-second-opinion.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1900,7 +1922,7 @@
           <t>https://cioncancerdrowais.com/preparing-for-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1927,7 +1949,7 @@
           <t>https://cioncancerdrowais.com/cancer-caregiver-guide.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1954,7 +1976,7 @@
           <t>https://cioncancerdrowais.com/cancer-pain-relief.html</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2660,29 +2682,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Types of cancer surgery</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>types-cancer-surgery</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrvinay.com/types-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2729,7 @@
           <t>https://cioncancerdrvinay.com/laparoscopic-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2734,7 +2756,7 @@
           <t>https://cioncancerdrvinay.com/lumpectomy-breast-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2761,7 +2783,7 @@
           <t>https://cioncancerdrvinay.com/mastectomy-types-recovery.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2788,7 +2810,7 @@
           <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2815,7 +2837,7 @@
           <t>https://cioncancerdrvinay.com/thyroid-surgery-cancer.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2842,7 +2864,7 @@
           <t>https://cioncancerdrvinay.com/colorectal-surgery.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2869,7 +2891,7 @@
           <t>https://cioncancerdrvinay.com/colostomy-explained.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2896,7 +2918,7 @@
           <t>https://cioncancerdrvinay.com/ileostomy-care.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2923,7 +2945,7 @@
           <t>https://cioncancerdrvinay.com/liver-resection-surgery.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2950,7 +2972,7 @@
           <t>https://cioncancerdrvinay.com/splenectomy-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2977,7 +2999,7 @@
           <t>https://cioncancerdrvinay.com/nephrectomy-surgery.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3004,7 +3026,7 @@
           <t>https://cioncancerdrvinay.com/ovarian-debulking-surgery.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3031,7 +3053,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-wound-care.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3058,7 +3080,7 @@
           <t>https://cioncancerdrvinay.com/post-surgery-pain-management.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3085,7 +3107,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3112,7 +3134,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-complications.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3139,7 +3161,7 @@
           <t>https://cioncancerdrvinay.com/dvt-prevention-after-surgery.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3166,7 +3188,7 @@
           <t>https://cioncancerdrvinay.com/pre-surgery-preparation.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3193,7 +3215,7 @@
           <t>https://cioncancerdrvinay.com/nutrition-before-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3220,7 +3242,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-anaesthesia.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3247,7 +3269,7 @@
           <t>https://cioncancerdrvinay.com/surgical-staging-cancer.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3274,7 +3296,7 @@
           <t>https://cioncancerdrvinay.com/curative-vs-palliative-surgery.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3301,7 +3323,7 @@
           <t>https://cioncancerdrvinay.com/breast-reconstruction-after-mastectomy.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3328,7 +3350,7 @@
           <t>https://cioncancerdrvinay.com/port-insertion-surgery.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3355,7 +3377,7 @@
           <t>https://cioncancerdrvinay.com/vats-thoracoscopy.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3382,7 +3404,7 @@
           <t>https://cioncancerdrvinay.com/esophagectomy-surgery.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3409,7 +3431,7 @@
           <t>https://cioncancerdrvinay.com/gastrectomy-types.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3436,7 +3458,7 @@
           <t>https://cioncancerdrvinay.com/pancreatectomy-procedure.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3463,7 +3485,7 @@
           <t>https://cioncancerdrvinay.com/whipple-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3490,7 +3512,7 @@
           <t>https://cioncancerdrvinay.com/hernia-after-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3517,7 +3539,7 @@
           <t>https://cioncancerdrvinay.com/scar-management-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3544,7 +3566,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-elderly.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3571,7 +3593,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-cost-hyderabad.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3598,7 +3620,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-questions.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3625,7 +3647,7 @@
           <t>https://cioncancerdrvinay.com/life-after-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3652,7 +3674,7 @@
           <t>https://cioncancerdrvinay.com/robotic-cancer-surgery-india.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3679,7 +3701,7 @@
           <t>https://cioncancerdrvinay.com/abdominal-cancer-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3706,7 +3728,7 @@
           <t>https://cioncancerdrvinay.com/rectal-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3733,7 +3755,7 @@
           <t>https://cioncancerdrvinay.com/parathyroid-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3760,7 +3782,7 @@
           <t>https://cioncancerdrvinay.com/adrenalectomy-procedure.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3787,7 +3809,7 @@
           <t>https://cioncancerdrvinay.com/pelvic-exenteration-surgery.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3814,7 +3836,7 @@
           <t>https://cioncancerdrvinay.com/lymph-node-removal-surgery.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3841,7 +3863,7 @@
           <t>https://cioncancerdrvinay.com/cancer-biopsy-types.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3868,7 +3890,7 @@
           <t>https://cioncancerdrvinay.com/intraoperative-frozen-section.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3895,7 +3917,7 @@
           <t>https://cioncancerdrvinay.com/cancer-resection-margins.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3922,7 +3944,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-second-opinion.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3949,7 +3971,7 @@
           <t>https://cioncancerdrvinay.com/day-surgery-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3976,7 +3998,7 @@
           <t>https://cioncancerdrvinay.com/reconstructive-flap-surgery.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4003,7 +4025,7 @@
           <t>https://cioncancerdrvinay.com/questions-for-cancer-surgeon.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4680,29 +4702,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Melanoma surgery and margins</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>melanoma-surgery</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrmurali.com/melanoma-surgery.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4749,7 @@
           <t>https://cioncancerdrmurali.com/skin-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4754,7 +4776,7 @@
           <t>https://cioncancerdrmurali.com/retroperitoneal-sarcoma-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4781,7 +4803,7 @@
           <t>https://cioncancerdrmurali.com/leiomyosarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4808,7 +4830,7 @@
           <t>https://cioncancerdrmurali.com/liposarcoma-surgery.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4835,7 +4857,7 @@
           <t>https://cioncancerdrmurali.com/limb-sparing-surgery.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4862,7 +4884,7 @@
           <t>https://cioncancerdrmurali.com/osteosarcoma-limb-salvage.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4889,7 +4911,7 @@
           <t>https://cioncancerdrmurali.com/rectal-sphincter-preservation.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4916,7 +4938,7 @@
           <t>https://cioncancerdrmurali.com/low-anterior-resection.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4943,7 +4965,7 @@
           <t>https://cioncancerdrmurali.com/sigmoid-colon-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4970,7 +4992,7 @@
           <t>https://cioncancerdrmurali.com/laparoscopic-bowel-resection.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4997,7 +5019,7 @@
           <t>https://cioncancerdrmurali.com/hemorrhoids-vs-rectal-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5024,7 +5046,7 @@
           <t>https://cioncancerdrmurali.com/liver-metastases-surgery.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5051,7 +5073,7 @@
           <t>https://cioncancerdrmurali.com/thermal-ablation-liver-tumours.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5078,7 +5100,7 @@
           <t>https://cioncancerdrmurali.com/bile-duct-repair-surgery.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5105,7 +5127,7 @@
           <t>https://cioncancerdrmurali.com/cholecystectomy-gallbladder-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5132,7 +5154,7 @@
           <t>https://cioncancerdrmurali.com/total-gastrectomy-recovery.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5159,7 +5181,7 @@
           <t>https://cioncancerdrmurali.com/small-bowel-resection.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5186,7 +5208,7 @@
           <t>https://cioncancerdrmurali.com/peritoneal-wash-cytology.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5213,7 +5235,7 @@
           <t>https://cioncancerdrmurali.com/second-look-surgery-ovarian.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5240,7 +5262,7 @@
           <t>https://cioncancerdrmurali.com/interval-debulking-surgery.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5267,7 +5289,7 @@
           <t>https://cioncancerdrmurali.com/cancer-surgery-diabetes.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5294,7 +5316,7 @@
           <t>https://cioncancerdrmurali.com/anastomosis-leak-prevention.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5321,7 +5343,7 @@
           <t>https://cioncancerdrmurali.com/ewing-sarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5348,7 +5370,7 @@
           <t>https://cioncancerdrmurali.com/synovial-sarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5375,7 +5397,7 @@
           <t>https://cioncancerdrmurali.com/amputation-bone-cancer.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5402,7 +5424,7 @@
           <t>https://cioncancerdrmurali.com/right-hemicolectomy.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5429,7 +5451,7 @@
           <t>https://cioncancerdrmurali.com/left-hemicolectomy.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5456,7 +5478,7 @@
           <t>https://cioncancerdrmurali.com/d2-lymphadenectomy-gastric.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5483,7 +5505,7 @@
           <t>https://cioncancerdrmurali.com/portal-vein-embolization.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5510,7 +5532,7 @@
           <t>https://cioncancerdrmurali.com/distal-pancreatectomy.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5537,7 +5559,7 @@
           <t>https://cioncancerdrmurali.com/radical-cholecystectomy-gallbladder.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5564,7 +5586,7 @@
           <t>https://cioncancerdrmurali.com/gist-tumour-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5591,7 +5613,7 @@
           <t>https://cioncancerdrmurali.com/mesenteric-tumour-resection.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5618,7 +5640,7 @@
           <t>https://cioncancerdrmurali.com/colon-cancer-peritoneal-spread.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5645,7 +5667,7 @@
           <t>https://cioncancerdrmurali.com/uterine-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5672,7 +5694,7 @@
           <t>https://cioncancerdrmurali.com/malignant-ascites-management.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5699,7 +5721,7 @@
           <t>https://cioncancerdrmurali.com/laparoscopic-staging-peritoneal.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5726,7 +5748,7 @@
           <t>https://cioncancerdrmurali.com/transverse-colon-cancer.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5753,7 +5775,7 @@
           <t>https://cioncancerdrmurali.com/anorectal-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5780,7 +5802,7 @@
           <t>https://cioncancerdrmurali.com/diverticulitis-vs-colon-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5807,7 +5829,7 @@
           <t>https://cioncancerdrmurali.com/phantom-limb-pain-management.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5834,7 +5856,7 @@
           <t>https://cioncancerdrmurali.com/intraoperative-bleeding-management.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5861,7 +5883,7 @@
           <t>https://cioncancerdrmurali.com/microwave-ablation-liver.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5888,7 +5910,7 @@
           <t>https://cioncancerdrmurali.com/proximal-gastrectomy.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5915,7 +5937,7 @@
           <t>https://cioncancerdrmurali.com/pancreatic-resection-recovery.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5942,7 +5964,7 @@
           <t>https://cioncancerdrmurali.com/abdominoperineal-resection.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5969,7 +5991,7 @@
           <t>https://cioncancerdrmurali.com/stoma-reversal-surgery.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5996,7 +6018,7 @@
           <t>https://cioncancerdrmurali.com/eras-protocol-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6023,7 +6045,7 @@
           <t>https://cioncancerdrmurali.com/cancer-surgery-blood-loss.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6728,29 +6750,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Oral cancer surgery treatment</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>oral-cancer-surgery</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrsandeep.com/oral-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6797,7 @@
           <t>https://cioncancerdrsandeep.com/tongue-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6802,7 +6824,7 @@
           <t>https://cioncancerdrsandeep.com/lip-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6829,7 +6851,7 @@
           <t>https://cioncancerdrsandeep.com/buccal-mucosa-cancer.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6856,7 +6878,7 @@
           <t>https://cioncancerdrsandeep.com/floor-of-mouth-cancer.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6883,7 +6905,7 @@
           <t>https://cioncancerdrsandeep.com/laryngeal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6910,7 +6932,7 @@
           <t>https://cioncancerdrsandeep.com/laryngectomy-voice-rehab.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6937,7 +6959,7 @@
           <t>https://cioncancerdrsandeep.com/hypopharyngeal-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6964,7 +6986,7 @@
           <t>https://cioncancerdrsandeep.com/oropharyngeal-cancer-hpv.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6991,7 +7013,7 @@
           <t>https://cioncancerdrsandeep.com/tonsil-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7018,7 +7040,7 @@
           <t>https://cioncancerdrsandeep.com/nasopharyngeal-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7045,7 +7067,7 @@
           <t>https://cioncancerdrsandeep.com/nasal-cavity-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7072,7 +7094,7 @@
           <t>https://cioncancerdrsandeep.com/salivary-gland-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7099,7 +7121,7 @@
           <t>https://cioncancerdrsandeep.com/parotid-gland-surgery.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7126,7 +7148,7 @@
           <t>https://cioncancerdrsandeep.com/neck-dissection-types.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7153,7 +7175,7 @@
           <t>https://cioncancerdrsandeep.com/modified-radical-neck-dissection.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7180,7 +7202,7 @@
           <t>https://cioncancerdrsandeep.com/total-thyroidectomy.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7207,7 +7229,7 @@
           <t>https://cioncancerdrsandeep.com/papillary-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7234,7 +7256,7 @@
           <t>https://cioncancerdrsandeep.com/follicular-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7261,7 +7283,7 @@
           <t>https://cioncancerdrsandeep.com/medullary-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7288,7 +7310,7 @@
           <t>https://cioncancerdrsandeep.com/thyroid-cancer-recurrence.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7315,7 +7337,7 @@
           <t>https://cioncancerdrsandeep.com/skull-base-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7342,7 +7364,7 @@
           <t>https://cioncancerdrsandeep.com/paraganglioma-treatment.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7369,7 +7391,7 @@
           <t>https://cioncancerdrsandeep.com/adenoid-cystic-carcinoma.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7396,7 +7418,7 @@
           <t>https://cioncancerdrsandeep.com/mucoepidermoid-carcinoma.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7423,7 +7445,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-trismus.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7450,7 +7472,7 @@
           <t>https://cioncancerdrsandeep.com/xerostomia-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7477,7 +7499,7 @@
           <t>https://cioncancerdrsandeep.com/dysphagia-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7504,7 +7526,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-rehabilitation.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7531,7 +7553,7 @@
           <t>https://cioncancerdrsandeep.com/speech-therapy-laryngectomy.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7558,7 +7580,7 @@
           <t>https://cioncancerdrsandeep.com/neck-lump-causes.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7585,7 +7607,7 @@
           <t>https://cioncancerdrsandeep.com/hoarseness-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7612,7 +7634,7 @@
           <t>https://cioncancerdrsandeep.com/mouth-ulcer-cancer-warning.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7639,7 +7661,7 @@
           <t>https://cioncancerdrsandeep.com/leukoplakia-oral-cancer.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7666,7 +7688,7 @@
           <t>https://cioncancerdrsandeep.com/submucous-fibrosis-cancer.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7693,7 +7715,7 @@
           <t>https://cioncancerdrsandeep.com/tobacco-oral-cancer.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7720,7 +7742,7 @@
           <t>https://cioncancerdrsandeep.com/base-of-tongue-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7747,7 +7769,7 @@
           <t>https://cioncancerdrsandeep.com/partial-laryngectomy.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7774,7 +7796,7 @@
           <t>https://cioncancerdrsandeep.com/palate-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7801,7 +7823,7 @@
           <t>https://cioncancerdrsandeep.com/jaw-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7828,7 +7850,7 @@
           <t>https://cioncancerdrsandeep.com/paranasal-sinus-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7855,7 +7877,7 @@
           <t>https://cioncancerdrsandeep.com/anaplastic-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7882,7 +7904,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-hyderabad.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7909,7 +7931,7 @@
           <t>https://cioncancerdrsandeep.com/swallowing-therapy-cancer.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7936,7 +7958,7 @@
           <t>https://cioncancerdrsandeep.com/radiation-head-neck-surgery.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7963,7 +7985,7 @@
           <t>https://cioncancerdrsandeep.com/chemotherapy-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7990,7 +8012,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-nutrition.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8017,7 +8039,7 @@
           <t>https://cioncancerdrsandeep.com/tracheostomy-care-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8044,7 +8066,7 @@
           <t>https://cioncancerdrsandeep.com/reconstruction-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8071,7 +8093,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-surgeon-questions.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8776,29 +8798,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Understanding cancer immunotherapy</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>understanding-immunotherapy</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrkiranmayee.com/understanding-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8845,7 @@
           <t>https://cioncancerdrkiranmayee.com/lung-cancer-types-stages.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8850,7 +8872,7 @@
           <t>https://cioncancerdrkiranmayee.com/hormone-receptor-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8877,7 +8899,7 @@
           <t>https://cioncancerdrkiranmayee.com/non-hodgkin-lymphoma.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8904,7 +8926,7 @@
           <t>https://cioncancerdrkiranmayee.com/chronic-myeloid-leukemia.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8931,7 +8953,7 @@
           <t>https://cioncancerdrkiranmayee.com/melanoma-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8958,7 +8980,7 @@
           <t>https://cioncancerdrkiranmayee.com/pancreatic-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8985,7 +9007,7 @@
           <t>https://cioncancerdrkiranmayee.com/liver-cancer-treatment-hyderabad.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9012,7 +9034,7 @@
           <t>https://cioncancerdrkiranmayee.com/uterine-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9039,7 +9061,7 @@
           <t>https://cioncancerdrkiranmayee.com/bone-cancer-types.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9066,7 +9088,7 @@
           <t>https://cioncancerdrkiranmayee.com/soft-tissue-sarcoma.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9093,7 +9115,7 @@
           <t>https://cioncancerdrkiranmayee.com/neuroendocrine-tumours.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9120,7 +9142,7 @@
           <t>https://cioncancerdrkiranmayee.com/bile-duct-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9147,7 +9169,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-blood-clots-dvt.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9174,7 +9196,7 @@
           <t>https://cioncancerdrkiranmayee.com/checkpoint-inhibitors-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9201,7 +9223,7 @@
           <t>https://cioncancerdrkiranmayee.com/car-t-cell-therapy.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9228,7 +9250,7 @@
           <t>https://cioncancerdrkiranmayee.com/parp-inhibitors-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9255,7 +9277,7 @@
           <t>https://cioncancerdrkiranmayee.com/cdk-inhibitors-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9282,7 +9304,7 @@
           <t>https://cioncancerdrkiranmayee.com/combination-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9309,7 +9331,7 @@
           <t>https://cioncancerdrkiranmayee.com/weight-management-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9336,7 +9358,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-mental-health.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9363,7 +9385,7 @@
           <t>https://cioncancerdrkiranmayee.com/exercise-during-cancer.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9390,7 +9412,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-pain-types.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9417,7 +9439,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-end-of-life-care.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9444,7 +9466,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-rehabilitation.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9471,7 +9493,7 @@
           <t>https://cioncancerdrkiranmayee.com/return-to-work-cancer.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9498,7 +9520,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-insurance-india.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9525,7 +9547,7 @@
           <t>https://cioncancerdrkiranmayee.com/government-cancer-schemes-india.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9552,7 +9574,7 @@
           <t>https://cioncancerdrkiranmayee.com/telemedicine-cancer-followup.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9579,7 +9601,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-young-adults.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9606,7 +9628,7 @@
           <t>https://cioncancerdrkiranmayee.com/antibody-drug-conjugates.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9633,7 +9655,7 @@
           <t>https://cioncancerdrkiranmayee.com/maintenance-therapy-cancer.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9660,7 +9682,7 @@
           <t>https://cioncancerdrkiranmayee.com/adjuvant-neoadjuvant-therapy.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9687,7 +9709,7 @@
           <t>https://cioncancerdrkiranmayee.com/dose-dense-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9714,7 +9736,7 @@
           <t>https://cioncancerdrkiranmayee.com/growth-factors-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9741,7 +9763,7 @@
           <t>https://cioncancerdrkiranmayee.com/febrile-neutropenia.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9768,7 +9790,7 @@
           <t>https://cioncancerdrkiranmayee.com/cardio-oncology-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9795,7 +9817,7 @@
           <t>https://cioncancerdrkiranmayee.com/second-primary-cancer.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9822,7 +9844,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-treatment-at-home.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9849,7 +9871,7 @@
           <t>https://cioncancerdrkiranmayee.com/oral-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9876,7 +9898,7 @@
           <t>https://cioncancerdrkiranmayee.com/colon-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9903,7 +9925,7 @@
           <t>https://cioncancerdrkiranmayee.com/pancreatic-cancer-warning-signs.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9930,7 +9952,7 @@
           <t>https://cioncancerdrkiranmayee.com/vulvar-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9957,7 +9979,7 @@
           <t>https://cioncancerdrkiranmayee.com/penile-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9984,7 +10006,7 @@
           <t>https://cioncancerdrkiranmayee.com/anal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10011,7 +10033,7 @@
           <t>https://cioncancerdrkiranmayee.com/adrenal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10038,7 +10060,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-genetic-counselling.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10065,7 +10087,7 @@
           <t>https://cioncancerdrkiranmayee.com/complementary-medicine-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10092,7 +10114,7 @@
           <t>https://cioncancerdrkiranmayee.com/hospice-care-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10119,7 +10141,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-caregiver-burnout.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10824,29 +10846,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Bone marrow transplant explained</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>bone-marrow-transplant-explained</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrbasudev.com/bone-marrow-transplant-explained.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10893,7 @@
           <t>https://cioncancerdrbasudev.com/autologous-bmt.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10898,7 +10920,7 @@
           <t>https://cioncancerdrbasudev.com/allogeneic-bmt.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10925,7 +10947,7 @@
           <t>https://cioncancerdrbasudev.com/stem-cell-donation.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10952,7 +10974,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-donor-compatibility.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10979,7 +11001,7 @@
           <t>https://cioncancerdrbasudev.com/bmt-recovery-timeline.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11006,7 +11028,7 @@
           <t>https://cioncancerdrbasudev.com/graft-versus-host-disease.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11033,7 +11055,7 @@
           <t>https://cioncancerdrbasudev.com/chronic-gvhd-management.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11060,7 +11082,7 @@
           <t>https://cioncancerdrbasudev.com/what-is-leukemia.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11087,7 +11109,7 @@
           <t>https://cioncancerdrbasudev.com/acute-myeloid-leukemia.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11114,7 +11136,7 @@
           <t>https://cioncancerdrbasudev.com/acute-lymphoblastic-leukemia.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11141,7 +11163,7 @@
           <t>https://cioncancerdrbasudev.com/chronic-lymphocytic-leukemia.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11168,7 +11190,7 @@
           <t>https://cioncancerdrbasudev.com/hairy-cell-leukemia.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11195,7 +11217,7 @@
           <t>https://cioncancerdrbasudev.com/myelodysplastic-syndrome.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11222,7 +11244,7 @@
           <t>https://cioncancerdrbasudev.com/myelofibrosis-treatment.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11249,7 +11271,7 @@
           <t>https://cioncancerdrbasudev.com/polycythemia-vera.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11276,7 +11298,7 @@
           <t>https://cioncancerdrbasudev.com/essential-thrombocythemia.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11303,7 +11325,7 @@
           <t>https://cioncancerdrbasudev.com/aplastic-anemia-treatment.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11330,7 +11352,7 @@
           <t>https://cioncancerdrbasudev.com/thalassemia-stem-cell-therapy.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11357,7 +11379,7 @@
           <t>https://cioncancerdrbasudev.com/hodgkin-lymphoma-treatment.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11384,7 +11406,7 @@
           <t>https://cioncancerdrbasudev.com/diffuse-large-b-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11411,7 +11433,7 @@
           <t>https://cioncancerdrbasudev.com/follicular-lymphoma.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11438,7 +11460,7 @@
           <t>https://cioncancerdrbasudev.com/mantle-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11465,7 +11487,7 @@
           <t>https://cioncancerdrbasudev.com/burkitt-lymphoma.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11492,7 +11514,7 @@
           <t>https://cioncancerdrbasudev.com/t-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11519,7 +11541,7 @@
           <t>https://cioncancerdrbasudev.com/waldenstrom-macroglobulinemia.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11546,7 +11568,7 @@
           <t>https://cioncancerdrbasudev.com/multiple-myeloma-bone-pain.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11573,7 +11595,7 @@
           <t>https://cioncancerdrbasudev.com/smoldering-myeloma.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11600,7 +11622,7 @@
           <t>https://cioncancerdrbasudev.com/bortezomib-myeloma.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11627,7 +11649,7 @@
           <t>https://cioncancerdrbasudev.com/daratumumab-myeloma.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11654,7 +11676,7 @@
           <t>https://cioncancerdrbasudev.com/venetoclax-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11681,7 +11703,7 @@
           <t>https://cioncancerdrbasudev.com/ibrutinib-cll.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11708,7 +11730,7 @@
           <t>https://cioncancerdrbasudev.com/rituximab-lymphoma.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11735,7 +11757,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-biopsy-procedure.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11762,7 +11784,7 @@
           <t>https://cioncancerdrbasudev.com/cbc-cancer-interpretation.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11789,7 +11811,7 @@
           <t>https://cioncancerdrbasudev.com/flow-cytometry-cancer.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11816,7 +11838,7 @@
           <t>https://cioncancerdrbasudev.com/fish-testing-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11843,7 +11865,7 @@
           <t>https://cioncancerdrbasudev.com/blood-cancer-treatment-hyderabad.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11870,7 +11892,7 @@
           <t>https://cioncancerdrbasudev.com/bmt-cost-india.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11897,7 +11919,7 @@
           <t>https://cioncancerdrbasudev.com/life-after-bmt.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11924,7 +11946,7 @@
           <t>https://cioncancerdrbasudev.com/infections-after-bmt.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11951,7 +11973,7 @@
           <t>https://cioncancerdrbasudev.com/engraftment-syndrome.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11978,7 +12000,7 @@
           <t>https://cioncancerdrbasudev.com/peripheral-blood-stem-cell-harvest.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12005,7 +12027,7 @@
           <t>https://cioncancerdrbasudev.com/cord-blood-transplant.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12032,7 +12054,7 @@
           <t>https://cioncancerdrbasudev.com/haploidentical-transplant.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12059,7 +12081,7 @@
           <t>https://cioncancerdrbasudev.com/reduced-intensity-conditioning-bmt.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12086,7 +12108,7 @@
           <t>https://cioncancerdrbasudev.com/nk-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12113,7 +12135,7 @@
           <t>https://cioncancerdrbasudev.com/amyloidosis-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12140,7 +12162,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-failure-syndromes.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12167,7 +12189,7 @@
           <t>https://cioncancerdrbasudev.com/blood-cancer-diet-nutrition.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12872,29 +12894,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>What is radiation therapy</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>what-is-radiation-therapy</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrraghvendra.com/what-is-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -12919,7 +12941,7 @@
           <t>https://cioncancerdrraghvendra.com/external-beam-radiation.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12946,7 +12968,7 @@
           <t>https://cioncancerdrraghvendra.com/imrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12973,7 +12995,7 @@
           <t>https://cioncancerdrraghvendra.com/igrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13000,7 +13022,7 @@
           <t>https://cioncancerdrraghvendra.com/stereotactic-radiosurgery.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13027,7 +13049,7 @@
           <t>https://cioncancerdrraghvendra.com/sbrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13054,7 +13076,7 @@
           <t>https://cioncancerdrraghvendra.com/brachytherapy-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13081,7 +13103,7 @@
           <t>https://cioncancerdrraghvendra.com/high-dose-rate-brachytherapy.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13108,7 +13130,7 @@
           <t>https://cioncancerdrraghvendra.com/breast-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13135,7 +13157,7 @@
           <t>https://cioncancerdrraghvendra.com/cervical-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13162,7 +13184,7 @@
           <t>https://cioncancerdrraghvendra.com/prostate-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13189,7 +13211,7 @@
           <t>https://cioncancerdrraghvendra.com/lung-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13216,7 +13238,7 @@
           <t>https://cioncancerdrraghvendra.com/head-neck-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13243,7 +13265,7 @@
           <t>https://cioncancerdrraghvendra.com/rectal-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13270,7 +13292,7 @@
           <t>https://cioncancerdrraghvendra.com/whole-brain-radiation.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13297,7 +13319,7 @@
           <t>https://cioncancerdrraghvendra.com/palliative-radiation-bone-pain.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13324,7 +13346,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-side-effects.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13351,7 +13373,7 @@
           <t>https://cioncancerdrraghvendra.com/skin-reactions-radiation.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13378,7 +13400,7 @@
           <t>https://cioncancerdrraghvendra.com/fatigue-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13405,7 +13427,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-mucositis.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13432,7 +13454,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-enteritis.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13459,7 +13481,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-cystitis.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13486,7 +13508,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-simulation.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13513,7 +13535,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-treatment-planning.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13540,7 +13562,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-fractions.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13567,7 +13589,7 @@
           <t>https://cioncancerdrraghvendra.com/hypofractionated-radiation.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13594,7 +13616,7 @@
           <t>https://cioncancerdrraghvendra.com/concurrent-chemoradiation.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13621,7 +13643,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-brain-metastases.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13648,7 +13670,7 @@
           <t>https://cioncancerdrraghvendra.com/spinal-cord-compression-radiation.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13675,7 +13697,7 @@
           <t>https://cioncancerdrraghvendra.com/sabr-liver-tumours.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13702,7 +13724,7 @@
           <t>https://cioncancerdrraghvendra.com/radioiodine-therapy-thyroid.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13729,7 +13751,7 @@
           <t>https://cioncancerdrraghvendra.com/prrt-neuroendocrine-tumours.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13756,7 +13778,7 @@
           <t>https://cioncancerdrraghvendra.com/lutetium-dotatate-therapy.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13783,7 +13805,7 @@
           <t>https://cioncancerdrraghvendra.com/y90-radioembolization.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13810,7 +13832,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-vs-surgery.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13837,7 +13859,7 @@
           <t>https://cioncancerdrraghvendra.com/proton-therapy-vs-radiation.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13864,7 +13886,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-quality-of-life.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13891,7 +13913,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-myths.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13918,7 +13940,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-cost-hyderabad.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13945,7 +13967,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-safety.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13972,7 +13994,7 @@
           <t>https://cioncancerdrraghvendra.com/re-irradiation-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13999,7 +14021,7 @@
           <t>https://cioncancerdrraghvendra.com/second-cancer-after-radiation.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14026,7 +14048,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-protection-family.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14053,7 +14075,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-fertility.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14080,7 +14102,7 @@
           <t>https://cioncancerdrraghvendra.com/accelerated-partial-breast-irradiation.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14107,7 +14129,7 @@
           <t>https://cioncancerdrraghvendra.com/intraoperative-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14134,7 +14156,7 @@
           <t>https://cioncancerdrraghvendra.com/total-body-irradiation.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14161,7 +14183,7 @@
           <t>https://cioncancerdrraghvendra.com/radiofrequency-ablation-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14188,7 +14210,7 @@
           <t>https://cioncancerdrraghvendra.com/tace-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14215,7 +14237,7 @@
           <t>https://cioncancerdrraghvendra.com/esophageal-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14920,29 +14942,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Colon cancer treatment options</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>colon-cancer-treatment</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrcraghavendra.info/colon-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14989,7 @@
           <t>https://cioncancerdrcraghavendra.info/rectal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14994,7 +15016,7 @@
           <t>https://cioncancerdrcraghavendra.info/appendix-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15021,7 +15043,7 @@
           <t>https://cioncancerdrcraghavendra.info/peritoneal-carcinomatosis.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15048,7 +15070,7 @@
           <t>https://cioncancerdrcraghavendra.info/cea-tumor-marker.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15075,7 +15097,7 @@
           <t>https://cioncancerdrcraghavendra.info/ca125-test-explained.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15102,7 +15124,7 @@
           <t>https://cioncancerdrcraghavendra.info/ca19-9-test-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15129,7 +15151,7 @@
           <t>https://cioncancerdrcraghavendra.info/afp-test-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15156,7 +15178,7 @@
           <t>https://cioncancerdrcraghavendra.info/psa-test-explained.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15183,7 +15205,7 @@
           <t>https://cioncancerdrcraghavendra.info/core-needle-biopsy.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15210,7 +15232,7 @@
           <t>https://cioncancerdrcraghavendra.info/liquid-biopsy-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15237,7 +15259,7 @@
           <t>https://cioncancerdrcraghavendra.info/next-generation-sequencing-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15264,7 +15286,7 @@
           <t>https://cioncancerdrcraghavendra.info/microsatellite-instability.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15291,7 +15313,7 @@
           <t>https://cioncancerdrcraghavendra.info/kras-mutation-colorectal.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15318,7 +15340,7 @@
           <t>https://cioncancerdrcraghavendra.info/egfr-mutation-lung-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15345,7 +15367,7 @@
           <t>https://cioncancerdrcraghavendra.info/braf-mutation-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15372,7 +15394,7 @@
           <t>https://cioncancerdrcraghavendra.info/pdl1-expression-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15399,7 +15421,7 @@
           <t>https://cioncancerdrcraghavendra.info/precision-oncology-hyderabad.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15426,7 +15448,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-diet-myths.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15453,7 +15475,7 @@
           <t>https://cioncancerdrcraghavendra.info/sugar-cancer-link.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15480,7 +15502,7 @@
           <t>https://cioncancerdrcraghavendra.info/alcohol-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15507,7 +15529,7 @@
           <t>https://cioncancerdrcraghavendra.info/obesity-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15534,7 +15556,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-prevention-strategies.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15561,7 +15583,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-early-detection-india.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15588,7 +15610,7 @@
           <t>https://cioncancerdrcraghavendra.info/colonoscopy-screening.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15615,7 +15637,7 @@
           <t>https://cioncancerdrcraghavendra.info/mammography-screening.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15642,7 +15664,7 @@
           <t>https://cioncancerdrcraghavendra.info/pap-smear-screening.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15669,7 +15691,7 @@
           <t>https://cioncancerdrcraghavendra.info/recist-criteria-cancer.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15696,7 +15718,7 @@
           <t>https://cioncancerdrcraghavendra.info/adjuvant-chemotherapy-explained.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15723,7 +15745,7 @@
           <t>https://cioncancerdrcraghavendra.info/bone-marrow-suppression.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15750,7 +15772,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-biomarkers-explained.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15777,7 +15799,7 @@
           <t>https://cioncancerdrcraghavendra.info/biliary-tract-cancer.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15804,7 +15826,7 @@
           <t>https://cioncancerdrcraghavendra.info/duodenal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15831,7 +15853,7 @@
           <t>https://cioncancerdrcraghavendra.info/small-intestine-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15858,7 +15880,7 @@
           <t>https://cioncancerdrcraghavendra.info/tumor-biopsy-types.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15885,7 +15907,7 @@
           <t>https://cioncancerdrcraghavendra.info/smoking-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15912,7 +15934,7 @@
           <t>https://cioncancerdrcraghavendra.info/red-meat-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15939,7 +15961,7 @@
           <t>https://cioncancerdrcraghavendra.info/stress-cancer-link.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15966,7 +15988,7 @@
           <t>https://cioncancerdrcraghavendra.info/turmeric-cancer-research.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15993,7 +16015,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-treatment-cost-india.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16020,7 +16042,7 @@
           <t>https://cioncancerdrcraghavendra.info/ayushman-bharat-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16047,7 +16069,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-screening-age-guidelines.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16074,7 +16096,7 @@
           <t>https://cioncancerdrcraghavendra.info/tumor-mutational-burden.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16101,7 +16123,7 @@
           <t>https://cioncancerdrcraghavendra.info/msi-high-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16128,7 +16150,7 @@
           <t>https://cioncancerdrcraghavendra.info/colorectal-cancer-followup.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16155,7 +16177,7 @@
           <t>https://cioncancerdrcraghavendra.info/kras-wildtype-colorectal.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16182,7 +16204,7 @@
           <t>https://cioncancerdrcraghavendra.info/stoma-care-colorectal.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16209,7 +16231,7 @@
           <t>https://cioncancerdrcraghavendra.info/rectal-bleeding-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16236,7 +16258,7 @@
           <t>https://cioncancerdrcraghavendra.info/bowel-habits-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16263,7 +16285,7 @@
           <t>https://cioncancerdrcraghavendra.info/iron-deficiency-anaemia-cancer.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16996,29 +17018,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>What is HIPEC surgery</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>what-is-hipec</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://cioncancerdrimad.com/what-is-hipec.html</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Today →</t>
         </is>
       </c>
     </row>
@@ -17043,7 +17065,7 @@
           <t>https://cioncancerdrimad.com/hipec-ovarian-cancer.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17070,7 +17092,7 @@
           <t>https://cioncancerdrimad.com/hipec-colorectal-cancer.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17097,7 +17119,7 @@
           <t>https://cioncancerdrimad.com/hipec-gastric-cancer.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17124,7 +17146,7 @@
           <t>https://cioncancerdrimad.com/pipac-procedure-explained.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17151,7 +17173,7 @@
           <t>https://cioncancerdrimad.com/pipac-vs-hipec.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17178,7 +17200,7 @@
           <t>https://cioncancerdrimad.com/cytoreductive-surgery-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17205,7 +17227,7 @@
           <t>https://cioncancerdrimad.com/pci-score-peritoneal-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17232,7 +17254,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-metastases-treatment.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17259,7 +17281,7 @@
           <t>https://cioncancerdrimad.com/pseudomyxoma-peritonei.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17286,7 +17308,7 @@
           <t>https://cioncancerdrimad.com/appendix-cancer-mucinous.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17313,7 +17335,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-mesothelioma.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17340,7 +17362,7 @@
           <t>https://cioncancerdrimad.com/primary-peritoneal-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17367,7 +17389,7 @@
           <t>https://cioncancerdrimad.com/gastric-cancer-surgery-options.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17394,7 +17416,7 @@
           <t>https://cioncancerdrimad.com/total-gastrectomy-stomach-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17421,7 +17443,7 @@
           <t>https://cioncancerdrimad.com/d2-dissection-gastric-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17448,7 +17470,7 @@
           <t>https://cioncancerdrimad.com/esophagogastric-junction-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17475,7 +17497,7 @@
           <t>https://cioncancerdrimad.com/whipple-procedure-guide.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17502,7 +17524,7 @@
           <t>https://cioncancerdrimad.com/whipple-recovery-diet.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17529,7 +17551,7 @@
           <t>https://cioncancerdrimad.com/pylorus-preserving-whipple.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17556,7 +17578,7 @@
           <t>https://cioncancerdrimad.com/distal-pancreatectomy-splenectomy.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17583,7 +17605,7 @@
           <t>https://cioncancerdrimad.com/borderline-resectable-pancreatic.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17610,7 +17632,7 @@
           <t>https://cioncancerdrimad.com/hepatobiliary-cancer-hyderabad.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17637,7 +17659,7 @@
           <t>https://cioncancerdrimad.com/right-hepatectomy-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17664,7 +17686,7 @@
           <t>https://cioncancerdrimad.com/klatskin-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17691,7 +17713,7 @@
           <t>https://cioncancerdrimad.com/gallbladder-cancer-surgery-options.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17718,7 +17740,7 @@
           <t>https://cioncancerdrimad.com/radical-cholecystectomy.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17745,7 +17767,7 @@
           <t>https://cioncancerdrimad.com/gist-treatment-imatinib.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17772,7 +17794,7 @@
           <t>https://cioncancerdrimad.com/retroperitoneal-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17799,7 +17821,7 @@
           <t>https://cioncancerdrimad.com/colorectal-liver-metastases-crs.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17826,7 +17848,7 @@
           <t>https://cioncancerdrimad.com/ovarian-cancer-hipec.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17853,7 +17875,7 @@
           <t>https://cioncancerdrimad.com/brca-ovarian-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17880,7 +17902,7 @@
           <t>https://cioncancerdrimad.com/malignant-ascites-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17907,7 +17929,7 @@
           <t>https://cioncancerdrimad.com/laparoscopic-staging.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17934,7 +17956,7 @@
           <t>https://cioncancerdrimad.com/second-opinion-hipec.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17961,7 +17983,7 @@
           <t>https://cioncancerdrimad.com/hipec-cost-india.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17988,7 +18010,7 @@
           <t>https://cioncancerdrimad.com/life-after-hipec.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18015,7 +18037,7 @@
           <t>https://cioncancerdrimad.com/recovery-cytoreductive-surgery.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18042,7 +18064,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-cancer-surgery-possible.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18069,7 +18091,7 @@
           <t>https://cioncancerdrimad.com/hipec-contraindications.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18096,7 +18118,7 @@
           <t>https://cioncancerdrimad.com/intraperitoneal-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18123,7 +18145,7 @@
           <t>https://cioncancerdrimad.com/gastric-cancer-peritoneal-spread.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18150,7 +18172,7 @@
           <t>https://cioncancerdrimad.com/appendix-rupture-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18177,7 +18199,7 @@
           <t>https://cioncancerdrimad.com/liver-cancer-resection.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18204,7 +18226,7 @@
           <t>https://cioncancerdrimad.com/portal-vein-pancreatic-cancer.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18231,7 +18253,7 @@
           <t>https://cioncancerdrimad.com/gi-cancer-second-opinion-hyderabad.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18258,7 +18280,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-cancer-survival.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18285,7 +18307,7 @@
           <t>https://cioncancerdrimad.com/laparoscopic-vs-open-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18312,7 +18334,7 @@
           <t>https://cioncancerdrimad.com/crs-hipec-vs-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18339,7 +18361,7 @@
           <t>https://cioncancerdrimad.com/cancers-that-spread-to-peritoneum.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>

--- a/trackers/all-sites.xlsx
+++ b/trackers/all-sites.xlsx
@@ -151,10 +151,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -635,22 +635,22 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Nausea and vomiting after chemotherapy</t>
+          <t>(pre-existing page)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>what-is-a-chemo-port</t>
+          <t>what-is-a-pet-ct-scan</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/what-is-a-chemo-port.html</t>
+          <t>https://cioncancerdrowais.com/what-is-a-pet-ct-scan.html</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -662,52 +662,52 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Hair loss during cancer treatment</t>
+          <t>Nausea and vomiting after chemotherapy</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>hair-loss-cancer-treatment</t>
+          <t>what-is-a-chemo-port</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/hair-loss-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+          <t>https://cioncancerdrowais.com/what-is-a-chemo-port.html</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cancer-related fatigue management</t>
+          <t>Hair loss during cancer treatment</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>cancer-fatigue-management</t>
+          <t>hair-loss-cancer-treatment</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-fatigue-management.html</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/hair-loss-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -716,25 +716,25 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Nutrition and diet during cancer treatment</t>
+          <t>Cancer-related fatigue management</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>cancer-nutrition-diet</t>
+          <t>cancer-fatigue-management</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-nutrition-diet.html</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-fatigue-management.html</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -743,25 +743,25 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Breast cancer treatment options</t>
+          <t>Nutrition and diet during cancer treatment</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>breast-cancer-treatment</t>
+          <t>cancer-nutrition-diet</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/breast-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-nutrition-diet.html</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -770,25 +770,25 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Cervical cancer symptoms and treatment</t>
+          <t>Breast cancer treatment options</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>cervical-cancer-treatment</t>
+          <t>breast-cancer-treatment</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cervical-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/breast-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -797,25 +797,25 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ovarian cancer signs and diagnosis</t>
+          <t>Cervical cancer symptoms and treatment</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>ovarian-cancer-diagnosis</t>
+          <t>cervical-cancer-treatment</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/ovarian-cancer-diagnosis.html</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cervical-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -824,25 +824,25 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Colorectal cancer screening</t>
+          <t>Ovarian cancer signs and diagnosis</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>colorectal-cancer-screening</t>
+          <t>ovarian-cancer-diagnosis</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/colorectal-cancer-screening.html</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/ovarian-cancer-diagnosis.html</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -851,25 +851,25 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>What is lymphoma</t>
+          <t>Colorectal cancer screening</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>what-is-lymphoma</t>
+          <t>colorectal-cancer-screening</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/what-is-lymphoma.html</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/colorectal-cancer-screening.html</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -878,25 +878,25 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Types of leukemia</t>
+          <t>What is lymphoma</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>types-of-leukemia</t>
+          <t>what-is-lymphoma</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/types-of-leukemia.html</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/what-is-lymphoma.html</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -905,25 +905,25 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Multiple myeloma treatment</t>
+          <t>Types of leukemia</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>multiple-myeloma-treatment</t>
+          <t>types-of-leukemia</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/multiple-myeloma-treatment.html</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/types-of-leukemia.html</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -932,25 +932,25 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Blood tests used in cancer diagnosis</t>
+          <t>Multiple myeloma treatment</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>blood-tests-cancer-diagnosis</t>
+          <t>multiple-myeloma-treatment</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/blood-tests-cancer-diagnosis.html</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/multiple-myeloma-treatment.html</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -959,25 +959,25 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PET-CT scan explained for patients</t>
+          <t>Blood tests used in cancer diagnosis</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>pet-ct-scan-explained</t>
+          <t>blood-tests-cancer-diagnosis</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/pet-ct-scan-explained.html</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/blood-tests-cancer-diagnosis.html</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -986,25 +986,25 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Palliative care in cancer</t>
+          <t>PET-CT scan explained for patients</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>palliative-care-cancer</t>
+          <t>pet-ct-scan-explained</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/palliative-care-cancer.html</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/pet-ct-scan-explained.html</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1013,25 +1013,25 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Genetic testing for cancer risk</t>
+          <t>Palliative care in cancer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>genetic-testing-cancer-risk</t>
+          <t>palliative-care-cancer</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/genetic-testing-cancer-risk.html</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/palliative-care-cancer.html</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1040,25 +1040,25 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Hereditary cancer syndromes</t>
+          <t>Genetic testing for cancer risk</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>hereditary-cancer-syndromes</t>
+          <t>genetic-testing-cancer-risk</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/hereditary-cancer-syndromes.html</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/genetic-testing-cancer-risk.html</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1067,25 +1067,25 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Managing cancer recurrence</t>
+          <t>Hereditary cancer syndromes</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>managing-cancer-recurrence</t>
+          <t>hereditary-cancer-syndromes</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/managing-cancer-recurrence.html</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/hereditary-cancer-syndromes.html</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1094,25 +1094,25 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Immunotherapy side effects</t>
+          <t>Managing cancer recurrence</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>immunotherapy-side-effects</t>
+          <t>managing-cancer-recurrence</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/immunotherapy-side-effects.html</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/managing-cancer-recurrence.html</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1121,25 +1121,25 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Targeted therapy explained</t>
+          <t>Immunotherapy side effects</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>targeted-therapy-explained</t>
+          <t>immunotherapy-side-effects</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/targeted-therapy-explained.html</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/immunotherapy-side-effects.html</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1148,25 +1148,25 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Oral chemotherapy medications</t>
+          <t>Targeted therapy explained</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>oral-chemotherapy-medications</t>
+          <t>targeted-therapy-explained</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/oral-chemotherapy-medications.html</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/targeted-therapy-explained.html</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1175,25 +1175,25 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chemotherapy port explained</t>
+          <t>Oral chemotherapy medications</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>chemotherapy-port-explained</t>
+          <t>oral-chemotherapy-medications</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy-port-explained.html</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/oral-chemotherapy-medications.html</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1202,25 +1202,25 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Cancer clinical trials in India</t>
+          <t>Chemotherapy port explained</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>cancer-clinical-trials-india</t>
+          <t>chemotherapy-port-explained</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-clinical-trials-india.html</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/chemotherapy-port-explained.html</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1229,25 +1229,25 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Questions to ask your oncologist</t>
+          <t>Cancer clinical trials in India</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>questions-to-ask-oncologist</t>
+          <t>cancer-clinical-trials-india</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/questions-to-ask-oncologist.html</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-clinical-trials-india.html</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1256,25 +1256,25 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Cancer survivorship care</t>
+          <t>Questions to ask your oncologist</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>cancer-survivorship-care</t>
+          <t>questions-to-ask-oncologist</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-survivorship-care.html</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/questions-to-ask-oncologist.html</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1283,25 +1283,25 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Fertility preservation before chemotherapy</t>
+          <t>Cancer survivorship care</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>fertility-preservation-chemotherapy</t>
+          <t>cancer-survivorship-care</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/fertility-preservation-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-survivorship-care.html</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1310,25 +1310,25 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Mouth sores during chemotherapy</t>
+          <t>Fertility preservation before chemotherapy</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>mouth-sores-chemotherapy</t>
+          <t>fertility-preservation-chemotherapy</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/mouth-sores-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/fertility-preservation-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1337,25 +1337,25 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Neuropathy from chemotherapy</t>
+          <t>Mouth sores during chemotherapy</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>chemotherapy-neuropathy</t>
+          <t>mouth-sores-chemotherapy</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy-neuropathy.html</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/mouth-sores-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1364,25 +1364,25 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Cancer and diabetes management</t>
+          <t>Neuropathy from chemotherapy</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>cancer-diabetes-management</t>
+          <t>chemotherapy-neuropathy</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-diabetes-management.html</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/chemotherapy-neuropathy.html</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1391,25 +1391,25 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Blood transfusion in cancer treatment</t>
+          <t>Cancer and diabetes management</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>blood-transfusion-cancer</t>
+          <t>cancer-diabetes-management</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/blood-transfusion-cancer.html</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-diabetes-management.html</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1418,25 +1418,25 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Anti-nausea medications for chemotherapy</t>
+          <t>Blood transfusion in cancer treatment</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>anti-nausea-medications-chemotherapy</t>
+          <t>blood-transfusion-cancer</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/anti-nausea-medications-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/blood-transfusion-cancer.html</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1445,25 +1445,25 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Cancer diagnosis process step by step</t>
+          <t>Anti-nausea medications for chemotherapy</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>cancer-diagnosis-process</t>
+          <t>anti-nausea-medications-chemotherapy</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-diagnosis-process.html</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/anti-nausea-medications-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1472,25 +1472,25 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Reading your pathology report</t>
+          <t>Cancer diagnosis process step by step</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>reading-pathology-report</t>
+          <t>cancer-diagnosis-process</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/reading-pathology-report.html</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-diagnosis-process.html</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1499,25 +1499,25 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Cancer prognosis what it means</t>
+          <t>Reading your pathology report</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>cancer-prognosis-explained</t>
+          <t>reading-pathology-report</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-prognosis-explained.html</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/reading-pathology-report.html</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1526,25 +1526,25 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Anaemia during cancer treatment</t>
+          <t>Cancer prognosis what it means</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>cancer-related-anaemia</t>
+          <t>cancer-prognosis-explained</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-related-anaemia.html</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-prognosis-explained.html</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1553,25 +1553,25 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Skin changes during chemotherapy</t>
+          <t>Anaemia during cancer treatment</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>skin-changes-chemotherapy</t>
+          <t>cancer-related-anaemia</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/skin-changes-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-related-anaemia.html</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1580,25 +1580,25 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Cancer treatment during pregnancy</t>
+          <t>Skin changes during chemotherapy</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>cancer-treatment-pregnancy</t>
+          <t>skin-changes-chemotherapy</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-treatment-pregnancy.html</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/skin-changes-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1607,25 +1607,25 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Triple negative breast cancer</t>
+          <t>Cancer treatment during pregnancy</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>triple-negative-breast-cancer</t>
+          <t>cancer-treatment-pregnancy</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/triple-negative-breast-cancer.html</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-treatment-pregnancy.html</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1634,25 +1634,25 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>HER2 positive breast cancer</t>
+          <t>Triple negative breast cancer</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>her2-positive-breast-cancer</t>
+          <t>triple-negative-breast-cancer</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/her2-positive-breast-cancer.html</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/triple-negative-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1661,25 +1661,25 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Stomach cancer symptoms</t>
+          <t>HER2 positive breast cancer</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>stomach-cancer-symptoms</t>
+          <t>her2-positive-breast-cancer</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/stomach-cancer-symptoms.html</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/her2-positive-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1688,25 +1688,25 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Kidney cancer treatment options</t>
+          <t>Stomach cancer symptoms</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>kidney-cancer-treatment</t>
+          <t>stomach-cancer-symptoms</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/kidney-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/stomach-cancer-symptoms.html</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1715,25 +1715,25 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Bladder cancer diagnosis</t>
+          <t>Kidney cancer treatment options</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>bladder-cancer-diagnosis</t>
+          <t>kidney-cancer-treatment</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/bladder-cancer-diagnosis.html</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/kidney-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1742,25 +1742,25 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Thyroid cancer types and treatment</t>
+          <t>Bladder cancer diagnosis</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>thyroid-cancer-treatment</t>
+          <t>bladder-cancer-diagnosis</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/thyroid-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/bladder-cancer-diagnosis.html</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1769,25 +1769,25 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Prostate cancer treatment options</t>
+          <t>Thyroid cancer types and treatment</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>prostate-cancer-treatment</t>
+          <t>thyroid-cancer-treatment</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/prostate-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/thyroid-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1796,25 +1796,25 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Esophageal cancer symptoms</t>
+          <t>Prostate cancer treatment options</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>esophageal-cancer-symptoms</t>
+          <t>prostate-cancer-treatment</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/esophageal-cancer-symptoms.html</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/prostate-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1823,25 +1823,25 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Cervical cancer prevention and HPV vaccine</t>
+          <t>Esophageal cancer symptoms</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>cervical-cancer-hpv-vaccine</t>
+          <t>esophageal-cancer-symptoms</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cervical-cancer-hpv-vaccine.html</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/esophageal-cancer-symptoms.html</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1850,25 +1850,25 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Cancer screening guidelines India</t>
+          <t>Cervical cancer prevention and HPV vaccine</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>cancer-screening-india</t>
+          <t>cervical-cancer-hpv-vaccine</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-screening-india.html</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cervical-cancer-hpv-vaccine.html</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1877,25 +1877,25 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Why cancer second opinion matters</t>
+          <t>Cancer screening guidelines India</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>why-cancer-second-opinion</t>
+          <t>cancer-screening-india</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/why-cancer-second-opinion.html</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-screening-india.html</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1904,25 +1904,25 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Preparing for your first chemotherapy session</t>
+          <t>Why cancer second opinion matters</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>preparing-for-chemotherapy</t>
+          <t>why-cancer-second-opinion</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/preparing-for-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/why-cancer-second-opinion.html</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1931,25 +1931,25 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Cancer caregiver guide</t>
+          <t>Preparing for your first chemotherapy session</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>cancer-caregiver-guide</t>
+          <t>preparing-for-chemotherapy</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-caregiver-guide.html</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/preparing-for-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1958,25 +1958,25 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Cancer pain relief options</t>
+          <t>Cancer caregiver guide</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>cancer-pain-relief</t>
+          <t>cancer-caregiver-guide</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-pain-relief.html</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-caregiver-guide.html</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1985,27 +1985,27 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>(pre-existing page)</t>
+          <t>Cancer pain relief options</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>_template</t>
+          <t>cancer-pain-relief</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/_template.html</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
+          <t>https://cioncancerdrowais.com/cancer-pain-relief.html</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>_template</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/about.html</t>
+          <t>https://cioncancerdrowais.com/_template.html</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>book-appointment</t>
+          <t>about</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/book-appointment.html</t>
+          <t>https://cioncancerdrowais.com/about.html</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>cancer-cost-and-aarogyasri</t>
+          <t>book-appointment</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-cost-and-aarogyasri.html</t>
+          <t>https://cioncancerdrowais.com/book-appointment.html</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>cancer-staging-explained</t>
+          <t>cancer-cost-and-aarogyasri</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-staging-explained.html</t>
+          <t>https://cioncancerdrowais.com/cancer-cost-and-aarogyasri.html</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>cancer-treatment-options</t>
+          <t>cancer-staging-explained</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-treatment-options.html</t>
+          <t>https://cioncancerdrowais.com/cancer-staging-explained.html</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>cancer-warning-signs</t>
+          <t>cancer-treatment-options</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-warning-signs.html</t>
+          <t>https://cioncancerdrowais.com/cancer-treatment-options.html</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>caring-for-a-cancer-patient</t>
+          <t>cancer-warning-signs</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/caring-for-a-cancer-patient.html</t>
+          <t>https://cioncancerdrowais.com/cancer-warning-signs.html</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>chemotherapy-side-effects</t>
+          <t>caring-for-a-cancer-patient</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy-side-effects.html</t>
+          <t>https://cioncancerdrowais.com/caring-for-a-cancer-patient.html</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>chemotherapy-side-effects</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy.html</t>
+          <t>https://cioncancerdrowais.com/chemotherapy-side-effects.html</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>chemotherapy</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/faq.html</t>
+          <t>https://cioncancerdrowais.com/chemotherapy.html</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>immunotherapy</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/immunotherapy.html</t>
+          <t>https://cioncancerdrowais.com/faq.html</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>immunotherapy</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/index.html</t>
+          <t>https://cioncancerdrowais.com/immunotherapy.html</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>low-white-blood-count-during-chemotherapy</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/low-white-blood-count-during-chemotherapy.html</t>
+          <t>https://cioncancerdrowais.com/index.html</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>lung-cancer</t>
+          <t>low-white-blood-count-during-chemotherapy</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/lung-cancer.html</t>
+          <t>https://cioncancerdrowais.com/low-white-blood-count-during-chemotherapy.html</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>lung-cancer</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/privacy.html</t>
+          <t>https://cioncancerdrowais.com/lung-cancer.html</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>second-opinion</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/second-opinion.html</t>
+          <t>https://cioncancerdrowais.com/privacy.html</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>targeted-therapy</t>
+          <t>second-opinion</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/targeted-therapy.html</t>
+          <t>https://cioncancerdrowais.com/second-opinion.html</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>understanding-cancer</t>
+          <t>targeted-therapy</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/understanding-cancer.html</t>
+          <t>https://cioncancerdrowais.com/targeted-therapy.html</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2508,15 +2508,42 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
+          <t>understanding-cancer</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrowais.com/understanding-cancer.html</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
           <t>what-is-a-biopsy</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>https://cioncancerdrowais.com/what-is-a-biopsy.html</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>Published ✓</t>
         </is>
@@ -2599,6 +2626,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2729,7 +2757,7 @@
           <t>https://cioncancerdrvinay.com/laparoscopic-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2756,7 +2784,7 @@
           <t>https://cioncancerdrvinay.com/lumpectomy-breast-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2783,7 +2811,7 @@
           <t>https://cioncancerdrvinay.com/mastectomy-types-recovery.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2810,7 +2838,7 @@
           <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2837,7 +2865,7 @@
           <t>https://cioncancerdrvinay.com/thyroid-surgery-cancer.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2864,7 +2892,7 @@
           <t>https://cioncancerdrvinay.com/colorectal-surgery.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2891,7 +2919,7 @@
           <t>https://cioncancerdrvinay.com/colostomy-explained.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2918,7 +2946,7 @@
           <t>https://cioncancerdrvinay.com/ileostomy-care.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2945,7 +2973,7 @@
           <t>https://cioncancerdrvinay.com/liver-resection-surgery.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2972,7 +3000,7 @@
           <t>https://cioncancerdrvinay.com/splenectomy-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2999,7 +3027,7 @@
           <t>https://cioncancerdrvinay.com/nephrectomy-surgery.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3026,7 +3054,7 @@
           <t>https://cioncancerdrvinay.com/ovarian-debulking-surgery.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3053,7 +3081,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-wound-care.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3080,7 +3108,7 @@
           <t>https://cioncancerdrvinay.com/post-surgery-pain-management.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3107,7 +3135,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3134,7 +3162,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-complications.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3161,7 +3189,7 @@
           <t>https://cioncancerdrvinay.com/dvt-prevention-after-surgery.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3188,7 +3216,7 @@
           <t>https://cioncancerdrvinay.com/pre-surgery-preparation.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3215,7 +3243,7 @@
           <t>https://cioncancerdrvinay.com/nutrition-before-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3242,7 +3270,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-anaesthesia.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3269,7 +3297,7 @@
           <t>https://cioncancerdrvinay.com/surgical-staging-cancer.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3296,7 +3324,7 @@
           <t>https://cioncancerdrvinay.com/curative-vs-palliative-surgery.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3323,7 +3351,7 @@
           <t>https://cioncancerdrvinay.com/breast-reconstruction-after-mastectomy.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3350,7 +3378,7 @@
           <t>https://cioncancerdrvinay.com/port-insertion-surgery.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3377,7 +3405,7 @@
           <t>https://cioncancerdrvinay.com/vats-thoracoscopy.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3404,7 +3432,7 @@
           <t>https://cioncancerdrvinay.com/esophagectomy-surgery.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3431,7 +3459,7 @@
           <t>https://cioncancerdrvinay.com/gastrectomy-types.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3458,7 +3486,7 @@
           <t>https://cioncancerdrvinay.com/pancreatectomy-procedure.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3485,7 +3513,7 @@
           <t>https://cioncancerdrvinay.com/whipple-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3512,7 +3540,7 @@
           <t>https://cioncancerdrvinay.com/hernia-after-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3539,7 +3567,7 @@
           <t>https://cioncancerdrvinay.com/scar-management-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3566,7 +3594,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-elderly.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3593,7 +3621,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-cost-hyderabad.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3620,7 +3648,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-questions.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3647,7 +3675,7 @@
           <t>https://cioncancerdrvinay.com/life-after-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3674,7 +3702,7 @@
           <t>https://cioncancerdrvinay.com/robotic-cancer-surgery-india.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3701,7 +3729,7 @@
           <t>https://cioncancerdrvinay.com/abdominal-cancer-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3728,7 +3756,7 @@
           <t>https://cioncancerdrvinay.com/rectal-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3755,7 +3783,7 @@
           <t>https://cioncancerdrvinay.com/parathyroid-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3782,7 +3810,7 @@
           <t>https://cioncancerdrvinay.com/adrenalectomy-procedure.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3809,7 +3837,7 @@
           <t>https://cioncancerdrvinay.com/pelvic-exenteration-surgery.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3836,7 +3864,7 @@
           <t>https://cioncancerdrvinay.com/lymph-node-removal-surgery.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3863,7 +3891,7 @@
           <t>https://cioncancerdrvinay.com/cancer-biopsy-types.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3890,7 +3918,7 @@
           <t>https://cioncancerdrvinay.com/intraoperative-frozen-section.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3917,7 +3945,7 @@
           <t>https://cioncancerdrvinay.com/cancer-resection-margins.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3944,7 +3972,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-second-opinion.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3971,7 +3999,7 @@
           <t>https://cioncancerdrvinay.com/day-surgery-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3998,7 +4026,7 @@
           <t>https://cioncancerdrvinay.com/reconstructive-flap-surgery.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4025,7 +4053,7 @@
           <t>https://cioncancerdrvinay.com/questions-for-cancer-surgeon.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4749,7 +4777,7 @@
           <t>https://cioncancerdrmurali.com/skin-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4776,7 +4804,7 @@
           <t>https://cioncancerdrmurali.com/retroperitoneal-sarcoma-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4803,7 +4831,7 @@
           <t>https://cioncancerdrmurali.com/leiomyosarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4830,7 +4858,7 @@
           <t>https://cioncancerdrmurali.com/liposarcoma-surgery.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4857,7 +4885,7 @@
           <t>https://cioncancerdrmurali.com/limb-sparing-surgery.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4884,7 +4912,7 @@
           <t>https://cioncancerdrmurali.com/osteosarcoma-limb-salvage.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4911,7 +4939,7 @@
           <t>https://cioncancerdrmurali.com/rectal-sphincter-preservation.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4938,7 +4966,7 @@
           <t>https://cioncancerdrmurali.com/low-anterior-resection.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4965,7 +4993,7 @@
           <t>https://cioncancerdrmurali.com/sigmoid-colon-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4992,7 +5020,7 @@
           <t>https://cioncancerdrmurali.com/laparoscopic-bowel-resection.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5019,7 +5047,7 @@
           <t>https://cioncancerdrmurali.com/hemorrhoids-vs-rectal-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5046,7 +5074,7 @@
           <t>https://cioncancerdrmurali.com/liver-metastases-surgery.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5073,7 +5101,7 @@
           <t>https://cioncancerdrmurali.com/thermal-ablation-liver-tumours.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5100,7 +5128,7 @@
           <t>https://cioncancerdrmurali.com/bile-duct-repair-surgery.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5127,7 +5155,7 @@
           <t>https://cioncancerdrmurali.com/cholecystectomy-gallbladder-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5154,7 +5182,7 @@
           <t>https://cioncancerdrmurali.com/total-gastrectomy-recovery.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5181,7 +5209,7 @@
           <t>https://cioncancerdrmurali.com/small-bowel-resection.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5208,7 +5236,7 @@
           <t>https://cioncancerdrmurali.com/peritoneal-wash-cytology.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5235,7 +5263,7 @@
           <t>https://cioncancerdrmurali.com/second-look-surgery-ovarian.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5262,7 +5290,7 @@
           <t>https://cioncancerdrmurali.com/interval-debulking-surgery.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5289,7 +5317,7 @@
           <t>https://cioncancerdrmurali.com/cancer-surgery-diabetes.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5316,7 +5344,7 @@
           <t>https://cioncancerdrmurali.com/anastomosis-leak-prevention.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5343,7 +5371,7 @@
           <t>https://cioncancerdrmurali.com/ewing-sarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5370,7 +5398,7 @@
           <t>https://cioncancerdrmurali.com/synovial-sarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5397,7 +5425,7 @@
           <t>https://cioncancerdrmurali.com/amputation-bone-cancer.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5424,7 +5452,7 @@
           <t>https://cioncancerdrmurali.com/right-hemicolectomy.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5451,7 +5479,7 @@
           <t>https://cioncancerdrmurali.com/left-hemicolectomy.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5478,7 +5506,7 @@
           <t>https://cioncancerdrmurali.com/d2-lymphadenectomy-gastric.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5505,7 +5533,7 @@
           <t>https://cioncancerdrmurali.com/portal-vein-embolization.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5532,7 +5560,7 @@
           <t>https://cioncancerdrmurali.com/distal-pancreatectomy.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5559,7 +5587,7 @@
           <t>https://cioncancerdrmurali.com/radical-cholecystectomy-gallbladder.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5586,7 +5614,7 @@
           <t>https://cioncancerdrmurali.com/gist-tumour-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5613,7 +5641,7 @@
           <t>https://cioncancerdrmurali.com/mesenteric-tumour-resection.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5640,7 +5668,7 @@
           <t>https://cioncancerdrmurali.com/colon-cancer-peritoneal-spread.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5667,7 +5695,7 @@
           <t>https://cioncancerdrmurali.com/uterine-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5694,7 +5722,7 @@
           <t>https://cioncancerdrmurali.com/malignant-ascites-management.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5721,7 +5749,7 @@
           <t>https://cioncancerdrmurali.com/laparoscopic-staging-peritoneal.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5748,7 +5776,7 @@
           <t>https://cioncancerdrmurali.com/transverse-colon-cancer.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5775,7 +5803,7 @@
           <t>https://cioncancerdrmurali.com/anorectal-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5802,7 +5830,7 @@
           <t>https://cioncancerdrmurali.com/diverticulitis-vs-colon-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5829,7 +5857,7 @@
           <t>https://cioncancerdrmurali.com/phantom-limb-pain-management.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5856,7 +5884,7 @@
           <t>https://cioncancerdrmurali.com/intraoperative-bleeding-management.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5883,7 +5911,7 @@
           <t>https://cioncancerdrmurali.com/microwave-ablation-liver.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5910,7 +5938,7 @@
           <t>https://cioncancerdrmurali.com/proximal-gastrectomy.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5937,7 +5965,7 @@
           <t>https://cioncancerdrmurali.com/pancreatic-resection-recovery.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5964,7 +5992,7 @@
           <t>https://cioncancerdrmurali.com/abdominoperineal-resection.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5991,7 +6019,7 @@
           <t>https://cioncancerdrmurali.com/stoma-reversal-surgery.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6018,7 +6046,7 @@
           <t>https://cioncancerdrmurali.com/eras-protocol-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6045,7 +6073,7 @@
           <t>https://cioncancerdrmurali.com/cancer-surgery-blood-loss.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6797,7 +6825,7 @@
           <t>https://cioncancerdrsandeep.com/tongue-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6824,7 +6852,7 @@
           <t>https://cioncancerdrsandeep.com/lip-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6851,7 +6879,7 @@
           <t>https://cioncancerdrsandeep.com/buccal-mucosa-cancer.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6878,7 +6906,7 @@
           <t>https://cioncancerdrsandeep.com/floor-of-mouth-cancer.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6905,7 +6933,7 @@
           <t>https://cioncancerdrsandeep.com/laryngeal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6932,7 +6960,7 @@
           <t>https://cioncancerdrsandeep.com/laryngectomy-voice-rehab.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6959,7 +6987,7 @@
           <t>https://cioncancerdrsandeep.com/hypopharyngeal-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6986,7 +7014,7 @@
           <t>https://cioncancerdrsandeep.com/oropharyngeal-cancer-hpv.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7013,7 +7041,7 @@
           <t>https://cioncancerdrsandeep.com/tonsil-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7040,7 +7068,7 @@
           <t>https://cioncancerdrsandeep.com/nasopharyngeal-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7067,7 +7095,7 @@
           <t>https://cioncancerdrsandeep.com/nasal-cavity-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7094,7 +7122,7 @@
           <t>https://cioncancerdrsandeep.com/salivary-gland-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7121,7 +7149,7 @@
           <t>https://cioncancerdrsandeep.com/parotid-gland-surgery.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7148,7 +7176,7 @@
           <t>https://cioncancerdrsandeep.com/neck-dissection-types.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7175,7 +7203,7 @@
           <t>https://cioncancerdrsandeep.com/modified-radical-neck-dissection.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7202,7 +7230,7 @@
           <t>https://cioncancerdrsandeep.com/total-thyroidectomy.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7229,7 +7257,7 @@
           <t>https://cioncancerdrsandeep.com/papillary-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7256,7 +7284,7 @@
           <t>https://cioncancerdrsandeep.com/follicular-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7283,7 +7311,7 @@
           <t>https://cioncancerdrsandeep.com/medullary-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7310,7 +7338,7 @@
           <t>https://cioncancerdrsandeep.com/thyroid-cancer-recurrence.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7337,7 +7365,7 @@
           <t>https://cioncancerdrsandeep.com/skull-base-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7364,7 +7392,7 @@
           <t>https://cioncancerdrsandeep.com/paraganglioma-treatment.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7391,7 +7419,7 @@
           <t>https://cioncancerdrsandeep.com/adenoid-cystic-carcinoma.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7418,7 +7446,7 @@
           <t>https://cioncancerdrsandeep.com/mucoepidermoid-carcinoma.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7445,7 +7473,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-trismus.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7472,7 +7500,7 @@
           <t>https://cioncancerdrsandeep.com/xerostomia-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7499,7 +7527,7 @@
           <t>https://cioncancerdrsandeep.com/dysphagia-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7526,7 +7554,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-rehabilitation.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7553,7 +7581,7 @@
           <t>https://cioncancerdrsandeep.com/speech-therapy-laryngectomy.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7580,7 +7608,7 @@
           <t>https://cioncancerdrsandeep.com/neck-lump-causes.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7607,7 +7635,7 @@
           <t>https://cioncancerdrsandeep.com/hoarseness-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7634,7 +7662,7 @@
           <t>https://cioncancerdrsandeep.com/mouth-ulcer-cancer-warning.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7661,7 +7689,7 @@
           <t>https://cioncancerdrsandeep.com/leukoplakia-oral-cancer.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7688,7 +7716,7 @@
           <t>https://cioncancerdrsandeep.com/submucous-fibrosis-cancer.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7715,7 +7743,7 @@
           <t>https://cioncancerdrsandeep.com/tobacco-oral-cancer.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7742,7 +7770,7 @@
           <t>https://cioncancerdrsandeep.com/base-of-tongue-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7769,7 +7797,7 @@
           <t>https://cioncancerdrsandeep.com/partial-laryngectomy.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7796,7 +7824,7 @@
           <t>https://cioncancerdrsandeep.com/palate-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7823,7 +7851,7 @@
           <t>https://cioncancerdrsandeep.com/jaw-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7850,7 +7878,7 @@
           <t>https://cioncancerdrsandeep.com/paranasal-sinus-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7877,7 +7905,7 @@
           <t>https://cioncancerdrsandeep.com/anaplastic-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7904,7 +7932,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-hyderabad.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7931,7 +7959,7 @@
           <t>https://cioncancerdrsandeep.com/swallowing-therapy-cancer.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7958,7 +7986,7 @@
           <t>https://cioncancerdrsandeep.com/radiation-head-neck-surgery.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7985,7 +8013,7 @@
           <t>https://cioncancerdrsandeep.com/chemotherapy-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8012,7 +8040,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-nutrition.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8039,7 +8067,7 @@
           <t>https://cioncancerdrsandeep.com/tracheostomy-care-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8066,7 +8094,7 @@
           <t>https://cioncancerdrsandeep.com/reconstruction-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8093,7 +8121,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-surgeon-questions.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8845,7 +8873,7 @@
           <t>https://cioncancerdrkiranmayee.com/lung-cancer-types-stages.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8872,7 +8900,7 @@
           <t>https://cioncancerdrkiranmayee.com/hormone-receptor-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8899,7 +8927,7 @@
           <t>https://cioncancerdrkiranmayee.com/non-hodgkin-lymphoma.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8926,7 +8954,7 @@
           <t>https://cioncancerdrkiranmayee.com/chronic-myeloid-leukemia.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8953,7 +8981,7 @@
           <t>https://cioncancerdrkiranmayee.com/melanoma-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8980,7 +9008,7 @@
           <t>https://cioncancerdrkiranmayee.com/pancreatic-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9007,7 +9035,7 @@
           <t>https://cioncancerdrkiranmayee.com/liver-cancer-treatment-hyderabad.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9034,7 +9062,7 @@
           <t>https://cioncancerdrkiranmayee.com/uterine-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9061,7 +9089,7 @@
           <t>https://cioncancerdrkiranmayee.com/bone-cancer-types.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9088,7 +9116,7 @@
           <t>https://cioncancerdrkiranmayee.com/soft-tissue-sarcoma.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9115,7 +9143,7 @@
           <t>https://cioncancerdrkiranmayee.com/neuroendocrine-tumours.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9142,7 +9170,7 @@
           <t>https://cioncancerdrkiranmayee.com/bile-duct-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9169,7 +9197,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-blood-clots-dvt.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9196,7 +9224,7 @@
           <t>https://cioncancerdrkiranmayee.com/checkpoint-inhibitors-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9223,7 +9251,7 @@
           <t>https://cioncancerdrkiranmayee.com/car-t-cell-therapy.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9250,7 +9278,7 @@
           <t>https://cioncancerdrkiranmayee.com/parp-inhibitors-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9277,7 +9305,7 @@
           <t>https://cioncancerdrkiranmayee.com/cdk-inhibitors-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9304,7 +9332,7 @@
           <t>https://cioncancerdrkiranmayee.com/combination-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9331,7 +9359,7 @@
           <t>https://cioncancerdrkiranmayee.com/weight-management-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9358,7 +9386,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-mental-health.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9385,7 +9413,7 @@
           <t>https://cioncancerdrkiranmayee.com/exercise-during-cancer.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9412,7 +9440,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-pain-types.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9439,7 +9467,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-end-of-life-care.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9466,7 +9494,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-rehabilitation.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9493,7 +9521,7 @@
           <t>https://cioncancerdrkiranmayee.com/return-to-work-cancer.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9520,7 +9548,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-insurance-india.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9547,7 +9575,7 @@
           <t>https://cioncancerdrkiranmayee.com/government-cancer-schemes-india.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9574,7 +9602,7 @@
           <t>https://cioncancerdrkiranmayee.com/telemedicine-cancer-followup.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9601,7 +9629,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-young-adults.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9628,7 +9656,7 @@
           <t>https://cioncancerdrkiranmayee.com/antibody-drug-conjugates.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9655,7 +9683,7 @@
           <t>https://cioncancerdrkiranmayee.com/maintenance-therapy-cancer.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9682,7 +9710,7 @@
           <t>https://cioncancerdrkiranmayee.com/adjuvant-neoadjuvant-therapy.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9709,7 +9737,7 @@
           <t>https://cioncancerdrkiranmayee.com/dose-dense-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9736,7 +9764,7 @@
           <t>https://cioncancerdrkiranmayee.com/growth-factors-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9763,7 +9791,7 @@
           <t>https://cioncancerdrkiranmayee.com/febrile-neutropenia.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9790,7 +9818,7 @@
           <t>https://cioncancerdrkiranmayee.com/cardio-oncology-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9817,7 +9845,7 @@
           <t>https://cioncancerdrkiranmayee.com/second-primary-cancer.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9844,7 +9872,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-treatment-at-home.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9871,7 +9899,7 @@
           <t>https://cioncancerdrkiranmayee.com/oral-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9898,7 +9926,7 @@
           <t>https://cioncancerdrkiranmayee.com/colon-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9925,7 +9953,7 @@
           <t>https://cioncancerdrkiranmayee.com/pancreatic-cancer-warning-signs.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9952,7 +9980,7 @@
           <t>https://cioncancerdrkiranmayee.com/vulvar-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9979,7 +10007,7 @@
           <t>https://cioncancerdrkiranmayee.com/penile-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10006,7 +10034,7 @@
           <t>https://cioncancerdrkiranmayee.com/anal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10033,7 +10061,7 @@
           <t>https://cioncancerdrkiranmayee.com/adrenal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10060,7 +10088,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-genetic-counselling.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10087,7 +10115,7 @@
           <t>https://cioncancerdrkiranmayee.com/complementary-medicine-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10114,7 +10142,7 @@
           <t>https://cioncancerdrkiranmayee.com/hospice-care-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10141,7 +10169,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-caregiver-burnout.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10893,7 +10921,7 @@
           <t>https://cioncancerdrbasudev.com/autologous-bmt.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10920,7 +10948,7 @@
           <t>https://cioncancerdrbasudev.com/allogeneic-bmt.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10947,7 +10975,7 @@
           <t>https://cioncancerdrbasudev.com/stem-cell-donation.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10974,7 +11002,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-donor-compatibility.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11001,7 +11029,7 @@
           <t>https://cioncancerdrbasudev.com/bmt-recovery-timeline.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11028,7 +11056,7 @@
           <t>https://cioncancerdrbasudev.com/graft-versus-host-disease.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11055,7 +11083,7 @@
           <t>https://cioncancerdrbasudev.com/chronic-gvhd-management.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11082,7 +11110,7 @@
           <t>https://cioncancerdrbasudev.com/what-is-leukemia.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11109,7 +11137,7 @@
           <t>https://cioncancerdrbasudev.com/acute-myeloid-leukemia.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11136,7 +11164,7 @@
           <t>https://cioncancerdrbasudev.com/acute-lymphoblastic-leukemia.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11163,7 +11191,7 @@
           <t>https://cioncancerdrbasudev.com/chronic-lymphocytic-leukemia.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11190,7 +11218,7 @@
           <t>https://cioncancerdrbasudev.com/hairy-cell-leukemia.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11217,7 +11245,7 @@
           <t>https://cioncancerdrbasudev.com/myelodysplastic-syndrome.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11244,7 +11272,7 @@
           <t>https://cioncancerdrbasudev.com/myelofibrosis-treatment.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11271,7 +11299,7 @@
           <t>https://cioncancerdrbasudev.com/polycythemia-vera.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11298,7 +11326,7 @@
           <t>https://cioncancerdrbasudev.com/essential-thrombocythemia.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11325,7 +11353,7 @@
           <t>https://cioncancerdrbasudev.com/aplastic-anemia-treatment.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11352,7 +11380,7 @@
           <t>https://cioncancerdrbasudev.com/thalassemia-stem-cell-therapy.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11379,7 +11407,7 @@
           <t>https://cioncancerdrbasudev.com/hodgkin-lymphoma-treatment.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11406,7 +11434,7 @@
           <t>https://cioncancerdrbasudev.com/diffuse-large-b-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11433,7 +11461,7 @@
           <t>https://cioncancerdrbasudev.com/follicular-lymphoma.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11460,7 +11488,7 @@
           <t>https://cioncancerdrbasudev.com/mantle-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11487,7 +11515,7 @@
           <t>https://cioncancerdrbasudev.com/burkitt-lymphoma.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11514,7 +11542,7 @@
           <t>https://cioncancerdrbasudev.com/t-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11541,7 +11569,7 @@
           <t>https://cioncancerdrbasudev.com/waldenstrom-macroglobulinemia.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11568,7 +11596,7 @@
           <t>https://cioncancerdrbasudev.com/multiple-myeloma-bone-pain.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11595,7 +11623,7 @@
           <t>https://cioncancerdrbasudev.com/smoldering-myeloma.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11622,7 +11650,7 @@
           <t>https://cioncancerdrbasudev.com/bortezomib-myeloma.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11649,7 +11677,7 @@
           <t>https://cioncancerdrbasudev.com/daratumumab-myeloma.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11676,7 +11704,7 @@
           <t>https://cioncancerdrbasudev.com/venetoclax-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11703,7 +11731,7 @@
           <t>https://cioncancerdrbasudev.com/ibrutinib-cll.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11730,7 +11758,7 @@
           <t>https://cioncancerdrbasudev.com/rituximab-lymphoma.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11757,7 +11785,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-biopsy-procedure.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11784,7 +11812,7 @@
           <t>https://cioncancerdrbasudev.com/cbc-cancer-interpretation.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11811,7 +11839,7 @@
           <t>https://cioncancerdrbasudev.com/flow-cytometry-cancer.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11838,7 +11866,7 @@
           <t>https://cioncancerdrbasudev.com/fish-testing-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11865,7 +11893,7 @@
           <t>https://cioncancerdrbasudev.com/blood-cancer-treatment-hyderabad.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11892,7 +11920,7 @@
           <t>https://cioncancerdrbasudev.com/bmt-cost-india.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11919,7 +11947,7 @@
           <t>https://cioncancerdrbasudev.com/life-after-bmt.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11946,7 +11974,7 @@
           <t>https://cioncancerdrbasudev.com/infections-after-bmt.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11973,7 +12001,7 @@
           <t>https://cioncancerdrbasudev.com/engraftment-syndrome.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12000,7 +12028,7 @@
           <t>https://cioncancerdrbasudev.com/peripheral-blood-stem-cell-harvest.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12027,7 +12055,7 @@
           <t>https://cioncancerdrbasudev.com/cord-blood-transplant.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12054,7 +12082,7 @@
           <t>https://cioncancerdrbasudev.com/haploidentical-transplant.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12081,7 +12109,7 @@
           <t>https://cioncancerdrbasudev.com/reduced-intensity-conditioning-bmt.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12108,7 +12136,7 @@
           <t>https://cioncancerdrbasudev.com/nk-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12135,7 +12163,7 @@
           <t>https://cioncancerdrbasudev.com/amyloidosis-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12162,7 +12190,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-failure-syndromes.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12189,7 +12217,7 @@
           <t>https://cioncancerdrbasudev.com/blood-cancer-diet-nutrition.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12941,7 +12969,7 @@
           <t>https://cioncancerdrraghvendra.com/external-beam-radiation.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12968,7 +12996,7 @@
           <t>https://cioncancerdrraghvendra.com/imrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12995,7 +13023,7 @@
           <t>https://cioncancerdrraghvendra.com/igrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13022,7 +13050,7 @@
           <t>https://cioncancerdrraghvendra.com/stereotactic-radiosurgery.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13049,7 +13077,7 @@
           <t>https://cioncancerdrraghvendra.com/sbrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13076,7 +13104,7 @@
           <t>https://cioncancerdrraghvendra.com/brachytherapy-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13103,7 +13131,7 @@
           <t>https://cioncancerdrraghvendra.com/high-dose-rate-brachytherapy.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13130,7 +13158,7 @@
           <t>https://cioncancerdrraghvendra.com/breast-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13157,7 +13185,7 @@
           <t>https://cioncancerdrraghvendra.com/cervical-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13184,7 +13212,7 @@
           <t>https://cioncancerdrraghvendra.com/prostate-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13211,7 +13239,7 @@
           <t>https://cioncancerdrraghvendra.com/lung-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13238,7 +13266,7 @@
           <t>https://cioncancerdrraghvendra.com/head-neck-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13265,7 +13293,7 @@
           <t>https://cioncancerdrraghvendra.com/rectal-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13292,7 +13320,7 @@
           <t>https://cioncancerdrraghvendra.com/whole-brain-radiation.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13319,7 +13347,7 @@
           <t>https://cioncancerdrraghvendra.com/palliative-radiation-bone-pain.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13346,7 +13374,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-side-effects.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13373,7 +13401,7 @@
           <t>https://cioncancerdrraghvendra.com/skin-reactions-radiation.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13400,7 +13428,7 @@
           <t>https://cioncancerdrraghvendra.com/fatigue-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13427,7 +13455,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-mucositis.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13454,7 +13482,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-enteritis.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13481,7 +13509,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-cystitis.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13508,7 +13536,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-simulation.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13535,7 +13563,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-treatment-planning.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13562,7 +13590,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-fractions.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13589,7 +13617,7 @@
           <t>https://cioncancerdrraghvendra.com/hypofractionated-radiation.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13616,7 +13644,7 @@
           <t>https://cioncancerdrraghvendra.com/concurrent-chemoradiation.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13643,7 +13671,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-brain-metastases.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13670,7 +13698,7 @@
           <t>https://cioncancerdrraghvendra.com/spinal-cord-compression-radiation.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13697,7 +13725,7 @@
           <t>https://cioncancerdrraghvendra.com/sabr-liver-tumours.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13724,7 +13752,7 @@
           <t>https://cioncancerdrraghvendra.com/radioiodine-therapy-thyroid.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13751,7 +13779,7 @@
           <t>https://cioncancerdrraghvendra.com/prrt-neuroendocrine-tumours.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13778,7 +13806,7 @@
           <t>https://cioncancerdrraghvendra.com/lutetium-dotatate-therapy.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13805,7 +13833,7 @@
           <t>https://cioncancerdrraghvendra.com/y90-radioembolization.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13832,7 +13860,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-vs-surgery.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13859,7 +13887,7 @@
           <t>https://cioncancerdrraghvendra.com/proton-therapy-vs-radiation.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13886,7 +13914,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-quality-of-life.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13913,7 +13941,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-myths.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13940,7 +13968,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-cost-hyderabad.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13967,7 +13995,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-safety.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13994,7 +14022,7 @@
           <t>https://cioncancerdrraghvendra.com/re-irradiation-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14021,7 +14049,7 @@
           <t>https://cioncancerdrraghvendra.com/second-cancer-after-radiation.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14048,7 +14076,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-protection-family.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14075,7 +14103,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-fertility.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14102,7 +14130,7 @@
           <t>https://cioncancerdrraghvendra.com/accelerated-partial-breast-irradiation.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14129,7 +14157,7 @@
           <t>https://cioncancerdrraghvendra.com/intraoperative-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14156,7 +14184,7 @@
           <t>https://cioncancerdrraghvendra.com/total-body-irradiation.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14183,7 +14211,7 @@
           <t>https://cioncancerdrraghvendra.com/radiofrequency-ablation-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14210,7 +14238,7 @@
           <t>https://cioncancerdrraghvendra.com/tace-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14237,7 +14265,7 @@
           <t>https://cioncancerdrraghvendra.com/esophageal-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14989,7 +15017,7 @@
           <t>https://cioncancerdrcraghavendra.info/rectal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15016,7 +15044,7 @@
           <t>https://cioncancerdrcraghavendra.info/appendix-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15043,7 +15071,7 @@
           <t>https://cioncancerdrcraghavendra.info/peritoneal-carcinomatosis.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15070,7 +15098,7 @@
           <t>https://cioncancerdrcraghavendra.info/cea-tumor-marker.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15097,7 +15125,7 @@
           <t>https://cioncancerdrcraghavendra.info/ca125-test-explained.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15124,7 +15152,7 @@
           <t>https://cioncancerdrcraghavendra.info/ca19-9-test-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15151,7 +15179,7 @@
           <t>https://cioncancerdrcraghavendra.info/afp-test-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15178,7 +15206,7 @@
           <t>https://cioncancerdrcraghavendra.info/psa-test-explained.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15205,7 +15233,7 @@
           <t>https://cioncancerdrcraghavendra.info/core-needle-biopsy.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15232,7 +15260,7 @@
           <t>https://cioncancerdrcraghavendra.info/liquid-biopsy-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15259,7 +15287,7 @@
           <t>https://cioncancerdrcraghavendra.info/next-generation-sequencing-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15286,7 +15314,7 @@
           <t>https://cioncancerdrcraghavendra.info/microsatellite-instability.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15313,7 +15341,7 @@
           <t>https://cioncancerdrcraghavendra.info/kras-mutation-colorectal.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15340,7 +15368,7 @@
           <t>https://cioncancerdrcraghavendra.info/egfr-mutation-lung-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15367,7 +15395,7 @@
           <t>https://cioncancerdrcraghavendra.info/braf-mutation-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15394,7 +15422,7 @@
           <t>https://cioncancerdrcraghavendra.info/pdl1-expression-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15421,7 +15449,7 @@
           <t>https://cioncancerdrcraghavendra.info/precision-oncology-hyderabad.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15448,7 +15476,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-diet-myths.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15475,7 +15503,7 @@
           <t>https://cioncancerdrcraghavendra.info/sugar-cancer-link.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15502,7 +15530,7 @@
           <t>https://cioncancerdrcraghavendra.info/alcohol-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15529,7 +15557,7 @@
           <t>https://cioncancerdrcraghavendra.info/obesity-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15556,7 +15584,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-prevention-strategies.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15583,7 +15611,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-early-detection-india.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15610,7 +15638,7 @@
           <t>https://cioncancerdrcraghavendra.info/colonoscopy-screening.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15637,7 +15665,7 @@
           <t>https://cioncancerdrcraghavendra.info/mammography-screening.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15664,7 +15692,7 @@
           <t>https://cioncancerdrcraghavendra.info/pap-smear-screening.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15691,7 +15719,7 @@
           <t>https://cioncancerdrcraghavendra.info/recist-criteria-cancer.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15718,7 +15746,7 @@
           <t>https://cioncancerdrcraghavendra.info/adjuvant-chemotherapy-explained.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15745,7 +15773,7 @@
           <t>https://cioncancerdrcraghavendra.info/bone-marrow-suppression.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15772,7 +15800,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-biomarkers-explained.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15799,7 +15827,7 @@
           <t>https://cioncancerdrcraghavendra.info/biliary-tract-cancer.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15826,7 +15854,7 @@
           <t>https://cioncancerdrcraghavendra.info/duodenal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15853,7 +15881,7 @@
           <t>https://cioncancerdrcraghavendra.info/small-intestine-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15880,7 +15908,7 @@
           <t>https://cioncancerdrcraghavendra.info/tumor-biopsy-types.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15907,7 +15935,7 @@
           <t>https://cioncancerdrcraghavendra.info/smoking-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15934,7 +15962,7 @@
           <t>https://cioncancerdrcraghavendra.info/red-meat-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15961,7 +15989,7 @@
           <t>https://cioncancerdrcraghavendra.info/stress-cancer-link.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15988,7 +16016,7 @@
           <t>https://cioncancerdrcraghavendra.info/turmeric-cancer-research.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16015,7 +16043,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-treatment-cost-india.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16042,7 +16070,7 @@
           <t>https://cioncancerdrcraghavendra.info/ayushman-bharat-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16069,7 +16097,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-screening-age-guidelines.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16096,7 +16124,7 @@
           <t>https://cioncancerdrcraghavendra.info/tumor-mutational-burden.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16123,7 +16151,7 @@
           <t>https://cioncancerdrcraghavendra.info/msi-high-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16150,7 +16178,7 @@
           <t>https://cioncancerdrcraghavendra.info/colorectal-cancer-followup.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16177,7 +16205,7 @@
           <t>https://cioncancerdrcraghavendra.info/kras-wildtype-colorectal.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16204,7 +16232,7 @@
           <t>https://cioncancerdrcraghavendra.info/stoma-care-colorectal.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16231,7 +16259,7 @@
           <t>https://cioncancerdrcraghavendra.info/rectal-bleeding-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16258,7 +16286,7 @@
           <t>https://cioncancerdrcraghavendra.info/bowel-habits-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16285,7 +16313,7 @@
           <t>https://cioncancerdrcraghavendra.info/iron-deficiency-anaemia-cancer.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17065,7 +17093,7 @@
           <t>https://cioncancerdrimad.com/hipec-ovarian-cancer.html</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17092,7 +17120,7 @@
           <t>https://cioncancerdrimad.com/hipec-colorectal-cancer.html</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17119,7 +17147,7 @@
           <t>https://cioncancerdrimad.com/hipec-gastric-cancer.html</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17146,7 +17174,7 @@
           <t>https://cioncancerdrimad.com/pipac-procedure-explained.html</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17173,7 +17201,7 @@
           <t>https://cioncancerdrimad.com/pipac-vs-hipec.html</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17200,7 +17228,7 @@
           <t>https://cioncancerdrimad.com/cytoreductive-surgery-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17227,7 +17255,7 @@
           <t>https://cioncancerdrimad.com/pci-score-peritoneal-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17254,7 +17282,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-metastases-treatment.html</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17281,7 +17309,7 @@
           <t>https://cioncancerdrimad.com/pseudomyxoma-peritonei.html</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17308,7 +17336,7 @@
           <t>https://cioncancerdrimad.com/appendix-cancer-mucinous.html</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17335,7 +17363,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-mesothelioma.html</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17362,7 +17390,7 @@
           <t>https://cioncancerdrimad.com/primary-peritoneal-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17389,7 +17417,7 @@
           <t>https://cioncancerdrimad.com/gastric-cancer-surgery-options.html</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17416,7 +17444,7 @@
           <t>https://cioncancerdrimad.com/total-gastrectomy-stomach-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17443,7 +17471,7 @@
           <t>https://cioncancerdrimad.com/d2-dissection-gastric-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17470,7 +17498,7 @@
           <t>https://cioncancerdrimad.com/esophagogastric-junction-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17497,7 +17525,7 @@
           <t>https://cioncancerdrimad.com/whipple-procedure-guide.html</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17524,7 +17552,7 @@
           <t>https://cioncancerdrimad.com/whipple-recovery-diet.html</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17551,7 +17579,7 @@
           <t>https://cioncancerdrimad.com/pylorus-preserving-whipple.html</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17578,7 +17606,7 @@
           <t>https://cioncancerdrimad.com/distal-pancreatectomy-splenectomy.html</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17605,7 +17633,7 @@
           <t>https://cioncancerdrimad.com/borderline-resectable-pancreatic.html</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17632,7 +17660,7 @@
           <t>https://cioncancerdrimad.com/hepatobiliary-cancer-hyderabad.html</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17659,7 +17687,7 @@
           <t>https://cioncancerdrimad.com/right-hepatectomy-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17686,7 +17714,7 @@
           <t>https://cioncancerdrimad.com/klatskin-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17713,7 +17741,7 @@
           <t>https://cioncancerdrimad.com/gallbladder-cancer-surgery-options.html</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17740,7 +17768,7 @@
           <t>https://cioncancerdrimad.com/radical-cholecystectomy.html</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17767,7 +17795,7 @@
           <t>https://cioncancerdrimad.com/gist-treatment-imatinib.html</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17794,7 +17822,7 @@
           <t>https://cioncancerdrimad.com/retroperitoneal-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17821,7 +17849,7 @@
           <t>https://cioncancerdrimad.com/colorectal-liver-metastases-crs.html</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17848,7 +17876,7 @@
           <t>https://cioncancerdrimad.com/ovarian-cancer-hipec.html</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17875,7 +17903,7 @@
           <t>https://cioncancerdrimad.com/brca-ovarian-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17902,7 +17930,7 @@
           <t>https://cioncancerdrimad.com/malignant-ascites-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17929,7 +17957,7 @@
           <t>https://cioncancerdrimad.com/laparoscopic-staging.html</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17956,7 +17984,7 @@
           <t>https://cioncancerdrimad.com/second-opinion-hipec.html</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17983,7 +18011,7 @@
           <t>https://cioncancerdrimad.com/hipec-cost-india.html</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18010,7 +18038,7 @@
           <t>https://cioncancerdrimad.com/life-after-hipec.html</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18037,7 +18065,7 @@
           <t>https://cioncancerdrimad.com/recovery-cytoreductive-surgery.html</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18064,7 +18092,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-cancer-surgery-possible.html</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18091,7 +18119,7 @@
           <t>https://cioncancerdrimad.com/hipec-contraindications.html</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18118,7 +18146,7 @@
           <t>https://cioncancerdrimad.com/intraperitoneal-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18145,7 +18173,7 @@
           <t>https://cioncancerdrimad.com/gastric-cancer-peritoneal-spread.html</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18172,7 +18200,7 @@
           <t>https://cioncancerdrimad.com/appendix-rupture-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18199,7 +18227,7 @@
           <t>https://cioncancerdrimad.com/liver-cancer-resection.html</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18226,7 +18254,7 @@
           <t>https://cioncancerdrimad.com/portal-vein-pancreatic-cancer.html</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18253,7 +18281,7 @@
           <t>https://cioncancerdrimad.com/gi-cancer-second-opinion-hyderabad.html</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18280,7 +18308,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-cancer-survival.html</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18307,7 +18335,7 @@
           <t>https://cioncancerdrimad.com/laparoscopic-vs-open-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18334,7 +18362,7 @@
           <t>https://cioncancerdrimad.com/crs-hipec-vs-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18361,7 +18389,7 @@
           <t>https://cioncancerdrimad.com/cancers-that-spread-to-peritoneum.html</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>

--- a/trackers/all-sites.xlsx
+++ b/trackers/all-sites.xlsx
@@ -2710,29 +2710,29 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Types of cancer surgery</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>types-cancer-surgery</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>https://cioncancerdrvinay.com/types-cancer-surgery.html</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Today →</t>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>breast-cancer-staging</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrvinay.com/breast-cancer-staging.html</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
         </is>
       </c>
     </row>

--- a/trackers/all-sites.xlsx
+++ b/trackers/all-sites.xlsx
@@ -151,10 +151,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -667,17 +667,17 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Nausea and vomiting after chemotherapy</t>
+          <t>(pre-existing page)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>what-is-a-chemo-port</t>
+          <t>what-is-cancer-remission</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/what-is-a-chemo-port.html</t>
+          <t>https://cioncancerdrowais.com/what-is-cancer-remission.html</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -689,52 +689,52 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Hair loss during cancer treatment</t>
+          <t>Nausea and vomiting after chemotherapy</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>hair-loss-cancer-treatment</t>
+          <t>what-is-a-chemo-port</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/hair-loss-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+          <t>https://cioncancerdrowais.com/what-is-a-chemo-port.html</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Cancer-related fatigue management</t>
+          <t>Hair loss during cancer treatment</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>cancer-fatigue-management</t>
+          <t>hair-loss-cancer-treatment</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-fatigue-management.html</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/hair-loss-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -743,25 +743,25 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Nutrition and diet during cancer treatment</t>
+          <t>Cancer-related fatigue management</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>cancer-nutrition-diet</t>
+          <t>cancer-fatigue-management</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-nutrition-diet.html</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-fatigue-management.html</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -770,25 +770,25 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Breast cancer treatment options</t>
+          <t>Nutrition and diet during cancer treatment</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>breast-cancer-treatment</t>
+          <t>cancer-nutrition-diet</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/breast-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-nutrition-diet.html</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -797,25 +797,25 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cervical cancer symptoms and treatment</t>
+          <t>Breast cancer treatment options</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>cervical-cancer-treatment</t>
+          <t>breast-cancer-treatment</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cervical-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/breast-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -824,25 +824,25 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Ovarian cancer signs and diagnosis</t>
+          <t>Cervical cancer symptoms and treatment</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>ovarian-cancer-diagnosis</t>
+          <t>cervical-cancer-treatment</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/ovarian-cancer-diagnosis.html</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cervical-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -851,25 +851,25 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Colorectal cancer screening</t>
+          <t>Ovarian cancer signs and diagnosis</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>colorectal-cancer-screening</t>
+          <t>ovarian-cancer-diagnosis</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/colorectal-cancer-screening.html</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/ovarian-cancer-diagnosis.html</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -878,25 +878,25 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>What is lymphoma</t>
+          <t>Colorectal cancer screening</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>what-is-lymphoma</t>
+          <t>colorectal-cancer-screening</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/what-is-lymphoma.html</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/colorectal-cancer-screening.html</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -905,25 +905,25 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Types of leukemia</t>
+          <t>What is lymphoma</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>types-of-leukemia</t>
+          <t>what-is-lymphoma</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/types-of-leukemia.html</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/what-is-lymphoma.html</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -932,25 +932,25 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Multiple myeloma treatment</t>
+          <t>Types of leukemia</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>multiple-myeloma-treatment</t>
+          <t>types-of-leukemia</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/multiple-myeloma-treatment.html</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/types-of-leukemia.html</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -959,25 +959,25 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Blood tests used in cancer diagnosis</t>
+          <t>Multiple myeloma treatment</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>blood-tests-cancer-diagnosis</t>
+          <t>multiple-myeloma-treatment</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/blood-tests-cancer-diagnosis.html</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/multiple-myeloma-treatment.html</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -986,25 +986,25 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>PET-CT scan explained for patients</t>
+          <t>Blood tests used in cancer diagnosis</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>pet-ct-scan-explained</t>
+          <t>blood-tests-cancer-diagnosis</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/pet-ct-scan-explained.html</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/blood-tests-cancer-diagnosis.html</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1013,25 +1013,25 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Palliative care in cancer</t>
+          <t>PET-CT scan explained for patients</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>palliative-care-cancer</t>
+          <t>pet-ct-scan-explained</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/palliative-care-cancer.html</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/pet-ct-scan-explained.html</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1040,25 +1040,25 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Genetic testing for cancer risk</t>
+          <t>Palliative care in cancer</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>genetic-testing-cancer-risk</t>
+          <t>palliative-care-cancer</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/genetic-testing-cancer-risk.html</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/palliative-care-cancer.html</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1067,25 +1067,25 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Hereditary cancer syndromes</t>
+          <t>Genetic testing for cancer risk</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>hereditary-cancer-syndromes</t>
+          <t>genetic-testing-cancer-risk</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/hereditary-cancer-syndromes.html</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/genetic-testing-cancer-risk.html</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1094,25 +1094,25 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Managing cancer recurrence</t>
+          <t>Hereditary cancer syndromes</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>managing-cancer-recurrence</t>
+          <t>hereditary-cancer-syndromes</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/managing-cancer-recurrence.html</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/hereditary-cancer-syndromes.html</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1121,25 +1121,25 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Immunotherapy side effects</t>
+          <t>Managing cancer recurrence</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>immunotherapy-side-effects</t>
+          <t>managing-cancer-recurrence</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/immunotherapy-side-effects.html</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/managing-cancer-recurrence.html</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1148,25 +1148,25 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Targeted therapy explained</t>
+          <t>Immunotherapy side effects</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>targeted-therapy-explained</t>
+          <t>immunotherapy-side-effects</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/targeted-therapy-explained.html</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/immunotherapy-side-effects.html</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1175,25 +1175,25 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Oral chemotherapy medications</t>
+          <t>Targeted therapy explained</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>oral-chemotherapy-medications</t>
+          <t>targeted-therapy-explained</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/oral-chemotherapy-medications.html</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/targeted-therapy-explained.html</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1202,25 +1202,25 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Chemotherapy port explained</t>
+          <t>Oral chemotherapy medications</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>chemotherapy-port-explained</t>
+          <t>oral-chemotherapy-medications</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy-port-explained.html</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/oral-chemotherapy-medications.html</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1229,25 +1229,25 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Cancer clinical trials in India</t>
+          <t>Chemotherapy port explained</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>cancer-clinical-trials-india</t>
+          <t>chemotherapy-port-explained</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-clinical-trials-india.html</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/chemotherapy-port-explained.html</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1256,25 +1256,25 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Questions to ask your oncologist</t>
+          <t>Cancer clinical trials in India</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>questions-to-ask-oncologist</t>
+          <t>cancer-clinical-trials-india</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/questions-to-ask-oncologist.html</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-clinical-trials-india.html</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1283,25 +1283,25 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Cancer survivorship care</t>
+          <t>Questions to ask your oncologist</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>cancer-survivorship-care</t>
+          <t>questions-to-ask-oncologist</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-survivorship-care.html</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/questions-to-ask-oncologist.html</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1310,25 +1310,25 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Fertility preservation before chemotherapy</t>
+          <t>Cancer survivorship care</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>fertility-preservation-chemotherapy</t>
+          <t>cancer-survivorship-care</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/fertility-preservation-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-survivorship-care.html</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1337,25 +1337,25 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Mouth sores during chemotherapy</t>
+          <t>Fertility preservation before chemotherapy</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>mouth-sores-chemotherapy</t>
+          <t>fertility-preservation-chemotherapy</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/mouth-sores-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/fertility-preservation-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1364,25 +1364,25 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Neuropathy from chemotherapy</t>
+          <t>Mouth sores during chemotherapy</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>chemotherapy-neuropathy</t>
+          <t>mouth-sores-chemotherapy</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy-neuropathy.html</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/mouth-sores-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1391,25 +1391,25 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Cancer and diabetes management</t>
+          <t>Neuropathy from chemotherapy</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>cancer-diabetes-management</t>
+          <t>chemotherapy-neuropathy</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-diabetes-management.html</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/chemotherapy-neuropathy.html</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1418,25 +1418,25 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Blood transfusion in cancer treatment</t>
+          <t>Cancer and diabetes management</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>blood-transfusion-cancer</t>
+          <t>cancer-diabetes-management</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/blood-transfusion-cancer.html</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-diabetes-management.html</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1445,25 +1445,25 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Anti-nausea medications for chemotherapy</t>
+          <t>Blood transfusion in cancer treatment</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>anti-nausea-medications-chemotherapy</t>
+          <t>blood-transfusion-cancer</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/anti-nausea-medications-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/blood-transfusion-cancer.html</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1472,25 +1472,25 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Cancer diagnosis process step by step</t>
+          <t>Anti-nausea medications for chemotherapy</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>cancer-diagnosis-process</t>
+          <t>anti-nausea-medications-chemotherapy</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-diagnosis-process.html</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/anti-nausea-medications-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1499,25 +1499,25 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Reading your pathology report</t>
+          <t>Cancer diagnosis process step by step</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>reading-pathology-report</t>
+          <t>cancer-diagnosis-process</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/reading-pathology-report.html</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-diagnosis-process.html</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1526,25 +1526,25 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Cancer prognosis what it means</t>
+          <t>Reading your pathology report</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>cancer-prognosis-explained</t>
+          <t>reading-pathology-report</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-prognosis-explained.html</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/reading-pathology-report.html</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1553,25 +1553,25 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Anaemia during cancer treatment</t>
+          <t>Cancer prognosis what it means</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>cancer-related-anaemia</t>
+          <t>cancer-prognosis-explained</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-related-anaemia.html</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-prognosis-explained.html</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1580,25 +1580,25 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Skin changes during chemotherapy</t>
+          <t>Anaemia during cancer treatment</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>skin-changes-chemotherapy</t>
+          <t>cancer-related-anaemia</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/skin-changes-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-related-anaemia.html</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1607,25 +1607,25 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Cancer treatment during pregnancy</t>
+          <t>Skin changes during chemotherapy</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>cancer-treatment-pregnancy</t>
+          <t>skin-changes-chemotherapy</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-treatment-pregnancy.html</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/skin-changes-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1634,25 +1634,25 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Triple negative breast cancer</t>
+          <t>Cancer treatment during pregnancy</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>triple-negative-breast-cancer</t>
+          <t>cancer-treatment-pregnancy</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/triple-negative-breast-cancer.html</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-treatment-pregnancy.html</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1661,25 +1661,25 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>HER2 positive breast cancer</t>
+          <t>Triple negative breast cancer</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>her2-positive-breast-cancer</t>
+          <t>triple-negative-breast-cancer</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/her2-positive-breast-cancer.html</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/triple-negative-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1688,25 +1688,25 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Stomach cancer symptoms</t>
+          <t>HER2 positive breast cancer</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>stomach-cancer-symptoms</t>
+          <t>her2-positive-breast-cancer</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/stomach-cancer-symptoms.html</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/her2-positive-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1715,25 +1715,25 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Kidney cancer treatment options</t>
+          <t>Stomach cancer symptoms</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>kidney-cancer-treatment</t>
+          <t>stomach-cancer-symptoms</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/kidney-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/stomach-cancer-symptoms.html</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1742,25 +1742,25 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Bladder cancer diagnosis</t>
+          <t>Kidney cancer treatment options</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>bladder-cancer-diagnosis</t>
+          <t>kidney-cancer-treatment</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/bladder-cancer-diagnosis.html</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/kidney-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1769,25 +1769,25 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Thyroid cancer types and treatment</t>
+          <t>Bladder cancer diagnosis</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>thyroid-cancer-treatment</t>
+          <t>bladder-cancer-diagnosis</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/thyroid-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/bladder-cancer-diagnosis.html</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1796,25 +1796,25 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Prostate cancer treatment options</t>
+          <t>Thyroid cancer types and treatment</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>prostate-cancer-treatment</t>
+          <t>thyroid-cancer-treatment</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/prostate-cancer-treatment.html</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/thyroid-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1823,25 +1823,25 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Esophageal cancer symptoms</t>
+          <t>Prostate cancer treatment options</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>esophageal-cancer-symptoms</t>
+          <t>prostate-cancer-treatment</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/esophageal-cancer-symptoms.html</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/prostate-cancer-treatment.html</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1850,25 +1850,25 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Cervical cancer prevention and HPV vaccine</t>
+          <t>Esophageal cancer symptoms</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>cervical-cancer-hpv-vaccine</t>
+          <t>esophageal-cancer-symptoms</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cervical-cancer-hpv-vaccine.html</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/esophageal-cancer-symptoms.html</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1877,25 +1877,25 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Cancer screening guidelines India</t>
+          <t>Cervical cancer prevention and HPV vaccine</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>cancer-screening-india</t>
+          <t>cervical-cancer-hpv-vaccine</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-screening-india.html</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cervical-cancer-hpv-vaccine.html</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1904,25 +1904,25 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Why cancer second opinion matters</t>
+          <t>Cancer screening guidelines India</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>why-cancer-second-opinion</t>
+          <t>cancer-screening-india</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/why-cancer-second-opinion.html</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-screening-india.html</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1931,25 +1931,25 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Preparing for your first chemotherapy session</t>
+          <t>Why cancer second opinion matters</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>preparing-for-chemotherapy</t>
+          <t>why-cancer-second-opinion</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/preparing-for-chemotherapy.html</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/why-cancer-second-opinion.html</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1958,25 +1958,25 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Cancer caregiver guide</t>
+          <t>Preparing for your first chemotherapy session</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>cancer-caregiver-guide</t>
+          <t>preparing-for-chemotherapy</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-caregiver-guide.html</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
+          <t>https://cioncancerdrowais.com/preparing-for-chemotherapy.html</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -1985,25 +1985,25 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Cancer pain relief options</t>
+          <t>Cancer caregiver guide</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>cancer-pain-relief</t>
+          <t>cancer-caregiver-guide</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-pain-relief.html</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
+          <t>https://cioncancerdrowais.com/cancer-caregiver-guide.html</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2012,27 +2012,27 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>(pre-existing page)</t>
+          <t>Cancer pain relief options</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>_template</t>
+          <t>cancer-pain-relief</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/_template.html</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Published ✓</t>
+          <t>https://cioncancerdrowais.com/cancer-pain-relief.html</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>_template</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/about.html</t>
+          <t>https://cioncancerdrowais.com/_template.html</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>book-appointment</t>
+          <t>about</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/book-appointment.html</t>
+          <t>https://cioncancerdrowais.com/about.html</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>cancer-cost-and-aarogyasri</t>
+          <t>book-appointment</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-cost-and-aarogyasri.html</t>
+          <t>https://cioncancerdrowais.com/book-appointment.html</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>cancer-staging-explained</t>
+          <t>cancer-cost-and-aarogyasri</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-staging-explained.html</t>
+          <t>https://cioncancerdrowais.com/cancer-cost-and-aarogyasri.html</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>cancer-treatment-options</t>
+          <t>cancer-staging-explained</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-treatment-options.html</t>
+          <t>https://cioncancerdrowais.com/cancer-staging-explained.html</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>cancer-warning-signs</t>
+          <t>cancer-treatment-options</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/cancer-warning-signs.html</t>
+          <t>https://cioncancerdrowais.com/cancer-treatment-options.html</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>caring-for-a-cancer-patient</t>
+          <t>cancer-warning-signs</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/caring-for-a-cancer-patient.html</t>
+          <t>https://cioncancerdrowais.com/cancer-warning-signs.html</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>chemotherapy-side-effects</t>
+          <t>caring-for-a-cancer-patient</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy-side-effects.html</t>
+          <t>https://cioncancerdrowais.com/caring-for-a-cancer-patient.html</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>chemotherapy-side-effects</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/chemotherapy.html</t>
+          <t>https://cioncancerdrowais.com/chemotherapy-side-effects.html</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>chemotherapy</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/faq.html</t>
+          <t>https://cioncancerdrowais.com/chemotherapy.html</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>immunotherapy</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/immunotherapy.html</t>
+          <t>https://cioncancerdrowais.com/faq.html</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>immunotherapy</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/index.html</t>
+          <t>https://cioncancerdrowais.com/immunotherapy.html</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>low-white-blood-count-during-chemotherapy</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/low-white-blood-count-during-chemotherapy.html</t>
+          <t>https://cioncancerdrowais.com/index.html</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>lung-cancer</t>
+          <t>low-white-blood-count-during-chemotherapy</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/lung-cancer.html</t>
+          <t>https://cioncancerdrowais.com/low-white-blood-count-during-chemotherapy.html</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>lung-cancer</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/privacy.html</t>
+          <t>https://cioncancerdrowais.com/lung-cancer.html</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>second-opinion</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/second-opinion.html</t>
+          <t>https://cioncancerdrowais.com/privacy.html</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>targeted-therapy</t>
+          <t>second-opinion</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/targeted-therapy.html</t>
+          <t>https://cioncancerdrowais.com/second-opinion.html</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>understanding-cancer</t>
+          <t>targeted-therapy</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>https://cioncancerdrowais.com/understanding-cancer.html</t>
+          <t>https://cioncancerdrowais.com/targeted-therapy.html</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
@@ -2535,15 +2535,42 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
+          <t>understanding-cancer</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>https://cioncancerdrowais.com/understanding-cancer.html</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Published ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>(pre-existing page)</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
           <t>what-is-a-biopsy</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>https://cioncancerdrowais.com/what-is-a-biopsy.html</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>Published ✓</t>
         </is>
@@ -2627,6 +2654,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2757,7 +2785,7 @@
           <t>https://cioncancerdrvinay.com/laparoscopic-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2784,7 +2812,7 @@
           <t>https://cioncancerdrvinay.com/lumpectomy-breast-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2811,7 +2839,7 @@
           <t>https://cioncancerdrvinay.com/mastectomy-types-recovery.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2838,7 +2866,7 @@
           <t>https://cioncancerdrvinay.com/sentinel-lymph-node-biopsy.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2865,7 +2893,7 @@
           <t>https://cioncancerdrvinay.com/thyroid-surgery-cancer.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2892,7 +2920,7 @@
           <t>https://cioncancerdrvinay.com/colorectal-surgery.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2919,7 +2947,7 @@
           <t>https://cioncancerdrvinay.com/colostomy-explained.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2946,7 +2974,7 @@
           <t>https://cioncancerdrvinay.com/ileostomy-care.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -2973,7 +3001,7 @@
           <t>https://cioncancerdrvinay.com/liver-resection-surgery.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3000,7 +3028,7 @@
           <t>https://cioncancerdrvinay.com/splenectomy-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3027,7 +3055,7 @@
           <t>https://cioncancerdrvinay.com/nephrectomy-surgery.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3054,7 +3082,7 @@
           <t>https://cioncancerdrvinay.com/ovarian-debulking-surgery.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3081,7 +3109,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-wound-care.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3108,7 +3136,7 @@
           <t>https://cioncancerdrvinay.com/post-surgery-pain-management.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3135,7 +3163,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3162,7 +3190,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-complications.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3189,7 +3217,7 @@
           <t>https://cioncancerdrvinay.com/dvt-prevention-after-surgery.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3216,7 +3244,7 @@
           <t>https://cioncancerdrvinay.com/pre-surgery-preparation.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3243,7 +3271,7 @@
           <t>https://cioncancerdrvinay.com/nutrition-before-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3270,7 +3298,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-anaesthesia.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3297,7 +3325,7 @@
           <t>https://cioncancerdrvinay.com/surgical-staging-cancer.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3324,7 +3352,7 @@
           <t>https://cioncancerdrvinay.com/curative-vs-palliative-surgery.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3351,7 +3379,7 @@
           <t>https://cioncancerdrvinay.com/breast-reconstruction-after-mastectomy.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3378,7 +3406,7 @@
           <t>https://cioncancerdrvinay.com/port-insertion-surgery.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3405,7 +3433,7 @@
           <t>https://cioncancerdrvinay.com/vats-thoracoscopy.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3432,7 +3460,7 @@
           <t>https://cioncancerdrvinay.com/esophagectomy-surgery.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3459,7 +3487,7 @@
           <t>https://cioncancerdrvinay.com/gastrectomy-types.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3486,7 +3514,7 @@
           <t>https://cioncancerdrvinay.com/pancreatectomy-procedure.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3513,7 +3541,7 @@
           <t>https://cioncancerdrvinay.com/whipple-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3540,7 +3568,7 @@
           <t>https://cioncancerdrvinay.com/hernia-after-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3567,7 +3595,7 @@
           <t>https://cioncancerdrvinay.com/scar-management-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3594,7 +3622,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-elderly.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3621,7 +3649,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-cost-hyderabad.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3648,7 +3676,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-questions.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3675,7 +3703,7 @@
           <t>https://cioncancerdrvinay.com/life-after-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3702,7 +3730,7 @@
           <t>https://cioncancerdrvinay.com/robotic-cancer-surgery-india.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3729,7 +3757,7 @@
           <t>https://cioncancerdrvinay.com/abdominal-cancer-surgery-recovery.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3756,7 +3784,7 @@
           <t>https://cioncancerdrvinay.com/rectal-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3783,7 +3811,7 @@
           <t>https://cioncancerdrvinay.com/parathyroid-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3810,7 +3838,7 @@
           <t>https://cioncancerdrvinay.com/adrenalectomy-procedure.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3837,7 +3865,7 @@
           <t>https://cioncancerdrvinay.com/pelvic-exenteration-surgery.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3864,7 +3892,7 @@
           <t>https://cioncancerdrvinay.com/lymph-node-removal-surgery.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3891,7 +3919,7 @@
           <t>https://cioncancerdrvinay.com/cancer-biopsy-types.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3918,7 +3946,7 @@
           <t>https://cioncancerdrvinay.com/intraoperative-frozen-section.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3945,7 +3973,7 @@
           <t>https://cioncancerdrvinay.com/cancer-resection-margins.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3972,7 +4000,7 @@
           <t>https://cioncancerdrvinay.com/cancer-surgery-second-opinion.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -3999,7 +4027,7 @@
           <t>https://cioncancerdrvinay.com/day-surgery-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4026,7 +4054,7 @@
           <t>https://cioncancerdrvinay.com/reconstructive-flap-surgery.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4053,7 +4081,7 @@
           <t>https://cioncancerdrvinay.com/questions-for-cancer-surgeon.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4777,7 +4805,7 @@
           <t>https://cioncancerdrmurali.com/skin-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4804,7 +4832,7 @@
           <t>https://cioncancerdrmurali.com/retroperitoneal-sarcoma-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4831,7 +4859,7 @@
           <t>https://cioncancerdrmurali.com/leiomyosarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4858,7 +4886,7 @@
           <t>https://cioncancerdrmurali.com/liposarcoma-surgery.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4885,7 +4913,7 @@
           <t>https://cioncancerdrmurali.com/limb-sparing-surgery.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4912,7 +4940,7 @@
           <t>https://cioncancerdrmurali.com/osteosarcoma-limb-salvage.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4939,7 +4967,7 @@
           <t>https://cioncancerdrmurali.com/rectal-sphincter-preservation.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4966,7 +4994,7 @@
           <t>https://cioncancerdrmurali.com/low-anterior-resection.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -4993,7 +5021,7 @@
           <t>https://cioncancerdrmurali.com/sigmoid-colon-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5020,7 +5048,7 @@
           <t>https://cioncancerdrmurali.com/laparoscopic-bowel-resection.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5047,7 +5075,7 @@
           <t>https://cioncancerdrmurali.com/hemorrhoids-vs-rectal-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5074,7 +5102,7 @@
           <t>https://cioncancerdrmurali.com/liver-metastases-surgery.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5101,7 +5129,7 @@
           <t>https://cioncancerdrmurali.com/thermal-ablation-liver-tumours.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5128,7 +5156,7 @@
           <t>https://cioncancerdrmurali.com/bile-duct-repair-surgery.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5155,7 +5183,7 @@
           <t>https://cioncancerdrmurali.com/cholecystectomy-gallbladder-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5182,7 +5210,7 @@
           <t>https://cioncancerdrmurali.com/total-gastrectomy-recovery.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5209,7 +5237,7 @@
           <t>https://cioncancerdrmurali.com/small-bowel-resection.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5236,7 +5264,7 @@
           <t>https://cioncancerdrmurali.com/peritoneal-wash-cytology.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5263,7 +5291,7 @@
           <t>https://cioncancerdrmurali.com/second-look-surgery-ovarian.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5290,7 +5318,7 @@
           <t>https://cioncancerdrmurali.com/interval-debulking-surgery.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5317,7 +5345,7 @@
           <t>https://cioncancerdrmurali.com/cancer-surgery-diabetes.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5344,7 +5372,7 @@
           <t>https://cioncancerdrmurali.com/anastomosis-leak-prevention.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5371,7 +5399,7 @@
           <t>https://cioncancerdrmurali.com/ewing-sarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5398,7 +5426,7 @@
           <t>https://cioncancerdrmurali.com/synovial-sarcoma-treatment.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5425,7 +5453,7 @@
           <t>https://cioncancerdrmurali.com/amputation-bone-cancer.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5452,7 +5480,7 @@
           <t>https://cioncancerdrmurali.com/right-hemicolectomy.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5479,7 +5507,7 @@
           <t>https://cioncancerdrmurali.com/left-hemicolectomy.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5506,7 +5534,7 @@
           <t>https://cioncancerdrmurali.com/d2-lymphadenectomy-gastric.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5533,7 +5561,7 @@
           <t>https://cioncancerdrmurali.com/portal-vein-embolization.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5560,7 +5588,7 @@
           <t>https://cioncancerdrmurali.com/distal-pancreatectomy.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5587,7 +5615,7 @@
           <t>https://cioncancerdrmurali.com/radical-cholecystectomy-gallbladder.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5614,7 +5642,7 @@
           <t>https://cioncancerdrmurali.com/gist-tumour-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5641,7 +5669,7 @@
           <t>https://cioncancerdrmurali.com/mesenteric-tumour-resection.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5668,7 +5696,7 @@
           <t>https://cioncancerdrmurali.com/colon-cancer-peritoneal-spread.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5695,7 +5723,7 @@
           <t>https://cioncancerdrmurali.com/uterine-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5722,7 +5750,7 @@
           <t>https://cioncancerdrmurali.com/malignant-ascites-management.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5749,7 +5777,7 @@
           <t>https://cioncancerdrmurali.com/laparoscopic-staging-peritoneal.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5776,7 +5804,7 @@
           <t>https://cioncancerdrmurali.com/transverse-colon-cancer.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5803,7 +5831,7 @@
           <t>https://cioncancerdrmurali.com/anorectal-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5830,7 +5858,7 @@
           <t>https://cioncancerdrmurali.com/diverticulitis-vs-colon-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5857,7 +5885,7 @@
           <t>https://cioncancerdrmurali.com/phantom-limb-pain-management.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5884,7 +5912,7 @@
           <t>https://cioncancerdrmurali.com/intraoperative-bleeding-management.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5911,7 +5939,7 @@
           <t>https://cioncancerdrmurali.com/microwave-ablation-liver.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5938,7 +5966,7 @@
           <t>https://cioncancerdrmurali.com/proximal-gastrectomy.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5965,7 +5993,7 @@
           <t>https://cioncancerdrmurali.com/pancreatic-resection-recovery.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -5992,7 +6020,7 @@
           <t>https://cioncancerdrmurali.com/abdominoperineal-resection.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6019,7 +6047,7 @@
           <t>https://cioncancerdrmurali.com/stoma-reversal-surgery.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6046,7 +6074,7 @@
           <t>https://cioncancerdrmurali.com/eras-protocol-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6073,7 +6101,7 @@
           <t>https://cioncancerdrmurali.com/cancer-surgery-blood-loss.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6825,7 +6853,7 @@
           <t>https://cioncancerdrsandeep.com/tongue-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6852,7 +6880,7 @@
           <t>https://cioncancerdrsandeep.com/lip-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6879,7 +6907,7 @@
           <t>https://cioncancerdrsandeep.com/buccal-mucosa-cancer.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6906,7 +6934,7 @@
           <t>https://cioncancerdrsandeep.com/floor-of-mouth-cancer.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6933,7 +6961,7 @@
           <t>https://cioncancerdrsandeep.com/laryngeal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6960,7 +6988,7 @@
           <t>https://cioncancerdrsandeep.com/laryngectomy-voice-rehab.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -6987,7 +7015,7 @@
           <t>https://cioncancerdrsandeep.com/hypopharyngeal-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7014,7 +7042,7 @@
           <t>https://cioncancerdrsandeep.com/oropharyngeal-cancer-hpv.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7041,7 +7069,7 @@
           <t>https://cioncancerdrsandeep.com/tonsil-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7068,7 +7096,7 @@
           <t>https://cioncancerdrsandeep.com/nasopharyngeal-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7095,7 +7123,7 @@
           <t>https://cioncancerdrsandeep.com/nasal-cavity-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7122,7 +7150,7 @@
           <t>https://cioncancerdrsandeep.com/salivary-gland-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7149,7 +7177,7 @@
           <t>https://cioncancerdrsandeep.com/parotid-gland-surgery.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7176,7 +7204,7 @@
           <t>https://cioncancerdrsandeep.com/neck-dissection-types.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7203,7 +7231,7 @@
           <t>https://cioncancerdrsandeep.com/modified-radical-neck-dissection.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7230,7 +7258,7 @@
           <t>https://cioncancerdrsandeep.com/total-thyroidectomy.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7257,7 +7285,7 @@
           <t>https://cioncancerdrsandeep.com/papillary-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7284,7 +7312,7 @@
           <t>https://cioncancerdrsandeep.com/follicular-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7311,7 +7339,7 @@
           <t>https://cioncancerdrsandeep.com/medullary-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7338,7 +7366,7 @@
           <t>https://cioncancerdrsandeep.com/thyroid-cancer-recurrence.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7365,7 +7393,7 @@
           <t>https://cioncancerdrsandeep.com/skull-base-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7392,7 +7420,7 @@
           <t>https://cioncancerdrsandeep.com/paraganglioma-treatment.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7419,7 +7447,7 @@
           <t>https://cioncancerdrsandeep.com/adenoid-cystic-carcinoma.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7446,7 +7474,7 @@
           <t>https://cioncancerdrsandeep.com/mucoepidermoid-carcinoma.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7473,7 +7501,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-trismus.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7500,7 +7528,7 @@
           <t>https://cioncancerdrsandeep.com/xerostomia-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7527,7 +7555,7 @@
           <t>https://cioncancerdrsandeep.com/dysphagia-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7554,7 +7582,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-rehabilitation.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7581,7 +7609,7 @@
           <t>https://cioncancerdrsandeep.com/speech-therapy-laryngectomy.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7608,7 +7636,7 @@
           <t>https://cioncancerdrsandeep.com/neck-lump-causes.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7635,7 +7663,7 @@
           <t>https://cioncancerdrsandeep.com/hoarseness-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7662,7 +7690,7 @@
           <t>https://cioncancerdrsandeep.com/mouth-ulcer-cancer-warning.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7689,7 +7717,7 @@
           <t>https://cioncancerdrsandeep.com/leukoplakia-oral-cancer.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7716,7 +7744,7 @@
           <t>https://cioncancerdrsandeep.com/submucous-fibrosis-cancer.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7743,7 +7771,7 @@
           <t>https://cioncancerdrsandeep.com/tobacco-oral-cancer.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7770,7 +7798,7 @@
           <t>https://cioncancerdrsandeep.com/base-of-tongue-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7797,7 +7825,7 @@
           <t>https://cioncancerdrsandeep.com/partial-laryngectomy.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7824,7 +7852,7 @@
           <t>https://cioncancerdrsandeep.com/palate-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7851,7 +7879,7 @@
           <t>https://cioncancerdrsandeep.com/jaw-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7878,7 +7906,7 @@
           <t>https://cioncancerdrsandeep.com/paranasal-sinus-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7905,7 +7933,7 @@
           <t>https://cioncancerdrsandeep.com/anaplastic-thyroid-cancer.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7932,7 +7960,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-hyderabad.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7959,7 +7987,7 @@
           <t>https://cioncancerdrsandeep.com/swallowing-therapy-cancer.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -7986,7 +8014,7 @@
           <t>https://cioncancerdrsandeep.com/radiation-head-neck-surgery.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8013,7 +8041,7 @@
           <t>https://cioncancerdrsandeep.com/chemotherapy-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8040,7 +8068,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-nutrition.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8067,7 +8095,7 @@
           <t>https://cioncancerdrsandeep.com/tracheostomy-care-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8094,7 +8122,7 @@
           <t>https://cioncancerdrsandeep.com/reconstruction-head-neck-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8121,7 +8149,7 @@
           <t>https://cioncancerdrsandeep.com/head-neck-cancer-surgeon-questions.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8873,7 +8901,7 @@
           <t>https://cioncancerdrkiranmayee.com/lung-cancer-types-stages.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8900,7 +8928,7 @@
           <t>https://cioncancerdrkiranmayee.com/hormone-receptor-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8927,7 +8955,7 @@
           <t>https://cioncancerdrkiranmayee.com/non-hodgkin-lymphoma.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8954,7 +8982,7 @@
           <t>https://cioncancerdrkiranmayee.com/chronic-myeloid-leukemia.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -8981,7 +9009,7 @@
           <t>https://cioncancerdrkiranmayee.com/melanoma-treatment.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9008,7 +9036,7 @@
           <t>https://cioncancerdrkiranmayee.com/pancreatic-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9035,7 +9063,7 @@
           <t>https://cioncancerdrkiranmayee.com/liver-cancer-treatment-hyderabad.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9062,7 +9090,7 @@
           <t>https://cioncancerdrkiranmayee.com/uterine-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9089,7 +9117,7 @@
           <t>https://cioncancerdrkiranmayee.com/bone-cancer-types.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9116,7 +9144,7 @@
           <t>https://cioncancerdrkiranmayee.com/soft-tissue-sarcoma.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9143,7 +9171,7 @@
           <t>https://cioncancerdrkiranmayee.com/neuroendocrine-tumours.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9170,7 +9198,7 @@
           <t>https://cioncancerdrkiranmayee.com/bile-duct-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9197,7 +9225,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-blood-clots-dvt.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9224,7 +9252,7 @@
           <t>https://cioncancerdrkiranmayee.com/checkpoint-inhibitors-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9251,7 +9279,7 @@
           <t>https://cioncancerdrkiranmayee.com/car-t-cell-therapy.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9278,7 +9306,7 @@
           <t>https://cioncancerdrkiranmayee.com/parp-inhibitors-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9305,7 +9333,7 @@
           <t>https://cioncancerdrkiranmayee.com/cdk-inhibitors-breast-cancer.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9332,7 +9360,7 @@
           <t>https://cioncancerdrkiranmayee.com/combination-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9359,7 +9387,7 @@
           <t>https://cioncancerdrkiranmayee.com/weight-management-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9386,7 +9414,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-mental-health.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9413,7 +9441,7 @@
           <t>https://cioncancerdrkiranmayee.com/exercise-during-cancer.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9440,7 +9468,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-pain-types.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9467,7 +9495,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-end-of-life-care.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9494,7 +9522,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-rehabilitation.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9521,7 +9549,7 @@
           <t>https://cioncancerdrkiranmayee.com/return-to-work-cancer.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9548,7 +9576,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-insurance-india.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9575,7 +9603,7 @@
           <t>https://cioncancerdrkiranmayee.com/government-cancer-schemes-india.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9602,7 +9630,7 @@
           <t>https://cioncancerdrkiranmayee.com/telemedicine-cancer-followup.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9629,7 +9657,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-young-adults.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9656,7 +9684,7 @@
           <t>https://cioncancerdrkiranmayee.com/antibody-drug-conjugates.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9683,7 +9711,7 @@
           <t>https://cioncancerdrkiranmayee.com/maintenance-therapy-cancer.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9710,7 +9738,7 @@
           <t>https://cioncancerdrkiranmayee.com/adjuvant-neoadjuvant-therapy.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9737,7 +9765,7 @@
           <t>https://cioncancerdrkiranmayee.com/dose-dense-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9764,7 +9792,7 @@
           <t>https://cioncancerdrkiranmayee.com/growth-factors-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9791,7 +9819,7 @@
           <t>https://cioncancerdrkiranmayee.com/febrile-neutropenia.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9818,7 +9846,7 @@
           <t>https://cioncancerdrkiranmayee.com/cardio-oncology-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9845,7 +9873,7 @@
           <t>https://cioncancerdrkiranmayee.com/second-primary-cancer.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9872,7 +9900,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-treatment-at-home.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9899,7 +9927,7 @@
           <t>https://cioncancerdrkiranmayee.com/oral-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9926,7 +9954,7 @@
           <t>https://cioncancerdrkiranmayee.com/colon-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9953,7 +9981,7 @@
           <t>https://cioncancerdrkiranmayee.com/pancreatic-cancer-warning-signs.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -9980,7 +10008,7 @@
           <t>https://cioncancerdrkiranmayee.com/vulvar-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10007,7 +10035,7 @@
           <t>https://cioncancerdrkiranmayee.com/penile-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10034,7 +10062,7 @@
           <t>https://cioncancerdrkiranmayee.com/anal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10061,7 +10089,7 @@
           <t>https://cioncancerdrkiranmayee.com/adrenal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10088,7 +10116,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-genetic-counselling.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10115,7 +10143,7 @@
           <t>https://cioncancerdrkiranmayee.com/complementary-medicine-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10142,7 +10170,7 @@
           <t>https://cioncancerdrkiranmayee.com/hospice-care-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10169,7 +10197,7 @@
           <t>https://cioncancerdrkiranmayee.com/cancer-caregiver-burnout.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10921,7 +10949,7 @@
           <t>https://cioncancerdrbasudev.com/autologous-bmt.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10948,7 +10976,7 @@
           <t>https://cioncancerdrbasudev.com/allogeneic-bmt.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -10975,7 +11003,7 @@
           <t>https://cioncancerdrbasudev.com/stem-cell-donation.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11002,7 +11030,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-donor-compatibility.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11029,7 +11057,7 @@
           <t>https://cioncancerdrbasudev.com/bmt-recovery-timeline.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11056,7 +11084,7 @@
           <t>https://cioncancerdrbasudev.com/graft-versus-host-disease.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11083,7 +11111,7 @@
           <t>https://cioncancerdrbasudev.com/chronic-gvhd-management.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11110,7 +11138,7 @@
           <t>https://cioncancerdrbasudev.com/what-is-leukemia.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11137,7 +11165,7 @@
           <t>https://cioncancerdrbasudev.com/acute-myeloid-leukemia.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11164,7 +11192,7 @@
           <t>https://cioncancerdrbasudev.com/acute-lymphoblastic-leukemia.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11191,7 +11219,7 @@
           <t>https://cioncancerdrbasudev.com/chronic-lymphocytic-leukemia.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11218,7 +11246,7 @@
           <t>https://cioncancerdrbasudev.com/hairy-cell-leukemia.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11245,7 +11273,7 @@
           <t>https://cioncancerdrbasudev.com/myelodysplastic-syndrome.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11272,7 +11300,7 @@
           <t>https://cioncancerdrbasudev.com/myelofibrosis-treatment.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11299,7 +11327,7 @@
           <t>https://cioncancerdrbasudev.com/polycythemia-vera.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11326,7 +11354,7 @@
           <t>https://cioncancerdrbasudev.com/essential-thrombocythemia.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11353,7 +11381,7 @@
           <t>https://cioncancerdrbasudev.com/aplastic-anemia-treatment.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11380,7 +11408,7 @@
           <t>https://cioncancerdrbasudev.com/thalassemia-stem-cell-therapy.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11407,7 +11435,7 @@
           <t>https://cioncancerdrbasudev.com/hodgkin-lymphoma-treatment.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11434,7 +11462,7 @@
           <t>https://cioncancerdrbasudev.com/diffuse-large-b-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11461,7 +11489,7 @@
           <t>https://cioncancerdrbasudev.com/follicular-lymphoma.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11488,7 +11516,7 @@
           <t>https://cioncancerdrbasudev.com/mantle-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11515,7 +11543,7 @@
           <t>https://cioncancerdrbasudev.com/burkitt-lymphoma.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11542,7 +11570,7 @@
           <t>https://cioncancerdrbasudev.com/t-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11569,7 +11597,7 @@
           <t>https://cioncancerdrbasudev.com/waldenstrom-macroglobulinemia.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11596,7 +11624,7 @@
           <t>https://cioncancerdrbasudev.com/multiple-myeloma-bone-pain.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11623,7 +11651,7 @@
           <t>https://cioncancerdrbasudev.com/smoldering-myeloma.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11650,7 +11678,7 @@
           <t>https://cioncancerdrbasudev.com/bortezomib-myeloma.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11677,7 +11705,7 @@
           <t>https://cioncancerdrbasudev.com/daratumumab-myeloma.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11704,7 +11732,7 @@
           <t>https://cioncancerdrbasudev.com/venetoclax-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11731,7 +11759,7 @@
           <t>https://cioncancerdrbasudev.com/ibrutinib-cll.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11758,7 +11786,7 @@
           <t>https://cioncancerdrbasudev.com/rituximab-lymphoma.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11785,7 +11813,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-biopsy-procedure.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11812,7 +11840,7 @@
           <t>https://cioncancerdrbasudev.com/cbc-cancer-interpretation.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11839,7 +11867,7 @@
           <t>https://cioncancerdrbasudev.com/flow-cytometry-cancer.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11866,7 +11894,7 @@
           <t>https://cioncancerdrbasudev.com/fish-testing-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11893,7 +11921,7 @@
           <t>https://cioncancerdrbasudev.com/blood-cancer-treatment-hyderabad.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11920,7 +11948,7 @@
           <t>https://cioncancerdrbasudev.com/bmt-cost-india.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11947,7 +11975,7 @@
           <t>https://cioncancerdrbasudev.com/life-after-bmt.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -11974,7 +12002,7 @@
           <t>https://cioncancerdrbasudev.com/infections-after-bmt.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12001,7 +12029,7 @@
           <t>https://cioncancerdrbasudev.com/engraftment-syndrome.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12028,7 +12056,7 @@
           <t>https://cioncancerdrbasudev.com/peripheral-blood-stem-cell-harvest.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12055,7 +12083,7 @@
           <t>https://cioncancerdrbasudev.com/cord-blood-transplant.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12082,7 +12110,7 @@
           <t>https://cioncancerdrbasudev.com/haploidentical-transplant.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12109,7 +12137,7 @@
           <t>https://cioncancerdrbasudev.com/reduced-intensity-conditioning-bmt.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12136,7 +12164,7 @@
           <t>https://cioncancerdrbasudev.com/nk-cell-lymphoma.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12163,7 +12191,7 @@
           <t>https://cioncancerdrbasudev.com/amyloidosis-blood-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12190,7 +12218,7 @@
           <t>https://cioncancerdrbasudev.com/bone-marrow-failure-syndromes.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12217,7 +12245,7 @@
           <t>https://cioncancerdrbasudev.com/blood-cancer-diet-nutrition.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12969,7 +12997,7 @@
           <t>https://cioncancerdrraghvendra.com/external-beam-radiation.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -12996,7 +13024,7 @@
           <t>https://cioncancerdrraghvendra.com/imrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13023,7 +13051,7 @@
           <t>https://cioncancerdrraghvendra.com/igrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13050,7 +13078,7 @@
           <t>https://cioncancerdrraghvendra.com/stereotactic-radiosurgery.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13077,7 +13105,7 @@
           <t>https://cioncancerdrraghvendra.com/sbrt-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13104,7 +13132,7 @@
           <t>https://cioncancerdrraghvendra.com/brachytherapy-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13131,7 +13159,7 @@
           <t>https://cioncancerdrraghvendra.com/high-dose-rate-brachytherapy.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13158,7 +13186,7 @@
           <t>https://cioncancerdrraghvendra.com/breast-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13185,7 +13213,7 @@
           <t>https://cioncancerdrraghvendra.com/cervical-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13212,7 +13240,7 @@
           <t>https://cioncancerdrraghvendra.com/prostate-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13239,7 +13267,7 @@
           <t>https://cioncancerdrraghvendra.com/lung-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13266,7 +13294,7 @@
           <t>https://cioncancerdrraghvendra.com/head-neck-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13293,7 +13321,7 @@
           <t>https://cioncancerdrraghvendra.com/rectal-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13320,7 +13348,7 @@
           <t>https://cioncancerdrraghvendra.com/whole-brain-radiation.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13347,7 +13375,7 @@
           <t>https://cioncancerdrraghvendra.com/palliative-radiation-bone-pain.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13374,7 +13402,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-side-effects.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13401,7 +13429,7 @@
           <t>https://cioncancerdrraghvendra.com/skin-reactions-radiation.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13428,7 +13456,7 @@
           <t>https://cioncancerdrraghvendra.com/fatigue-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13455,7 +13483,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-mucositis.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13482,7 +13510,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-enteritis.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13509,7 +13537,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-cystitis.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13536,7 +13564,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-simulation.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13563,7 +13591,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-treatment-planning.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13590,7 +13618,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-fractions.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13617,7 +13645,7 @@
           <t>https://cioncancerdrraghvendra.com/hypofractionated-radiation.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13644,7 +13672,7 @@
           <t>https://cioncancerdrraghvendra.com/concurrent-chemoradiation.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13671,7 +13699,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-brain-metastases.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13698,7 +13726,7 @@
           <t>https://cioncancerdrraghvendra.com/spinal-cord-compression-radiation.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13725,7 +13753,7 @@
           <t>https://cioncancerdrraghvendra.com/sabr-liver-tumours.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13752,7 +13780,7 @@
           <t>https://cioncancerdrraghvendra.com/radioiodine-therapy-thyroid.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13779,7 +13807,7 @@
           <t>https://cioncancerdrraghvendra.com/prrt-neuroendocrine-tumours.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13806,7 +13834,7 @@
           <t>https://cioncancerdrraghvendra.com/lutetium-dotatate-therapy.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13833,7 +13861,7 @@
           <t>https://cioncancerdrraghvendra.com/y90-radioembolization.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13860,7 +13888,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-vs-surgery.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13887,7 +13915,7 @@
           <t>https://cioncancerdrraghvendra.com/proton-therapy-vs-radiation.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13914,7 +13942,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-quality-of-life.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13941,7 +13969,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-myths.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13968,7 +13996,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-cost-hyderabad.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -13995,7 +14023,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-safety.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14022,7 +14050,7 @@
           <t>https://cioncancerdrraghvendra.com/re-irradiation-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14049,7 +14077,7 @@
           <t>https://cioncancerdrraghvendra.com/second-cancer-after-radiation.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14076,7 +14104,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-protection-family.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14103,7 +14131,7 @@
           <t>https://cioncancerdrraghvendra.com/radiation-therapy-fertility.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14130,7 +14158,7 @@
           <t>https://cioncancerdrraghvendra.com/accelerated-partial-breast-irradiation.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14157,7 +14185,7 @@
           <t>https://cioncancerdrraghvendra.com/intraoperative-radiation-therapy.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14184,7 +14212,7 @@
           <t>https://cioncancerdrraghvendra.com/total-body-irradiation.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14211,7 +14239,7 @@
           <t>https://cioncancerdrraghvendra.com/radiofrequency-ablation-cancer.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14238,7 +14266,7 @@
           <t>https://cioncancerdrraghvendra.com/tace-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -14265,7 +14293,7 @@
           <t>https://cioncancerdrraghvendra.com/esophageal-cancer-radiation.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15017,7 +15045,7 @@
           <t>https://cioncancerdrcraghavendra.info/rectal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15044,7 +15072,7 @@
           <t>https://cioncancerdrcraghavendra.info/appendix-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15071,7 +15099,7 @@
           <t>https://cioncancerdrcraghavendra.info/peritoneal-carcinomatosis.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15098,7 +15126,7 @@
           <t>https://cioncancerdrcraghavendra.info/cea-tumor-marker.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15125,7 +15153,7 @@
           <t>https://cioncancerdrcraghavendra.info/ca125-test-explained.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15152,7 +15180,7 @@
           <t>https://cioncancerdrcraghavendra.info/ca19-9-test-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15179,7 +15207,7 @@
           <t>https://cioncancerdrcraghavendra.info/afp-test-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15206,7 +15234,7 @@
           <t>https://cioncancerdrcraghavendra.info/psa-test-explained.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15233,7 +15261,7 @@
           <t>https://cioncancerdrcraghavendra.info/core-needle-biopsy.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15260,7 +15288,7 @@
           <t>https://cioncancerdrcraghavendra.info/liquid-biopsy-cancer.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15287,7 +15315,7 @@
           <t>https://cioncancerdrcraghavendra.info/next-generation-sequencing-cancer.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15314,7 +15342,7 @@
           <t>https://cioncancerdrcraghavendra.info/microsatellite-instability.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15341,7 +15369,7 @@
           <t>https://cioncancerdrcraghavendra.info/kras-mutation-colorectal.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15368,7 +15396,7 @@
           <t>https://cioncancerdrcraghavendra.info/egfr-mutation-lung-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15395,7 +15423,7 @@
           <t>https://cioncancerdrcraghavendra.info/braf-mutation-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15422,7 +15450,7 @@
           <t>https://cioncancerdrcraghavendra.info/pdl1-expression-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15449,7 +15477,7 @@
           <t>https://cioncancerdrcraghavendra.info/precision-oncology-hyderabad.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15476,7 +15504,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-diet-myths.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15503,7 +15531,7 @@
           <t>https://cioncancerdrcraghavendra.info/sugar-cancer-link.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15530,7 +15558,7 @@
           <t>https://cioncancerdrcraghavendra.info/alcohol-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15557,7 +15585,7 @@
           <t>https://cioncancerdrcraghavendra.info/obesity-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15584,7 +15612,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-prevention-strategies.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15611,7 +15639,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-early-detection-india.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15638,7 +15666,7 @@
           <t>https://cioncancerdrcraghavendra.info/colonoscopy-screening.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15665,7 +15693,7 @@
           <t>https://cioncancerdrcraghavendra.info/mammography-screening.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15692,7 +15720,7 @@
           <t>https://cioncancerdrcraghavendra.info/pap-smear-screening.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15719,7 +15747,7 @@
           <t>https://cioncancerdrcraghavendra.info/recist-criteria-cancer.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15746,7 +15774,7 @@
           <t>https://cioncancerdrcraghavendra.info/adjuvant-chemotherapy-explained.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15773,7 +15801,7 @@
           <t>https://cioncancerdrcraghavendra.info/bone-marrow-suppression.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15800,7 +15828,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-biomarkers-explained.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15827,7 +15855,7 @@
           <t>https://cioncancerdrcraghavendra.info/biliary-tract-cancer.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15854,7 +15882,7 @@
           <t>https://cioncancerdrcraghavendra.info/duodenal-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15881,7 +15909,7 @@
           <t>https://cioncancerdrcraghavendra.info/small-intestine-cancer-treatment.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15908,7 +15936,7 @@
           <t>https://cioncancerdrcraghavendra.info/tumor-biopsy-types.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15935,7 +15963,7 @@
           <t>https://cioncancerdrcraghavendra.info/smoking-cancer-prevention.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15962,7 +15990,7 @@
           <t>https://cioncancerdrcraghavendra.info/red-meat-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -15989,7 +16017,7 @@
           <t>https://cioncancerdrcraghavendra.info/stress-cancer-link.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16016,7 +16044,7 @@
           <t>https://cioncancerdrcraghavendra.info/turmeric-cancer-research.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16043,7 +16071,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-treatment-cost-india.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16070,7 +16098,7 @@
           <t>https://cioncancerdrcraghavendra.info/ayushman-bharat-cancer.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16097,7 +16125,7 @@
           <t>https://cioncancerdrcraghavendra.info/cancer-screening-age-guidelines.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16124,7 +16152,7 @@
           <t>https://cioncancerdrcraghavendra.info/tumor-mutational-burden.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16151,7 +16179,7 @@
           <t>https://cioncancerdrcraghavendra.info/msi-high-immunotherapy.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16178,7 +16206,7 @@
           <t>https://cioncancerdrcraghavendra.info/colorectal-cancer-followup.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16205,7 +16233,7 @@
           <t>https://cioncancerdrcraghavendra.info/kras-wildtype-colorectal.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16232,7 +16260,7 @@
           <t>https://cioncancerdrcraghavendra.info/stoma-care-colorectal.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16259,7 +16287,7 @@
           <t>https://cioncancerdrcraghavendra.info/rectal-bleeding-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16286,7 +16314,7 @@
           <t>https://cioncancerdrcraghavendra.info/bowel-habits-cancer-signs.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -16313,7 +16341,7 @@
           <t>https://cioncancerdrcraghavendra.info/iron-deficiency-anaemia-cancer.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17093,7 +17121,7 @@
           <t>https://cioncancerdrimad.com/hipec-ovarian-cancer.html</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17120,7 +17148,7 @@
           <t>https://cioncancerdrimad.com/hipec-colorectal-cancer.html</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17147,7 +17175,7 @@
           <t>https://cioncancerdrimad.com/hipec-gastric-cancer.html</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17174,7 +17202,7 @@
           <t>https://cioncancerdrimad.com/pipac-procedure-explained.html</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17201,7 +17229,7 @@
           <t>https://cioncancerdrimad.com/pipac-vs-hipec.html</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17228,7 +17256,7 @@
           <t>https://cioncancerdrimad.com/cytoreductive-surgery-explained.html</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17255,7 +17283,7 @@
           <t>https://cioncancerdrimad.com/pci-score-peritoneal-cancer.html</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17282,7 +17310,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-metastases-treatment.html</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17309,7 +17337,7 @@
           <t>https://cioncancerdrimad.com/pseudomyxoma-peritonei.html</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17336,7 +17364,7 @@
           <t>https://cioncancerdrimad.com/appendix-cancer-mucinous.html</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17363,7 +17391,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-mesothelioma.html</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17390,7 +17418,7 @@
           <t>https://cioncancerdrimad.com/primary-peritoneal-cancer.html</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17417,7 +17445,7 @@
           <t>https://cioncancerdrimad.com/gastric-cancer-surgery-options.html</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17444,7 +17472,7 @@
           <t>https://cioncancerdrimad.com/total-gastrectomy-stomach-cancer.html</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17471,7 +17499,7 @@
           <t>https://cioncancerdrimad.com/d2-dissection-gastric-cancer.html</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17498,7 +17526,7 @@
           <t>https://cioncancerdrimad.com/esophagogastric-junction-cancer.html</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17525,7 +17553,7 @@
           <t>https://cioncancerdrimad.com/whipple-procedure-guide.html</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17552,7 +17580,7 @@
           <t>https://cioncancerdrimad.com/whipple-recovery-diet.html</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17579,7 +17607,7 @@
           <t>https://cioncancerdrimad.com/pylorus-preserving-whipple.html</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17606,7 +17634,7 @@
           <t>https://cioncancerdrimad.com/distal-pancreatectomy-splenectomy.html</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17633,7 +17661,7 @@
           <t>https://cioncancerdrimad.com/borderline-resectable-pancreatic.html</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17660,7 +17688,7 @@
           <t>https://cioncancerdrimad.com/hepatobiliary-cancer-hyderabad.html</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17687,7 +17715,7 @@
           <t>https://cioncancerdrimad.com/right-hepatectomy-liver-cancer.html</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17714,7 +17742,7 @@
           <t>https://cioncancerdrimad.com/klatskin-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17741,7 +17769,7 @@
           <t>https://cioncancerdrimad.com/gallbladder-cancer-surgery-options.html</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17768,7 +17796,7 @@
           <t>https://cioncancerdrimad.com/radical-cholecystectomy.html</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17795,7 +17823,7 @@
           <t>https://cioncancerdrimad.com/gist-treatment-imatinib.html</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17822,7 +17850,7 @@
           <t>https://cioncancerdrimad.com/retroperitoneal-tumour-surgery.html</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17849,7 +17877,7 @@
           <t>https://cioncancerdrimad.com/colorectal-liver-metastases-crs.html</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17876,7 +17904,7 @@
           <t>https://cioncancerdrimad.com/ovarian-cancer-hipec.html</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17903,7 +17931,7 @@
           <t>https://cioncancerdrimad.com/brca-ovarian-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17930,7 +17958,7 @@
           <t>https://cioncancerdrimad.com/malignant-ascites-treatment.html</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17957,7 +17985,7 @@
           <t>https://cioncancerdrimad.com/laparoscopic-staging.html</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -17984,7 +18012,7 @@
           <t>https://cioncancerdrimad.com/second-opinion-hipec.html</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18011,7 +18039,7 @@
           <t>https://cioncancerdrimad.com/hipec-cost-india.html</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18038,7 +18066,7 @@
           <t>https://cioncancerdrimad.com/life-after-hipec.html</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18065,7 +18093,7 @@
           <t>https://cioncancerdrimad.com/recovery-cytoreductive-surgery.html</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18092,7 +18120,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-cancer-surgery-possible.html</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18119,7 +18147,7 @@
           <t>https://cioncancerdrimad.com/hipec-contraindications.html</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18146,7 +18174,7 @@
           <t>https://cioncancerdrimad.com/intraperitoneal-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18173,7 +18201,7 @@
           <t>https://cioncancerdrimad.com/gastric-cancer-peritoneal-spread.html</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18200,7 +18228,7 @@
           <t>https://cioncancerdrimad.com/appendix-rupture-cancer-risk.html</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18227,7 +18255,7 @@
           <t>https://cioncancerdrimad.com/liver-cancer-resection.html</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18254,7 +18282,7 @@
           <t>https://cioncancerdrimad.com/portal-vein-pancreatic-cancer.html</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18281,7 +18309,7 @@
           <t>https://cioncancerdrimad.com/gi-cancer-second-opinion-hyderabad.html</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18308,7 +18336,7 @@
           <t>https://cioncancerdrimad.com/peritoneal-cancer-survival.html</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18335,7 +18363,7 @@
           <t>https://cioncancerdrimad.com/laparoscopic-vs-open-cancer-surgery.html</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18362,7 +18390,7 @@
           <t>https://cioncancerdrimad.com/crs-hipec-vs-chemotherapy.html</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -18389,7 +18417,7 @@
           <t>https://cioncancerdrimad.com/cancers-that-spread-to-peritoneum.html</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
